--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121254027</v>
       </c>
       <c r="B2" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121254027</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>57354</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121254027</v>
       </c>
       <c r="B2" t="n">
-        <v>57354</v>
+        <v>57355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121254027</v>
       </c>
       <c r="B2" t="n">
-        <v>57355</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122824296</v>
+        <v>122823780</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>79844</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,39 +934,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528849</v>
+        <v>528879</v>
       </c>
       <c r="R4" t="n">
-        <v>6998016</v>
+        <v>6998066</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,11 +994,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122824314</v>
+        <v>122824296</v>
       </c>
       <c r="B5" t="n">
-        <v>78499</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,37 +1036,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528828</v>
+        <v>528849</v>
       </c>
       <c r="R5" t="n">
-        <v>6998005</v>
+        <v>6998016</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,24 +1098,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,22 +1120,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122823780</v>
+        <v>122824314</v>
       </c>
       <c r="B6" t="n">
-        <v>79844</v>
+        <v>78499</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1187,13 +1172,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528879</v>
+        <v>528828</v>
       </c>
       <c r="R6" t="n">
-        <v>6998066</v>
+        <v>6998005</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,9 +1205,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,22 +1237,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122823943</v>
+        <v>122824138</v>
       </c>
       <c r="B7" t="n">
-        <v>79843</v>
+        <v>78762</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,27 +1265,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1294,10 +1298,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528895</v>
+        <v>528887</v>
       </c>
       <c r="R7" t="n">
-        <v>6998055</v>
+        <v>6998044</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1327,9 +1331,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,22 +1363,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122824729</v>
+        <v>122823943</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>79843</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,34 +1391,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528904</v>
+        <v>528895</v>
       </c>
       <c r="R8" t="n">
-        <v>6998036</v>
+        <v>6998055</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1429,24 +1453,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,19 +1470,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122824138</v>
+        <v>122824729</v>
       </c>
       <c r="B9" t="n">
         <v>78762</v>
@@ -1506,26 +1515,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528887</v>
+        <v>528904</v>
       </c>
       <c r="R9" t="n">
-        <v>6998044</v>
+        <v>6998036</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1813,10 +1813,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122824608</v>
+        <v>122823224</v>
       </c>
       <c r="B12" t="n">
-        <v>56680</v>
+        <v>79747</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,47 +1825,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528928</v>
+        <v>528911</v>
       </c>
       <c r="R12" t="n">
-        <v>6998035</v>
+        <v>6998157</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,9 +1886,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,22 +1918,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122823959</v>
+        <v>122825157</v>
       </c>
       <c r="B13" t="n">
-        <v>79844</v>
+        <v>79843</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1940,21 +1946,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1964,13 +1970,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528918</v>
+        <v>528946</v>
       </c>
       <c r="R13" t="n">
-        <v>6998048</v>
+        <v>6998089</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1997,24 +2003,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,22 +2020,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122823224</v>
+        <v>122823959</v>
       </c>
       <c r="B14" t="n">
-        <v>79747</v>
+        <v>79844</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,25 +2044,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2081,13 +2072,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528911</v>
+        <v>528918</v>
       </c>
       <c r="R14" t="n">
-        <v>6998157</v>
+        <v>6998048</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2116,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2126,12 +2117,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,22 +2137,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122825157</v>
+        <v>122824608</v>
       </c>
       <c r="B15" t="n">
-        <v>79843</v>
+        <v>56680</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,34 +2165,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528946</v>
+        <v>528928</v>
       </c>
       <c r="R15" t="n">
-        <v>6998089</v>
+        <v>6998035</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122825263</v>
+        <v>122824871</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>79747</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2730,46 +2730,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528938</v>
+        <v>528956</v>
       </c>
       <c r="R20" t="n">
-        <v>6998101</v>
+        <v>6998028</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2796,14 +2791,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,22 +2823,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122824871</v>
+        <v>122825263</v>
       </c>
       <c r="B21" t="n">
-        <v>79747</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2842,41 +2847,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528956</v>
+        <v>528938</v>
       </c>
       <c r="R21" t="n">
-        <v>6998028</v>
+        <v>6998101</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2903,24 +2913,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På asp i gammal granskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,12 +2935,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3517,10 +3517,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122824716</v>
+        <v>122824775</v>
       </c>
       <c r="B27" t="n">
-        <v>79843</v>
+        <v>90905</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3529,25 +3529,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3557,13 +3557,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528980</v>
+        <v>528928</v>
       </c>
       <c r="R27" t="n">
-        <v>6998018</v>
+        <v>6998037</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3590,9 +3590,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gammal död stående gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3607,22 +3622,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122824775</v>
+        <v>122824203</v>
       </c>
       <c r="B28" t="n">
-        <v>90905</v>
+        <v>56688</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3635,37 +3650,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528928</v>
+        <v>528874</v>
       </c>
       <c r="R28" t="n">
-        <v>6998037</v>
+        <v>6998038</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3694,7 +3714,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3704,12 +3724,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal död stående gran i gammal barrblandskog</t>
+          <t>Rikligt med spillning under tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3736,10 +3756,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122824203</v>
+        <v>122824716</v>
       </c>
       <c r="B29" t="n">
-        <v>56688</v>
+        <v>79843</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3748,43 +3768,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528874</v>
+        <v>528980</v>
       </c>
       <c r="R29" t="n">
-        <v>6998038</v>
+        <v>6998018</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3814,24 +3829,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med spillning under tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3846,22 +3846,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122824798</v>
+        <v>122823776</v>
       </c>
       <c r="B30" t="n">
-        <v>74863</v>
+        <v>79843</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3874,37 +3874,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528929</v>
+        <v>528879</v>
       </c>
       <c r="R30" t="n">
-        <v>6998043</v>
+        <v>6998065</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3931,24 +3936,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3963,22 +3953,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122823776</v>
+        <v>122824798</v>
       </c>
       <c r="B31" t="n">
-        <v>79843</v>
+        <v>74863</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3991,42 +3981,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528879</v>
+        <v>528929</v>
       </c>
       <c r="R31" t="n">
-        <v>6998065</v>
+        <v>6998043</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4053,9 +4038,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,19 +4070,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122823935</v>
+        <v>122824928</v>
       </c>
       <c r="B32" t="n">
         <v>79843</v>
@@ -4122,13 +4122,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528934</v>
+        <v>528989</v>
       </c>
       <c r="R32" t="n">
-        <v>6998051</v>
+        <v>6998039</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4155,24 +4155,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4187,22 +4172,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122823789</v>
+        <v>122823935</v>
       </c>
       <c r="B33" t="n">
-        <v>79844</v>
+        <v>79843</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4215,21 +4200,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4239,13 +4224,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528910</v>
+        <v>528934</v>
       </c>
       <c r="R33" t="n">
-        <v>6998072</v>
+        <v>6998051</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4274,7 +4259,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4284,12 +4269,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På sälglåga i gammal granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4304,22 +4289,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122824928</v>
+        <v>122823789</v>
       </c>
       <c r="B34" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4332,21 +4317,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4356,10 +4341,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528989</v>
+        <v>528910</v>
       </c>
       <c r="R34" t="n">
-        <v>6998039</v>
+        <v>6998072</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4389,9 +4374,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4406,12 +4406,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122824883</v>
+        <v>122824294</v>
       </c>
       <c r="B36" t="n">
-        <v>79843</v>
+        <v>78762</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4545,46 +4545,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528973</v>
+        <v>528874</v>
       </c>
       <c r="R36" t="n">
         <v>6998038</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4613,7 +4604,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4623,12 +4614,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På död sälg (kort)</t>
+          <t>På gammal tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4643,22 +4634,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122824294</v>
+        <v>122824883</v>
       </c>
       <c r="B37" t="n">
-        <v>78762</v>
+        <v>79843</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4671,37 +4662,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528874</v>
+        <v>528973</v>
       </c>
       <c r="R37" t="n">
         <v>6998038</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal tall</t>
+          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4760,12 +4760,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5697,7 +5697,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122823876</v>
+        <v>122823389</v>
       </c>
       <c r="B46" t="n">
         <v>78762</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5746,13 +5746,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528897</v>
+        <v>528893</v>
       </c>
       <c r="R46" t="n">
-        <v>6998064</v>
+        <v>6998121</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal senvuxen granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5811,12 +5811,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5940,10 +5940,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122823389</v>
+        <v>122824617</v>
       </c>
       <c r="B48" t="n">
-        <v>78762</v>
+        <v>78498</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5956,46 +5956,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528893</v>
+        <v>528897</v>
       </c>
       <c r="R48" t="n">
-        <v>6998121</v>
+        <v>6998014</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6024,7 +6015,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6034,12 +6025,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6054,22 +6045,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122824617</v>
+        <v>122823876</v>
       </c>
       <c r="B49" t="n">
-        <v>78498</v>
+        <v>78762</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6082,24 +6073,33 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
@@ -6109,7 +6109,7 @@
         <v>528897</v>
       </c>
       <c r="R49" t="n">
-        <v>6998014</v>
+        <v>6998064</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
+          <t>På gamla granar i gammal senvuxen granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122823616</v>
+        <v>122823780</v>
       </c>
       <c r="B3" t="n">
-        <v>79803</v>
+        <v>79848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229497</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528903</v>
+        <v>528879</v>
       </c>
       <c r="R3" t="n">
-        <v>6998106</v>
+        <v>6998066</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,24 +874,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,22 +891,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122823780</v>
+        <v>122824883</v>
       </c>
       <c r="B4" t="n">
-        <v>79844</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,37 +919,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528879</v>
+        <v>528973</v>
       </c>
       <c r="R4" t="n">
-        <v>6998066</v>
+        <v>6998038</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,9 +985,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +1017,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122824296</v>
+        <v>122823876</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,27 +1045,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1065,10 +1078,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528849</v>
+        <v>528897</v>
       </c>
       <c r="R5" t="n">
-        <v>6998016</v>
+        <v>6998064</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,14 +1111,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gamla granar i gammal senvuxen granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,22 +1143,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122824314</v>
+        <v>122825192</v>
       </c>
       <c r="B6" t="n">
-        <v>78499</v>
+        <v>79848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1148,21 +1171,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,13 +1195,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528828</v>
+        <v>528946</v>
       </c>
       <c r="R6" t="n">
-        <v>6998005</v>
+        <v>6998089</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,24 +1228,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,22 +1245,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122824138</v>
+        <v>122824798</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,46 +1273,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528887</v>
+        <v>528929</v>
       </c>
       <c r="R7" t="n">
-        <v>6998044</v>
+        <v>6998043</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,7 +1332,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,12 +1342,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,22 +1362,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122823943</v>
+        <v>122824139</v>
       </c>
       <c r="B8" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1409,24 +1408,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528895</v>
+        <v>528870</v>
       </c>
       <c r="R8" t="n">
-        <v>6998055</v>
+        <v>6997994</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1453,9 +1447,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,22 +1474,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122824729</v>
+        <v>122824608</v>
       </c>
       <c r="B9" t="n">
-        <v>78762</v>
+        <v>56680</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,34 +1502,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528904</v>
+        <v>528928</v>
       </c>
       <c r="R9" t="n">
-        <v>6998036</v>
+        <v>6998035</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1555,24 +1568,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,22 +1585,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122824669</v>
+        <v>122823943</v>
       </c>
       <c r="B10" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,16 +1631,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528962</v>
+        <v>528895</v>
       </c>
       <c r="R10" t="n">
-        <v>6998022</v>
+        <v>6998055</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1701,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122824139</v>
+        <v>122824294</v>
       </c>
       <c r="B11" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,21 +1720,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1741,13 +1744,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528870</v>
+        <v>528874</v>
       </c>
       <c r="R11" t="n">
-        <v>6997994</v>
+        <v>6998038</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,7 +1779,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1789,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gammal tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,22 +1809,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122823224</v>
+        <v>122823542</v>
       </c>
       <c r="B12" t="n">
-        <v>79747</v>
+        <v>78503</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,25 +1833,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1853,13 +1861,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528911</v>
+        <v>528881</v>
       </c>
       <c r="R12" t="n">
-        <v>6998157</v>
+        <v>6998117</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1888,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1898,12 +1906,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1930,10 +1938,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122825157</v>
+        <v>122824729</v>
       </c>
       <c r="B13" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,21 +1954,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1970,10 +1978,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528946</v>
+        <v>528904</v>
       </c>
       <c r="R13" t="n">
-        <v>6998089</v>
+        <v>6998036</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2003,9 +2011,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2020,22 +2043,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122823959</v>
+        <v>122824203</v>
       </c>
       <c r="B14" t="n">
-        <v>79844</v>
+        <v>56688</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,41 +2067,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528918</v>
+        <v>528874</v>
       </c>
       <c r="R14" t="n">
-        <v>6998048</v>
+        <v>6998038</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2107,7 +2135,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,12 +2145,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Rikligt med spillning under tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2137,22 +2165,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122824608</v>
+        <v>122824296</v>
       </c>
       <c r="B15" t="n">
-        <v>56680</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2165,16 +2193,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2182,14 +2210,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2198,10 +2222,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528928</v>
+        <v>528849</v>
       </c>
       <c r="R15" t="n">
-        <v>6998035</v>
+        <v>6998016</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2234,6 +2258,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,10 +2289,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122823534</v>
+        <v>122824775</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>90909</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,46 +2301,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528883</v>
+        <v>528928</v>
       </c>
       <c r="R16" t="n">
-        <v>6998125</v>
+        <v>6998037</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2338,14 +2362,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal död stående gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,22 +2394,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122824159</v>
+        <v>122824689</v>
       </c>
       <c r="B17" t="n">
-        <v>77699</v>
+        <v>78411</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,21 +2422,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2412,10 +2446,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528887</v>
+        <v>528901</v>
       </c>
       <c r="R17" t="n">
-        <v>6998044</v>
+        <v>6998033</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2447,7 +2481,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2457,12 +2491,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2489,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122823666</v>
+        <v>122824645</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,39 +2539,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528890</v>
+        <v>528897</v>
       </c>
       <c r="R18" t="n">
-        <v>6998089</v>
+        <v>6998014</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2567,14 +2596,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2589,22 +2628,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122824915</v>
+        <v>122823640</v>
       </c>
       <c r="B19" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2641,10 +2680,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528964</v>
+        <v>528890</v>
       </c>
       <c r="R19" t="n">
-        <v>6998032</v>
+        <v>6998093</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2674,24 +2713,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,22 +2730,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122824871</v>
+        <v>122824928</v>
       </c>
       <c r="B20" t="n">
-        <v>79747</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2730,25 +2754,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2758,13 +2782,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528956</v>
+        <v>528989</v>
       </c>
       <c r="R20" t="n">
-        <v>6998028</v>
+        <v>6998039</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2791,24 +2815,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2823,19 +2832,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122825263</v>
+        <v>122823534</v>
       </c>
       <c r="B21" t="n">
         <v>57478</v>
@@ -2880,10 +2889,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528938</v>
+        <v>528883</v>
       </c>
       <c r="R21" t="n">
-        <v>6998101</v>
+        <v>6998125</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2920,7 +2929,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2947,10 +2956,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122824689</v>
+        <v>122824419</v>
       </c>
       <c r="B22" t="n">
-        <v>78407</v>
+        <v>79384</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2963,21 +2972,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2987,10 +2996,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528901</v>
+        <v>528853</v>
       </c>
       <c r="R22" t="n">
-        <v>6998033</v>
+        <v>6998012</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3022,7 +3031,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3032,12 +3041,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3064,10 +3073,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122823640</v>
+        <v>122823616</v>
       </c>
       <c r="B23" t="n">
-        <v>79843</v>
+        <v>79807</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3076,25 +3085,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3104,10 +3113,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528890</v>
+        <v>528903</v>
       </c>
       <c r="R23" t="n">
-        <v>6998093</v>
+        <v>6998106</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3137,9 +3146,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3154,22 +3178,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122824517</v>
+        <v>122824314</v>
       </c>
       <c r="B24" t="n">
-        <v>78499</v>
+        <v>78503</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3206,13 +3230,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528878</v>
+        <v>528828</v>
       </c>
       <c r="R24" t="n">
-        <v>6997997</v>
+        <v>6998005</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3241,7 +3265,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3251,12 +3275,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
+          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3271,22 +3295,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122824645</v>
+        <v>122823224</v>
       </c>
       <c r="B25" t="n">
-        <v>78499</v>
+        <v>79751</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3295,25 +3319,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3323,10 +3347,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528897</v>
+        <v>528911</v>
       </c>
       <c r="R25" t="n">
-        <v>6998014</v>
+        <v>6998157</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3358,7 +3382,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3368,12 +3392,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3400,10 +3424,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122825055</v>
+        <v>122823308</v>
       </c>
       <c r="B26" t="n">
-        <v>79843</v>
+        <v>78502</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3416,21 +3440,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3440,13 +3464,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529003</v>
+        <v>528904</v>
       </c>
       <c r="R26" t="n">
-        <v>6998021</v>
+        <v>6998141</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3475,7 +3499,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3485,12 +3509,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3505,7 +3529,7 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -3517,10 +3541,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122824775</v>
+        <v>122824871</v>
       </c>
       <c r="B27" t="n">
-        <v>90905</v>
+        <v>79751</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3533,21 +3557,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3557,13 +3581,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528928</v>
+        <v>528956</v>
       </c>
       <c r="R27" t="n">
-        <v>6998037</v>
+        <v>6998028</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3592,7 +3616,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3602,12 +3626,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal död stående gran i gammal barrblandskog</t>
+          <t>På asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3634,10 +3658,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122824203</v>
+        <v>122823935</v>
       </c>
       <c r="B28" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3646,46 +3670,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528874</v>
+        <v>528934</v>
       </c>
       <c r="R28" t="n">
-        <v>6998038</v>
+        <v>6998051</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3714,7 +3733,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3724,12 +3743,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt med spillning under tall</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3744,22 +3763,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122824716</v>
+        <v>122823666</v>
       </c>
       <c r="B29" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3772,34 +3791,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528980</v>
+        <v>528890</v>
       </c>
       <c r="R29" t="n">
-        <v>6998018</v>
+        <v>6998089</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3832,6 +3856,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3858,10 +3887,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122823776</v>
+        <v>122824915</v>
       </c>
       <c r="B30" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3892,21 +3921,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528879</v>
+        <v>528964</v>
       </c>
       <c r="R30" t="n">
-        <v>6998065</v>
+        <v>6998032</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3936,9 +3960,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3953,22 +3992,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122824798</v>
+        <v>122824996</v>
       </c>
       <c r="B31" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3981,21 +4020,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4005,10 +4044,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528929</v>
+        <v>528952</v>
       </c>
       <c r="R31" t="n">
-        <v>6998043</v>
+        <v>6998039</v>
       </c>
       <c r="S31" t="n">
         <v>6</v>
@@ -4040,7 +4079,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4050,12 +4089,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande glasbjörk med savflöde</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4070,22 +4109,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122824928</v>
+        <v>122823789</v>
       </c>
       <c r="B32" t="n">
-        <v>79843</v>
+        <v>79848</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4098,21 +4137,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4122,10 +4161,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528989</v>
+        <v>528910</v>
       </c>
       <c r="R32" t="n">
-        <v>6998039</v>
+        <v>6998072</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4155,9 +4194,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4172,22 +4226,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122823935</v>
+        <v>122824940</v>
       </c>
       <c r="B33" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4217,20 +4271,29 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528934</v>
+        <v>528993</v>
       </c>
       <c r="R33" t="n">
-        <v>6998051</v>
+        <v>6998013</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4259,7 +4322,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4269,12 +4332,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4301,10 +4359,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122823789</v>
+        <v>122823653</v>
       </c>
       <c r="B34" t="n">
-        <v>79844</v>
+        <v>74863</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4317,21 +4375,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4341,10 +4399,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528910</v>
+        <v>528898</v>
       </c>
       <c r="R34" t="n">
-        <v>6998072</v>
+        <v>6998091</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4376,7 +4434,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4386,12 +4444,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På sälglåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4418,10 +4476,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122824504</v>
+        <v>122825059</v>
       </c>
       <c r="B35" t="n">
-        <v>57631</v>
+        <v>77699</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4434,43 +4492,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528884</v>
+        <v>528960</v>
       </c>
       <c r="R35" t="n">
-        <v>6997998</v>
+        <v>6998066</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4500,9 +4549,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4517,22 +4581,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122824294</v>
+        <v>122823959</v>
       </c>
       <c r="B36" t="n">
-        <v>78762</v>
+        <v>79848</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4545,21 +4609,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4569,13 +4633,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528874</v>
+        <v>528918</v>
       </c>
       <c r="R36" t="n">
-        <v>6998038</v>
+        <v>6998048</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4604,7 +4668,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4614,12 +4678,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal tall</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4634,22 +4698,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122824883</v>
+        <v>122824716</v>
       </c>
       <c r="B37" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4679,29 +4743,20 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528973</v>
+        <v>528980</v>
       </c>
       <c r="R37" t="n">
-        <v>6998038</v>
+        <v>6998018</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4728,24 +4783,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4760,22 +4800,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122823653</v>
+        <v>122824669</v>
       </c>
       <c r="B38" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4788,21 +4828,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4812,10 +4852,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528898</v>
+        <v>528962</v>
       </c>
       <c r="R38" t="n">
-        <v>6998091</v>
+        <v>6998022</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4845,24 +4885,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4877,22 +4902,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122825093</v>
+        <v>122823776</v>
       </c>
       <c r="B39" t="n">
-        <v>91507</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4901,38 +4926,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528967</v>
+        <v>528879</v>
       </c>
       <c r="R39" t="n">
-        <v>6998079</v>
+        <v>6998065</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4962,24 +4992,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4994,22 +5009,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122824419</v>
+        <v>122824517</v>
       </c>
       <c r="B40" t="n">
-        <v>79380</v>
+        <v>78503</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5022,21 +5037,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5046,13 +5061,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528853</v>
+        <v>528878</v>
       </c>
       <c r="R40" t="n">
-        <v>6998012</v>
+        <v>6997997</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5081,7 +5096,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5091,12 +5106,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På ved på gammal tallhögstubbe</t>
+          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5123,10 +5138,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122824114</v>
+        <v>122825055</v>
       </c>
       <c r="B41" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5139,21 +5154,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5163,13 +5178,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528886</v>
+        <v>529003</v>
       </c>
       <c r="R41" t="n">
-        <v>6998049</v>
+        <v>6998021</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5198,7 +5213,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5208,12 +5223,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5228,22 +5243,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122823308</v>
+        <v>122825157</v>
       </c>
       <c r="B42" t="n">
-        <v>78498</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5256,21 +5271,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5280,13 +5295,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528904</v>
+        <v>528946</v>
       </c>
       <c r="R42" t="n">
-        <v>6998141</v>
+        <v>6998089</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5313,24 +5328,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5345,22 +5345,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122823605</v>
+        <v>122823389</v>
       </c>
       <c r="B43" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5373,37 +5373,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528887</v>
+        <v>528893</v>
       </c>
       <c r="R43" t="n">
-        <v>6998073</v>
+        <v>6998121</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5432,7 +5441,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5442,12 +5451,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5474,10 +5483,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122825192</v>
+        <v>122825263</v>
       </c>
       <c r="B44" t="n">
-        <v>79844</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5490,34 +5499,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528946</v>
+        <v>528938</v>
       </c>
       <c r="R44" t="n">
-        <v>6998089</v>
+        <v>6998101</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5550,6 +5564,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5576,10 +5595,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122824940</v>
+        <v>122824504</v>
       </c>
       <c r="B45" t="n">
-        <v>79843</v>
+        <v>57631</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5592,31 +5611,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5625,13 +5644,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528993</v>
+        <v>528884</v>
       </c>
       <c r="R45" t="n">
-        <v>6998013</v>
+        <v>6997998</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5658,19 +5677,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5685,22 +5694,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122823389</v>
+        <v>122824138</v>
       </c>
       <c r="B46" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5732,7 +5741,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5746,13 +5755,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528893</v>
+        <v>528887</v>
       </c>
       <c r="R46" t="n">
-        <v>6998121</v>
+        <v>6998044</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5781,7 +5790,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5791,12 +5800,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5811,22 +5820,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122824996</v>
+        <v>122824617</v>
       </c>
       <c r="B47" t="n">
-        <v>79843</v>
+        <v>78502</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5839,21 +5848,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5863,13 +5872,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528952</v>
+        <v>528897</v>
       </c>
       <c r="R47" t="n">
-        <v>6998039</v>
+        <v>6998014</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5898,7 +5907,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5908,12 +5917,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På bark på stam av levande glasbjörk med savflöde</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5940,10 +5949,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122824617</v>
+        <v>122823605</v>
       </c>
       <c r="B48" t="n">
-        <v>78498</v>
+        <v>79847</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5956,21 +5965,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5980,10 +5989,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528897</v>
+        <v>528887</v>
       </c>
       <c r="R48" t="n">
-        <v>6998014</v>
+        <v>6998073</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6015,7 +6024,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6025,12 +6034,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6045,22 +6054,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122823876</v>
+        <v>122824114</v>
       </c>
       <c r="B49" t="n">
-        <v>78762</v>
+        <v>74863</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6073,43 +6082,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528897</v>
+        <v>528886</v>
       </c>
       <c r="R49" t="n">
-        <v>6998064</v>
+        <v>6998049</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal senvuxen granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6183,10 +6183,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122823542</v>
+        <v>122825093</v>
       </c>
       <c r="B50" t="n">
-        <v>78499</v>
+        <v>91511</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6195,25 +6195,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>760</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6223,13 +6223,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528881</v>
+        <v>528967</v>
       </c>
       <c r="R50" t="n">
-        <v>6998117</v>
+        <v>6998079</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6300,7 +6300,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122825059</v>
+        <v>122824159</v>
       </c>
       <c r="B51" t="n">
         <v>77699</v>
@@ -6340,10 +6340,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528960</v>
+        <v>528887</v>
       </c>
       <c r="R51" t="n">
-        <v>6998066</v>
+        <v>6998044</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122823780</v>
+        <v>122824883</v>
       </c>
       <c r="B3" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,37 +817,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528879</v>
+        <v>528973</v>
       </c>
       <c r="R3" t="n">
-        <v>6998066</v>
+        <v>6998038</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,9 +883,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,22 +915,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122824883</v>
+        <v>122823876</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,26 +943,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -952,13 +976,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528973</v>
+        <v>528897</v>
       </c>
       <c r="R4" t="n">
-        <v>6998038</v>
+        <v>6998064</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +1011,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,12 +1021,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På död sälg (kort)</t>
+          <t>På gamla granar i gammal senvuxen granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,22 +1041,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122823876</v>
+        <v>122823780</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,43 +1069,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528897</v>
+        <v>528879</v>
       </c>
       <c r="R5" t="n">
-        <v>6998064</v>
+        <v>6998066</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,24 +1126,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal senvuxen granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,12 +1143,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122823943</v>
+        <v>122824294</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,39 +1613,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528895</v>
+        <v>528874</v>
       </c>
       <c r="R10" t="n">
-        <v>6998055</v>
+        <v>6998038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,9 +1670,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gammal tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,22 +1702,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122824294</v>
+        <v>122823943</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,34 +1730,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528874</v>
+        <v>528895</v>
       </c>
       <c r="R11" t="n">
-        <v>6998038</v>
+        <v>6998055</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1777,24 +1792,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gammal tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,12 +1809,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2956,10 +2956,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122824419</v>
+        <v>122823616</v>
       </c>
       <c r="B22" t="n">
-        <v>79384</v>
+        <v>79807</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2968,25 +2968,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2996,10 +2996,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528853</v>
+        <v>528903</v>
       </c>
       <c r="R22" t="n">
-        <v>6998012</v>
+        <v>6998106</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På ved på gammal tallhögstubbe</t>
+          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3073,10 +3073,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122823616</v>
+        <v>122824419</v>
       </c>
       <c r="B23" t="n">
-        <v>79807</v>
+        <v>79384</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3085,25 +3085,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528903</v>
+        <v>528853</v>
       </c>
       <c r="R23" t="n">
-        <v>6998106</v>
+        <v>6998012</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
+          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3190,10 +3190,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122824314</v>
+        <v>122823224</v>
       </c>
       <c r="B24" t="n">
-        <v>78503</v>
+        <v>79751</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3202,25 +3202,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3230,13 +3230,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528828</v>
+        <v>528911</v>
       </c>
       <c r="R24" t="n">
-        <v>6998005</v>
+        <v>6998157</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3295,19 +3295,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122823224</v>
+        <v>122824871</v>
       </c>
       <c r="B25" t="n">
         <v>79751</v>
@@ -3347,13 +3347,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528911</v>
+        <v>528956</v>
       </c>
       <c r="R25" t="n">
-        <v>6998157</v>
+        <v>6998028</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3424,10 +3424,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122823308</v>
+        <v>122823666</v>
       </c>
       <c r="B26" t="n">
-        <v>78502</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3440,37 +3440,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528904</v>
+        <v>528890</v>
       </c>
       <c r="R26" t="n">
-        <v>6998141</v>
+        <v>6998089</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3497,24 +3502,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3529,22 +3524,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122824871</v>
+        <v>122824314</v>
       </c>
       <c r="B27" t="n">
-        <v>79751</v>
+        <v>78503</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3553,25 +3548,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3581,10 +3576,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528956</v>
+        <v>528828</v>
       </c>
       <c r="R27" t="n">
-        <v>6998028</v>
+        <v>6998005</v>
       </c>
       <c r="S27" t="n">
         <v>9</v>
@@ -3616,7 +3611,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3626,12 +3621,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På asp i gammal granskog</t>
+          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3646,22 +3641,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122823935</v>
+        <v>122823308</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3674,21 +3669,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3698,13 +3693,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528934</v>
+        <v>528904</v>
       </c>
       <c r="R28" t="n">
-        <v>6998051</v>
+        <v>6998141</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3733,7 +3728,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3743,12 +3738,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3763,7 +3758,7 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -3775,10 +3770,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122823666</v>
+        <v>122823935</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3791,42 +3786,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528890</v>
+        <v>528934</v>
       </c>
       <c r="R29" t="n">
-        <v>6998089</v>
+        <v>6998051</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3853,14 +3843,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3875,12 +3875,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -5021,10 +5021,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122824517</v>
+        <v>122825055</v>
       </c>
       <c r="B40" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5037,21 +5037,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5061,13 +5061,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528878</v>
+        <v>529003</v>
       </c>
       <c r="R40" t="n">
-        <v>6997997</v>
+        <v>6998021</v>
       </c>
       <c r="S40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5126,22 +5126,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122825055</v>
+        <v>122824517</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5154,21 +5154,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5178,13 +5178,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>529003</v>
+        <v>528878</v>
       </c>
       <c r="R41" t="n">
-        <v>6998021</v>
+        <v>6997997</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5243,12 +5243,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122824883</v>
+        <v>122823876</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,26 +817,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528973</v>
+        <v>528897</v>
       </c>
       <c r="R3" t="n">
-        <v>6998038</v>
+        <v>6998064</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På död sälg (kort)</t>
+          <t>På gamla granar i gammal senvuxen granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,22 +915,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122823876</v>
+        <v>122824114</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,43 +943,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528897</v>
+        <v>528886</v>
       </c>
       <c r="R4" t="n">
-        <v>6998064</v>
+        <v>6998049</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1021,12 +1012,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal senvuxen granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122823780</v>
+        <v>122824419</v>
       </c>
       <c r="B5" t="n">
-        <v>79848</v>
+        <v>79384</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,21 +1060,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1093,10 +1084,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528879</v>
+        <v>528853</v>
       </c>
       <c r="R5" t="n">
-        <v>6998066</v>
+        <v>6998012</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,9 +1117,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,22 +1149,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122825192</v>
+        <v>122824517</v>
       </c>
       <c r="B6" t="n">
-        <v>79848</v>
+        <v>78503</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,21 +1177,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1195,13 +1201,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528946</v>
+        <v>528878</v>
       </c>
       <c r="R6" t="n">
-        <v>6998089</v>
+        <v>6997997</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,9 +1234,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,22 +1266,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122824798</v>
+        <v>122824940</v>
       </c>
       <c r="B7" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,37 +1294,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528929</v>
+        <v>528993</v>
       </c>
       <c r="R7" t="n">
-        <v>6998043</v>
+        <v>6998013</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,7 +1362,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1342,12 +1372,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122824139</v>
+        <v>122825192</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,21 +1415,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1414,13 +1439,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528870</v>
+        <v>528946</v>
       </c>
       <c r="R8" t="n">
-        <v>6997994</v>
+        <v>6998089</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,19 +1472,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,22 +1489,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122824608</v>
+        <v>122824294</v>
       </c>
       <c r="B9" t="n">
-        <v>56680</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1502,43 +1517,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528928</v>
+        <v>528874</v>
       </c>
       <c r="R9" t="n">
-        <v>6998035</v>
+        <v>6998038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,9 +1574,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gammal tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,22 +1606,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122824294</v>
+        <v>122824645</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1613,21 +1634,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1637,10 +1658,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528874</v>
+        <v>528897</v>
       </c>
       <c r="R10" t="n">
-        <v>6998038</v>
+        <v>6998014</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,7 +1693,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,12 +1703,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal tall</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,10 +1735,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122823943</v>
+        <v>122824296</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1730,27 +1751,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1759,10 +1780,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528895</v>
+        <v>528849</v>
       </c>
       <c r="R11" t="n">
-        <v>6998055</v>
+        <v>6998016</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1795,6 +1816,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,10 +1847,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122823542</v>
+        <v>122824203</v>
       </c>
       <c r="B12" t="n">
-        <v>78503</v>
+        <v>56688</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,41 +1859,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528881</v>
+        <v>528874</v>
       </c>
       <c r="R12" t="n">
-        <v>6998117</v>
+        <v>6998038</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1896,7 +1927,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,12 +1937,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>Rikligt med spillning under tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,10 +1969,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122824729</v>
+        <v>122823308</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1954,21 +1985,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1981,10 +2012,10 @@
         <v>528904</v>
       </c>
       <c r="R13" t="n">
-        <v>6998036</v>
+        <v>6998141</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2013,7 +2044,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,12 +2054,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2055,10 +2086,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122824203</v>
+        <v>122824871</v>
       </c>
       <c r="B14" t="n">
-        <v>56688</v>
+        <v>79751</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,42 +2102,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528874</v>
+        <v>528956</v>
       </c>
       <c r="R14" t="n">
-        <v>6998038</v>
+        <v>6998028</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2135,7 +2161,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2145,12 +2171,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt med spillning under tall</t>
+          <t>På asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2177,10 +2203,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122824296</v>
+        <v>122824138</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2193,27 +2219,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2222,10 +2252,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528849</v>
+        <v>528887</v>
       </c>
       <c r="R15" t="n">
-        <v>6998016</v>
+        <v>6998044</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,14 +2285,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,22 +2317,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122824775</v>
+        <v>122823605</v>
       </c>
       <c r="B16" t="n">
-        <v>90909</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,25 +2341,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2329,13 +2369,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528928</v>
+        <v>528887</v>
       </c>
       <c r="R16" t="n">
-        <v>6998037</v>
+        <v>6998073</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2364,7 +2404,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2374,12 +2414,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal död stående gran i gammal barrblandskog</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,22 +2434,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122824689</v>
+        <v>122823776</v>
       </c>
       <c r="B17" t="n">
-        <v>78411</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,34 +2462,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528901</v>
+        <v>528879</v>
       </c>
       <c r="R17" t="n">
-        <v>6998033</v>
+        <v>6998065</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,24 +2524,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,22 +2541,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122824645</v>
+        <v>122823640</v>
       </c>
       <c r="B18" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2539,21 +2569,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2563,10 +2593,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528897</v>
+        <v>528890</v>
       </c>
       <c r="R18" t="n">
-        <v>6998014</v>
+        <v>6998093</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2596,24 +2626,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,22 +2643,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122823640</v>
+        <v>122825093</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>91511</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2652,25 +2667,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2680,10 +2695,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528890</v>
+        <v>528967</v>
       </c>
       <c r="R19" t="n">
-        <v>6998093</v>
+        <v>6998079</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2713,9 +2728,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,22 +2760,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122824928</v>
+        <v>122823780</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2758,21 +2788,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2782,10 +2812,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528989</v>
+        <v>528879</v>
       </c>
       <c r="R20" t="n">
-        <v>6998039</v>
+        <v>6998066</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2844,10 +2874,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122823534</v>
+        <v>122824314</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2860,42 +2890,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528883</v>
+        <v>528828</v>
       </c>
       <c r="R21" t="n">
-        <v>6998125</v>
+        <v>6998005</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2922,14 +2947,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2944,22 +2979,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122823616</v>
+        <v>122825157</v>
       </c>
       <c r="B22" t="n">
-        <v>79807</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2968,25 +3003,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2996,10 +3031,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528903</v>
+        <v>528946</v>
       </c>
       <c r="R22" t="n">
-        <v>6998106</v>
+        <v>6998089</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3029,24 +3064,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,22 +3081,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122824419</v>
+        <v>122824159</v>
       </c>
       <c r="B23" t="n">
-        <v>79384</v>
+        <v>77699</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3089,21 +3109,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3113,10 +3133,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528853</v>
+        <v>528887</v>
       </c>
       <c r="R23" t="n">
-        <v>6998012</v>
+        <v>6998044</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3148,7 +3168,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3158,12 +3178,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På ved på gammal tallhögstubbe</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3190,10 +3210,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122823224</v>
+        <v>122823935</v>
       </c>
       <c r="B24" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3202,25 +3222,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3230,13 +3250,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528911</v>
+        <v>528934</v>
       </c>
       <c r="R24" t="n">
-        <v>6998157</v>
+        <v>6998051</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3265,7 +3285,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3275,12 +3295,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3295,22 +3315,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122824871</v>
+        <v>122824798</v>
       </c>
       <c r="B25" t="n">
-        <v>79751</v>
+        <v>74863</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3319,25 +3339,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3347,13 +3367,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528956</v>
+        <v>528929</v>
       </c>
       <c r="R25" t="n">
-        <v>6998028</v>
+        <v>6998043</v>
       </c>
       <c r="S25" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3382,7 +3402,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3392,12 +3412,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På asp i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3412,22 +3432,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122823666</v>
+        <v>122824689</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>78411</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3440,39 +3460,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528890</v>
+        <v>528901</v>
       </c>
       <c r="R26" t="n">
-        <v>6998089</v>
+        <v>6998033</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3502,14 +3517,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3524,22 +3549,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122824314</v>
+        <v>122824716</v>
       </c>
       <c r="B27" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3552,21 +3577,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3576,13 +3601,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528828</v>
+        <v>528980</v>
       </c>
       <c r="R27" t="n">
-        <v>6998005</v>
+        <v>6998018</v>
       </c>
       <c r="S27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3609,24 +3634,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3641,22 +3651,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122823308</v>
+        <v>122824775</v>
       </c>
       <c r="B28" t="n">
-        <v>78502</v>
+        <v>90909</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3665,25 +3675,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3693,13 +3703,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528904</v>
+        <v>528928</v>
       </c>
       <c r="R28" t="n">
-        <v>6998141</v>
+        <v>6998037</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3728,7 +3738,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3738,12 +3748,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>På gammal död stående gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3763,14 +3773,14 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122823935</v>
+        <v>122823943</v>
       </c>
       <c r="B29" t="n">
         <v>79847</v>
@@ -3804,19 +3814,24 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528934</v>
+        <v>528895</v>
       </c>
       <c r="R29" t="n">
-        <v>6998051</v>
+        <v>6998055</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3843,24 +3858,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3875,22 +3875,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122824915</v>
+        <v>122824608</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3903,34 +3903,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528964</v>
+        <v>528928</v>
       </c>
       <c r="R30" t="n">
-        <v>6998032</v>
+        <v>6998035</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3960,24 +3969,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3992,22 +3986,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122824996</v>
+        <v>122825059</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4020,21 +4014,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4044,13 +4038,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528952</v>
+        <v>528960</v>
       </c>
       <c r="R31" t="n">
-        <v>6998039</v>
+        <v>6998066</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4094,7 +4088,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark på stam av levande glasbjörk med savflöde</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4121,10 +4115,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122823789</v>
+        <v>122823653</v>
       </c>
       <c r="B32" t="n">
-        <v>79848</v>
+        <v>74863</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4137,21 +4131,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4161,10 +4155,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528910</v>
+        <v>528898</v>
       </c>
       <c r="R32" t="n">
-        <v>6998072</v>
+        <v>6998091</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4196,7 +4190,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4206,12 +4200,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På sälglåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4238,10 +4232,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122824940</v>
+        <v>122823789</v>
       </c>
       <c r="B33" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4254,46 +4248,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528993</v>
+        <v>528910</v>
       </c>
       <c r="R33" t="n">
-        <v>6998013</v>
+        <v>6998072</v>
       </c>
       <c r="S33" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4322,7 +4307,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4332,7 +4317,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4347,22 +4337,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122823653</v>
+        <v>122823534</v>
       </c>
       <c r="B34" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4375,34 +4365,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528898</v>
+        <v>528883</v>
       </c>
       <c r="R34" t="n">
-        <v>6998091</v>
+        <v>6998125</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4432,24 +4427,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4464,22 +4449,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122825059</v>
+        <v>122825055</v>
       </c>
       <c r="B35" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4492,21 +4477,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4516,13 +4501,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528960</v>
+        <v>529003</v>
       </c>
       <c r="R35" t="n">
-        <v>6998066</v>
+        <v>6998021</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4551,7 +4536,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4561,12 +4546,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4581,22 +4566,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122823959</v>
+        <v>122823224</v>
       </c>
       <c r="B36" t="n">
-        <v>79848</v>
+        <v>79751</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4605,25 +4590,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4633,13 +4618,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528918</v>
+        <v>528911</v>
       </c>
       <c r="R36" t="n">
-        <v>6998048</v>
+        <v>6998157</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4668,7 +4653,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4678,12 +4663,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4698,22 +4683,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122824716</v>
+        <v>122823616</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4722,25 +4707,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4750,10 +4735,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528980</v>
+        <v>528903</v>
       </c>
       <c r="R37" t="n">
-        <v>6998018</v>
+        <v>6998106</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4783,9 +4768,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4800,22 +4800,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122824669</v>
+        <v>122823542</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4828,21 +4828,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4852,13 +4852,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528962</v>
+        <v>528881</v>
       </c>
       <c r="R38" t="n">
-        <v>6998022</v>
+        <v>6998117</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4885,9 +4885,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4902,22 +4917,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122823776</v>
+        <v>122824617</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4930,39 +4945,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528879</v>
+        <v>528897</v>
       </c>
       <c r="R39" t="n">
-        <v>6998065</v>
+        <v>6998014</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4992,9 +5002,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5009,19 +5034,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122825055</v>
+        <v>122824996</v>
       </c>
       <c r="B40" t="n">
         <v>79847</v>
@@ -5061,13 +5086,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>529003</v>
+        <v>528952</v>
       </c>
       <c r="R40" t="n">
-        <v>6998021</v>
+        <v>6998039</v>
       </c>
       <c r="S40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5096,7 +5121,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5106,12 +5131,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På bark på stam av levande glasbjörk med savflöde</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5126,22 +5151,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122824517</v>
+        <v>122824669</v>
       </c>
       <c r="B41" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5154,21 +5179,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5178,13 +5203,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528878</v>
+        <v>528962</v>
       </c>
       <c r="R41" t="n">
-        <v>6997997</v>
+        <v>6998022</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5211,24 +5236,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5243,19 +5253,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122825157</v>
+        <v>122824139</v>
       </c>
       <c r="B42" t="n">
         <v>79847</v>
@@ -5295,13 +5305,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528946</v>
+        <v>528870</v>
       </c>
       <c r="R42" t="n">
-        <v>6998089</v>
+        <v>6997994</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5328,9 +5338,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5345,19 +5365,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122823389</v>
+        <v>122824729</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -5390,29 +5410,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528893</v>
+        <v>528904</v>
       </c>
       <c r="R43" t="n">
-        <v>6998121</v>
+        <v>6998036</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5441,7 +5452,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5451,12 +5462,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5471,19 +5482,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122825263</v>
+        <v>122823666</v>
       </c>
       <c r="B44" t="n">
         <v>57478</v>
@@ -5528,10 +5539,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528938</v>
+        <v>528890</v>
       </c>
       <c r="R44" t="n">
-        <v>6998101</v>
+        <v>6998089</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5568,7 +5579,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5595,10 +5606,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122824504</v>
+        <v>122824883</v>
       </c>
       <c r="B45" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5611,31 +5622,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5644,13 +5655,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528884</v>
+        <v>528973</v>
       </c>
       <c r="R45" t="n">
-        <v>6997998</v>
+        <v>6998038</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5677,9 +5688,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5694,22 +5720,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122824138</v>
+        <v>122824915</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5722,43 +5748,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528887</v>
+        <v>528964</v>
       </c>
       <c r="R46" t="n">
-        <v>6998044</v>
+        <v>6998032</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5790,7 +5807,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5800,12 +5817,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5832,10 +5849,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122824617</v>
+        <v>122825263</v>
       </c>
       <c r="B47" t="n">
-        <v>78502</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5848,34 +5865,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528897</v>
+        <v>528938</v>
       </c>
       <c r="R47" t="n">
-        <v>6998014</v>
+        <v>6998101</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5905,24 +5927,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5937,22 +5949,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122823605</v>
+        <v>122823389</v>
       </c>
       <c r="B48" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5965,37 +5977,46 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528887</v>
+        <v>528893</v>
       </c>
       <c r="R48" t="n">
-        <v>6998073</v>
+        <v>6998121</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6024,7 +6045,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6034,12 +6055,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6066,10 +6087,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122824114</v>
+        <v>122824928</v>
       </c>
       <c r="B49" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6082,21 +6103,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6106,10 +6127,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528886</v>
+        <v>528989</v>
       </c>
       <c r="R49" t="n">
-        <v>6998049</v>
+        <v>6998039</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6139,24 +6160,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6171,22 +6177,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122825093</v>
+        <v>122823959</v>
       </c>
       <c r="B50" t="n">
-        <v>91511</v>
+        <v>79848</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6195,25 +6201,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6223,13 +6229,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528967</v>
+        <v>528918</v>
       </c>
       <c r="R50" t="n">
-        <v>6998079</v>
+        <v>6998048</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6258,7 +6264,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6268,7 +6274,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6288,22 +6294,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122824159</v>
+        <v>122824504</v>
       </c>
       <c r="B51" t="n">
-        <v>77699</v>
+        <v>57631</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6316,34 +6322,43 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528887</v>
+        <v>528884</v>
       </c>
       <c r="R51" t="n">
-        <v>6998044</v>
+        <v>6997998</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6373,24 +6388,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6405,12 +6405,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122823876</v>
+        <v>122825157</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,43 +817,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528897</v>
+        <v>528946</v>
       </c>
       <c r="R3" t="n">
-        <v>6998064</v>
+        <v>6998089</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,24 +874,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal senvuxen granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,22 +891,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122824114</v>
+        <v>122823943</v>
       </c>
       <c r="B4" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,34 +919,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528886</v>
+        <v>528895</v>
       </c>
       <c r="R4" t="n">
-        <v>6998049</v>
+        <v>6998055</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,24 +981,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,22 +998,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122824419</v>
+        <v>122824996</v>
       </c>
       <c r="B5" t="n">
-        <v>79384</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,21 +1026,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1084,13 +1050,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528853</v>
+        <v>528952</v>
       </c>
       <c r="R5" t="n">
-        <v>6998012</v>
+        <v>6998039</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,7 +1085,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1129,12 +1095,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På ved på gammal tallhögstubbe</t>
+          <t>På bark på stam av levande glasbjörk med savflöde</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,7 +1127,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122824517</v>
+        <v>122823542</v>
       </c>
       <c r="B6" t="n">
         <v>78503</v>
@@ -1201,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528878</v>
+        <v>528881</v>
       </c>
       <c r="R6" t="n">
-        <v>6997997</v>
+        <v>6998117</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,12 +1212,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122824940</v>
+        <v>122823789</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,46 +1260,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528993</v>
+        <v>528910</v>
       </c>
       <c r="R7" t="n">
-        <v>6998013</v>
+        <v>6998072</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1362,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1372,7 +1329,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1387,22 +1349,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122825192</v>
+        <v>122824689</v>
       </c>
       <c r="B8" t="n">
-        <v>79848</v>
+        <v>78411</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,21 +1377,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1439,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528946</v>
+        <v>528901</v>
       </c>
       <c r="R8" t="n">
-        <v>6998089</v>
+        <v>6998033</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1472,9 +1434,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,22 +1466,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122824294</v>
+        <v>122824915</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,21 +1494,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1541,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528874</v>
+        <v>528964</v>
       </c>
       <c r="R9" t="n">
-        <v>6998038</v>
+        <v>6998032</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1586,12 +1563,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gammal tall</t>
+          <t>På asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122824645</v>
+        <v>122824729</v>
       </c>
       <c r="B10" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,21 +1611,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1658,10 +1635,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528897</v>
+        <v>528904</v>
       </c>
       <c r="R10" t="n">
-        <v>6998014</v>
+        <v>6998036</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,7 +1670,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1703,12 +1680,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,10 +1712,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122824296</v>
+        <v>122823653</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1751,39 +1728,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528849</v>
+        <v>528898</v>
       </c>
       <c r="R11" t="n">
-        <v>6998016</v>
+        <v>6998091</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1813,14 +1785,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,22 +1817,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122824203</v>
+        <v>122824775</v>
       </c>
       <c r="B12" t="n">
-        <v>56688</v>
+        <v>90909</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,42 +1845,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528874</v>
+        <v>528928</v>
       </c>
       <c r="R12" t="n">
-        <v>6998038</v>
+        <v>6998037</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1927,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1937,12 +1914,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt med spillning under tall</t>
+          <t>På gammal död stående gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1969,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122823308</v>
+        <v>122825093</v>
       </c>
       <c r="B13" t="n">
-        <v>78502</v>
+        <v>91511</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,25 +1958,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>760</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2009,13 +1986,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528904</v>
+        <v>528967</v>
       </c>
       <c r="R13" t="n">
-        <v>6998141</v>
+        <v>6998079</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2044,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2054,12 +2031,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122824871</v>
+        <v>122823959</v>
       </c>
       <c r="B14" t="n">
-        <v>79751</v>
+        <v>79848</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2098,25 +2075,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2126,13 +2103,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528956</v>
+        <v>528918</v>
       </c>
       <c r="R14" t="n">
-        <v>6998028</v>
+        <v>6998048</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2161,7 +2138,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2171,12 +2148,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På asp i gammal granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2191,22 +2168,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122824138</v>
+        <v>122824871</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2215,50 +2192,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528887</v>
+        <v>528956</v>
       </c>
       <c r="R15" t="n">
-        <v>6998044</v>
+        <v>6998028</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2287,7 +2255,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2297,12 +2265,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2329,7 +2297,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122823605</v>
+        <v>122823640</v>
       </c>
       <c r="B16" t="n">
         <v>79847</v>
@@ -2369,10 +2337,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528887</v>
+        <v>528890</v>
       </c>
       <c r="R16" t="n">
-        <v>6998073</v>
+        <v>6998093</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2402,24 +2370,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2434,22 +2387,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122823776</v>
+        <v>122823666</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2462,27 +2415,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2491,10 +2444,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528879</v>
+        <v>528890</v>
       </c>
       <c r="R17" t="n">
-        <v>6998065</v>
+        <v>6998089</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2527,6 +2480,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2553,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122823640</v>
+        <v>122825059</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2569,21 +2527,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2593,10 +2551,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528890</v>
+        <v>528960</v>
       </c>
       <c r="R18" t="n">
-        <v>6998093</v>
+        <v>6998066</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2626,9 +2584,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,22 +2616,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122825093</v>
+        <v>122824203</v>
       </c>
       <c r="B19" t="n">
-        <v>91511</v>
+        <v>56688</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2667,38 +2640,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>760</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528967</v>
+        <v>528874</v>
       </c>
       <c r="R19" t="n">
-        <v>6998079</v>
+        <v>6998038</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2730,7 +2708,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2740,12 +2718,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Rikligt med spillning under tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2772,10 +2750,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122823780</v>
+        <v>122824504</v>
       </c>
       <c r="B20" t="n">
-        <v>79848</v>
+        <v>57631</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2788,34 +2766,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528879</v>
+        <v>528884</v>
       </c>
       <c r="R20" t="n">
-        <v>6998066</v>
+        <v>6997998</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2874,10 +2861,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122824314</v>
+        <v>122823308</v>
       </c>
       <c r="B21" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2890,21 +2877,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2914,13 +2901,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528828</v>
+        <v>528904</v>
       </c>
       <c r="R21" t="n">
-        <v>6998005</v>
+        <v>6998141</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2949,7 +2936,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2959,12 +2946,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,22 +2966,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122825157</v>
+        <v>122824419</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>79384</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3007,21 +2994,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3031,10 +3018,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528946</v>
+        <v>528853</v>
       </c>
       <c r="R22" t="n">
-        <v>6998089</v>
+        <v>6998012</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3064,9 +3051,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3081,22 +3083,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122824159</v>
+        <v>122824138</v>
       </c>
       <c r="B23" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3109,24 +3111,33 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
@@ -3168,7 +3179,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3178,12 +3189,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3327,10 +3338,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122824798</v>
+        <v>122824139</v>
       </c>
       <c r="B25" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3343,21 +3354,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3367,10 +3378,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528929</v>
+        <v>528870</v>
       </c>
       <c r="R25" t="n">
-        <v>6998043</v>
+        <v>6997994</v>
       </c>
       <c r="S25" t="n">
         <v>6</v>
@@ -3402,7 +3413,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3412,12 +3423,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3444,10 +3450,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122824689</v>
+        <v>122823776</v>
       </c>
       <c r="B26" t="n">
-        <v>78411</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3460,34 +3466,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528901</v>
+        <v>528879</v>
       </c>
       <c r="R26" t="n">
-        <v>6998033</v>
+        <v>6998065</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3517,24 +3528,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3549,22 +3545,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122824716</v>
+        <v>122825263</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3577,34 +3573,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528980</v>
+        <v>528938</v>
       </c>
       <c r="R27" t="n">
-        <v>6998018</v>
+        <v>6998101</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3637,6 +3638,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3663,10 +3669,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122824775</v>
+        <v>122823780</v>
       </c>
       <c r="B28" t="n">
-        <v>90909</v>
+        <v>79848</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3675,25 +3681,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3703,13 +3709,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528928</v>
+        <v>528879</v>
       </c>
       <c r="R28" t="n">
-        <v>6998037</v>
+        <v>6998066</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3736,24 +3742,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gammal död stående gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3768,22 +3759,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122823943</v>
+        <v>122823389</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3796,27 +3787,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3825,13 +3820,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528895</v>
+        <v>528893</v>
       </c>
       <c r="R29" t="n">
-        <v>6998055</v>
+        <v>6998121</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3858,9 +3853,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3875,22 +3885,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122824608</v>
+        <v>122823616</v>
       </c>
       <c r="B30" t="n">
-        <v>56680</v>
+        <v>79807</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3899,47 +3909,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528928</v>
+        <v>528903</v>
       </c>
       <c r="R30" t="n">
-        <v>6998035</v>
+        <v>6998106</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3969,9 +3970,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3986,19 +4002,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122825059</v>
+        <v>122824159</v>
       </c>
       <c r="B31" t="n">
         <v>77699</v>
@@ -4038,10 +4054,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528960</v>
+        <v>528887</v>
       </c>
       <c r="R31" t="n">
-        <v>6998066</v>
+        <v>6998044</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4073,7 +4089,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4083,12 +4099,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4115,10 +4131,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122823653</v>
+        <v>122825055</v>
       </c>
       <c r="B32" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4131,21 +4147,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4155,13 +4171,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528898</v>
+        <v>529003</v>
       </c>
       <c r="R32" t="n">
-        <v>6998091</v>
+        <v>6998021</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4190,7 +4206,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4200,12 +4216,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4220,22 +4236,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122823789</v>
+        <v>122824716</v>
       </c>
       <c r="B33" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4248,21 +4264,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4272,10 +4288,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528910</v>
+        <v>528980</v>
       </c>
       <c r="R33" t="n">
-        <v>6998072</v>
+        <v>6998018</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4305,24 +4321,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4337,22 +4338,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122823534</v>
+        <v>122824114</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>74863</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4365,39 +4366,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528883</v>
+        <v>528886</v>
       </c>
       <c r="R34" t="n">
-        <v>6998125</v>
+        <v>6998049</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4427,14 +4423,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4449,19 +4455,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122825055</v>
+        <v>122824928</v>
       </c>
       <c r="B35" t="n">
         <v>79847</v>
@@ -4501,13 +4507,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>529003</v>
+        <v>528989</v>
       </c>
       <c r="R35" t="n">
-        <v>6998021</v>
+        <v>6998039</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4534,24 +4540,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4566,22 +4557,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122823224</v>
+        <v>122824940</v>
       </c>
       <c r="B36" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4590,41 +4581,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528911</v>
+        <v>528993</v>
       </c>
       <c r="R36" t="n">
-        <v>6998157</v>
+        <v>6998013</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4663,12 +4663,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4683,22 +4678,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122823616</v>
+        <v>122824608</v>
       </c>
       <c r="B37" t="n">
-        <v>79807</v>
+        <v>56680</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4707,38 +4702,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528903</v>
+        <v>528928</v>
       </c>
       <c r="R37" t="n">
-        <v>6998106</v>
+        <v>6998035</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4768,24 +4772,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4800,22 +4789,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122823542</v>
+        <v>122824669</v>
       </c>
       <c r="B38" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4828,21 +4817,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4852,13 +4841,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528881</v>
+        <v>528962</v>
       </c>
       <c r="R38" t="n">
-        <v>6998117</v>
+        <v>6998022</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4885,24 +4874,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4917,22 +4891,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122824617</v>
+        <v>122824798</v>
       </c>
       <c r="B39" t="n">
-        <v>78502</v>
+        <v>74863</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4945,21 +4919,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4969,13 +4943,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528897</v>
+        <v>528929</v>
       </c>
       <c r="R39" t="n">
-        <v>6998014</v>
+        <v>6998043</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5004,7 +4978,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5014,12 +4988,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5034,22 +5008,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122824996</v>
+        <v>122824294</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5062,21 +5036,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5086,13 +5060,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528952</v>
+        <v>528874</v>
       </c>
       <c r="R40" t="n">
-        <v>6998039</v>
+        <v>6998038</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5121,7 +5095,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5131,12 +5105,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På bark på stam av levande glasbjörk med savflöde</t>
+          <t>På gammal tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5163,10 +5137,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122824669</v>
+        <v>122825192</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5179,21 +5153,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5203,10 +5177,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528962</v>
+        <v>528946</v>
       </c>
       <c r="R41" t="n">
-        <v>6998022</v>
+        <v>6998089</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5265,7 +5239,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122824139</v>
+        <v>122824883</v>
       </c>
       <c r="B42" t="n">
         <v>79847</v>
@@ -5298,20 +5272,29 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528870</v>
+        <v>528973</v>
       </c>
       <c r="R42" t="n">
-        <v>6997994</v>
+        <v>6998038</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5340,7 +5323,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5350,7 +5333,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5377,10 +5365,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122824729</v>
+        <v>122824517</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5393,21 +5381,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5417,13 +5405,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528904</v>
+        <v>528878</v>
       </c>
       <c r="R43" t="n">
-        <v>6998036</v>
+        <v>6997997</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5452,7 +5440,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5462,12 +5450,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5494,10 +5482,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122823666</v>
+        <v>122824645</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5510,39 +5498,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528890</v>
+        <v>528897</v>
       </c>
       <c r="R44" t="n">
-        <v>6998089</v>
+        <v>6998014</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5572,14 +5555,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5594,22 +5587,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122824883</v>
+        <v>122823876</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5622,26 +5615,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5655,13 +5648,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528973</v>
+        <v>528897</v>
       </c>
       <c r="R45" t="n">
-        <v>6998038</v>
+        <v>6998064</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5690,7 +5683,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5700,12 +5693,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På död sälg (kort)</t>
+          <t>På gamla granar i gammal senvuxen granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5720,22 +5713,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122824915</v>
+        <v>122824617</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5748,21 +5741,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5772,10 +5765,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528964</v>
+        <v>528897</v>
       </c>
       <c r="R46" t="n">
-        <v>6998032</v>
+        <v>6998014</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5807,7 +5800,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5817,12 +5810,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På asp i gammal barrblandskog</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5849,10 +5842,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122825263</v>
+        <v>122823224</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>79751</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5861,43 +5854,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528938</v>
+        <v>528911</v>
       </c>
       <c r="R47" t="n">
-        <v>6998101</v>
+        <v>6998157</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5927,14 +5915,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5949,22 +5947,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122823389</v>
+        <v>122824296</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5977,31 +5975,27 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6010,13 +6004,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528893</v>
+        <v>528849</v>
       </c>
       <c r="R48" t="n">
-        <v>6998121</v>
+        <v>6998016</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6043,24 +6037,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6075,22 +6059,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122824928</v>
+        <v>122823534</v>
       </c>
       <c r="B49" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6103,34 +6087,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528989</v>
+        <v>528883</v>
       </c>
       <c r="R49" t="n">
-        <v>6998039</v>
+        <v>6998125</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6163,6 +6152,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6189,10 +6183,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122823959</v>
+        <v>122823605</v>
       </c>
       <c r="B50" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6205,21 +6199,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6229,13 +6223,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528918</v>
+        <v>528887</v>
       </c>
       <c r="R50" t="n">
-        <v>6998048</v>
+        <v>6998073</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6264,7 +6258,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6274,12 +6268,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6306,10 +6300,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122824504</v>
+        <v>122824314</v>
       </c>
       <c r="B51" t="n">
-        <v>57631</v>
+        <v>78503</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6322,46 +6316,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528884</v>
+        <v>528828</v>
       </c>
       <c r="R51" t="n">
-        <v>6997998</v>
+        <v>6998005</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6388,9 +6373,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6405,12 +6405,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122825157</v>
+        <v>122823789</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528946</v>
+        <v>528910</v>
       </c>
       <c r="R3" t="n">
-        <v>6998089</v>
+        <v>6998072</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,9 +874,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,19 +906,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122823943</v>
+        <v>122825157</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -937,21 +952,16 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528895</v>
+        <v>528946</v>
       </c>
       <c r="R4" t="n">
-        <v>6998055</v>
+        <v>6998089</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1010,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122824996</v>
+        <v>122823943</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1044,19 +1054,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528952</v>
+        <v>528895</v>
       </c>
       <c r="R5" t="n">
-        <v>6998039</v>
+        <v>6998055</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,24 +1098,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande glasbjörk med savflöde</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,22 +1115,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122823542</v>
+        <v>122824996</v>
       </c>
       <c r="B6" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,21 +1143,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528881</v>
+        <v>528952</v>
       </c>
       <c r="R6" t="n">
-        <v>6998117</v>
+        <v>6998039</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>På bark på stam av levande glasbjörk med savflöde</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122823789</v>
+        <v>122823542</v>
       </c>
       <c r="B7" t="n">
-        <v>79848</v>
+        <v>78503</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,21 +1260,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,13 +1284,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528910</v>
+        <v>528881</v>
       </c>
       <c r="R7" t="n">
-        <v>6998072</v>
+        <v>6998117</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På sälglåga i gammal granskog</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -2297,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122823640</v>
+        <v>122823666</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,24 +2313,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
@@ -2340,7 +2345,7 @@
         <v>528890</v>
       </c>
       <c r="R16" t="n">
-        <v>6998093</v>
+        <v>6998089</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2373,6 +2378,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122823666</v>
+        <v>122825059</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,39 +2425,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528890</v>
+        <v>528960</v>
       </c>
       <c r="R17" t="n">
-        <v>6998089</v>
+        <v>6998066</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2477,14 +2482,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,22 +2514,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122825059</v>
+        <v>122823640</v>
       </c>
       <c r="B18" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2527,21 +2542,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2551,10 +2566,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528960</v>
+        <v>528890</v>
       </c>
       <c r="R18" t="n">
-        <v>6998066</v>
+        <v>6998093</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,24 +2599,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,12 +2616,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -5482,10 +5482,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122824645</v>
+        <v>122824617</v>
       </c>
       <c r="B44" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5498,21 +5498,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5725,10 +5725,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122824617</v>
+        <v>122823224</v>
       </c>
       <c r="B46" t="n">
-        <v>78502</v>
+        <v>79751</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5737,25 +5737,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5765,10 +5765,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528897</v>
+        <v>528911</v>
       </c>
       <c r="R46" t="n">
-        <v>6998014</v>
+        <v>6998157</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5842,10 +5842,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122823224</v>
+        <v>122824645</v>
       </c>
       <c r="B47" t="n">
-        <v>79751</v>
+        <v>78503</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5854,25 +5854,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5882,10 +5882,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528911</v>
+        <v>528897</v>
       </c>
       <c r="R47" t="n">
-        <v>6998157</v>
+        <v>6998014</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -2297,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122823666</v>
+        <v>122823640</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,29 +2313,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
@@ -2345,7 +2340,7 @@
         <v>528890</v>
       </c>
       <c r="R16" t="n">
-        <v>6998089</v>
+        <v>6998093</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,11 +2373,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,10 +2399,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122825059</v>
+        <v>122823666</v>
       </c>
       <c r="B17" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2425,34 +2415,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528960</v>
+        <v>528890</v>
       </c>
       <c r="R17" t="n">
-        <v>6998066</v>
+        <v>6998089</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2482,24 +2477,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,22 +2499,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122823640</v>
+        <v>122825059</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2542,21 +2527,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2566,10 +2551,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528890</v>
+        <v>528960</v>
       </c>
       <c r="R18" t="n">
-        <v>6998093</v>
+        <v>6998066</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2599,9 +2584,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,22 +2616,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122824203</v>
+        <v>122823308</v>
       </c>
       <c r="B19" t="n">
-        <v>56688</v>
+        <v>78502</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2640,46 +2640,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528874</v>
+        <v>528904</v>
       </c>
       <c r="R19" t="n">
-        <v>6998038</v>
+        <v>6998141</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2708,7 +2703,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2718,12 +2713,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med spillning under tall</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2750,10 +2745,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122824504</v>
+        <v>122824419</v>
       </c>
       <c r="B20" t="n">
-        <v>57631</v>
+        <v>79384</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2766,43 +2761,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528884</v>
+        <v>528853</v>
       </c>
       <c r="R20" t="n">
-        <v>6997998</v>
+        <v>6998012</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2832,9 +2818,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2849,22 +2850,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122823308</v>
+        <v>122824203</v>
       </c>
       <c r="B21" t="n">
-        <v>78502</v>
+        <v>56688</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2873,41 +2874,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528904</v>
+        <v>528874</v>
       </c>
       <c r="R21" t="n">
-        <v>6998141</v>
+        <v>6998038</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2936,7 +2942,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2946,12 +2952,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>Rikligt med spillning under tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,10 +2984,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122824419</v>
+        <v>122824504</v>
       </c>
       <c r="B22" t="n">
-        <v>79384</v>
+        <v>57631</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2994,34 +3000,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528853</v>
+        <v>528884</v>
       </c>
       <c r="R22" t="n">
-        <v>6998012</v>
+        <v>6997998</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3051,24 +3066,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3083,12 +3083,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122823935</v>
+        <v>122825263</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3237,37 +3237,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528934</v>
+        <v>528938</v>
       </c>
       <c r="R24" t="n">
-        <v>6998051</v>
+        <v>6998101</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3294,24 +3299,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3326,19 +3321,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122824139</v>
+        <v>122823935</v>
       </c>
       <c r="B25" t="n">
         <v>79847</v>
@@ -3378,13 +3373,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528870</v>
+        <v>528934</v>
       </c>
       <c r="R25" t="n">
-        <v>6997994</v>
+        <v>6998051</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3413,7 +3408,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3423,7 +3418,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3450,7 +3450,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122823776</v>
+        <v>122824139</v>
       </c>
       <c r="B26" t="n">
         <v>79847</v>
@@ -3484,24 +3484,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528879</v>
+        <v>528870</v>
       </c>
       <c r="R26" t="n">
-        <v>6998065</v>
+        <v>6997994</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3528,9 +3523,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3545,22 +3550,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122825263</v>
+        <v>122823776</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3573,27 +3578,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3602,10 +3607,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528938</v>
+        <v>528879</v>
       </c>
       <c r="R27" t="n">
-        <v>6998101</v>
+        <v>6998065</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3638,11 +3643,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -5137,10 +5137,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122825192</v>
+        <v>122824517</v>
       </c>
       <c r="B41" t="n">
-        <v>79848</v>
+        <v>78503</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5153,21 +5153,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528946</v>
+        <v>528878</v>
       </c>
       <c r="R41" t="n">
-        <v>6998089</v>
+        <v>6997997</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5210,9 +5210,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5227,22 +5242,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122824883</v>
+        <v>122825192</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5255,46 +5270,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528973</v>
+        <v>528946</v>
       </c>
       <c r="R42" t="n">
-        <v>6998038</v>
+        <v>6998089</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5321,24 +5327,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5353,22 +5344,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122824517</v>
+        <v>122824883</v>
       </c>
       <c r="B43" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5381,37 +5372,46 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528878</v>
+        <v>528973</v>
       </c>
       <c r="R43" t="n">
-        <v>6997997</v>
+        <v>6998038</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
+          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5470,22 +5470,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122824617</v>
+        <v>122824645</v>
       </c>
       <c r="B44" t="n">
-        <v>78502</v>
+        <v>78503</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5498,21 +5498,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5725,10 +5725,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122823224</v>
+        <v>122824617</v>
       </c>
       <c r="B46" t="n">
-        <v>79751</v>
+        <v>78502</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5737,25 +5737,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5765,10 +5765,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528911</v>
+        <v>528897</v>
       </c>
       <c r="R46" t="n">
-        <v>6998157</v>
+        <v>6998014</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5842,10 +5842,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122824645</v>
+        <v>122823224</v>
       </c>
       <c r="B47" t="n">
-        <v>78503</v>
+        <v>79751</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5854,25 +5854,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5882,10 +5882,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528897</v>
+        <v>528911</v>
       </c>
       <c r="R47" t="n">
-        <v>6998014</v>
+        <v>6998157</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -2297,10 +2297,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122823640</v>
+        <v>122823666</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,24 +2313,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
@@ -2340,7 +2345,7 @@
         <v>528890</v>
       </c>
       <c r="R16" t="n">
-        <v>6998093</v>
+        <v>6998089</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2373,6 +2378,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122823666</v>
+        <v>122825059</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,39 +2425,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528890</v>
+        <v>528960</v>
       </c>
       <c r="R17" t="n">
-        <v>6998089</v>
+        <v>6998066</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2477,14 +2482,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2499,22 +2514,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122825059</v>
+        <v>122823640</v>
       </c>
       <c r="B18" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2527,21 +2542,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2551,10 +2566,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528960</v>
+        <v>528890</v>
       </c>
       <c r="R18" t="n">
-        <v>6998066</v>
+        <v>6998093</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,24 +2599,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,22 +2616,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122823308</v>
+        <v>122824203</v>
       </c>
       <c r="B19" t="n">
-        <v>78502</v>
+        <v>56688</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2640,41 +2640,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528904</v>
+        <v>528874</v>
       </c>
       <c r="R19" t="n">
-        <v>6998141</v>
+        <v>6998038</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2703,7 +2708,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2713,12 +2718,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>Rikligt med spillning under tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,10 +2750,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122824419</v>
+        <v>122824504</v>
       </c>
       <c r="B20" t="n">
-        <v>79384</v>
+        <v>57631</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,34 +2766,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528853</v>
+        <v>528884</v>
       </c>
       <c r="R20" t="n">
-        <v>6998012</v>
+        <v>6997998</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2818,24 +2832,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2850,22 +2849,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122824203</v>
+        <v>122823308</v>
       </c>
       <c r="B21" t="n">
-        <v>56688</v>
+        <v>78502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2874,46 +2873,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528874</v>
+        <v>528904</v>
       </c>
       <c r="R21" t="n">
-        <v>6998038</v>
+        <v>6998141</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2942,7 +2936,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2952,12 +2946,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt med spillning under tall</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2984,10 +2978,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122824504</v>
+        <v>122824419</v>
       </c>
       <c r="B22" t="n">
-        <v>57631</v>
+        <v>79384</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3000,43 +2994,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528884</v>
+        <v>528853</v>
       </c>
       <c r="R22" t="n">
-        <v>6997998</v>
+        <v>6998012</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3066,9 +3051,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3083,12 +3083,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122825263</v>
+        <v>122823935</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3237,42 +3237,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528938</v>
+        <v>528934</v>
       </c>
       <c r="R24" t="n">
-        <v>6998101</v>
+        <v>6998051</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3299,14 +3294,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3321,19 +3326,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122823935</v>
+        <v>122824139</v>
       </c>
       <c r="B25" t="n">
         <v>79847</v>
@@ -3373,13 +3378,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528934</v>
+        <v>528870</v>
       </c>
       <c r="R25" t="n">
-        <v>6998051</v>
+        <v>6997994</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3408,7 +3413,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3418,12 +3423,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3450,7 +3450,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122824139</v>
+        <v>122823776</v>
       </c>
       <c r="B26" t="n">
         <v>79847</v>
@@ -3484,19 +3484,24 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528870</v>
+        <v>528879</v>
       </c>
       <c r="R26" t="n">
-        <v>6997994</v>
+        <v>6998065</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3523,19 +3528,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3550,22 +3545,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122823776</v>
+        <v>122825263</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3578,27 +3573,27 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3607,10 +3602,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528879</v>
+        <v>528938</v>
       </c>
       <c r="R27" t="n">
-        <v>6998065</v>
+        <v>6998101</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3643,6 +3638,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -5137,10 +5137,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122824517</v>
+        <v>122825192</v>
       </c>
       <c r="B41" t="n">
-        <v>78503</v>
+        <v>79848</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5153,21 +5153,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528878</v>
+        <v>528946</v>
       </c>
       <c r="R41" t="n">
-        <v>6997997</v>
+        <v>6998089</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5210,24 +5210,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5242,22 +5227,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122825192</v>
+        <v>122824883</v>
       </c>
       <c r="B42" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5270,37 +5255,46 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528946</v>
+        <v>528973</v>
       </c>
       <c r="R42" t="n">
-        <v>6998089</v>
+        <v>6998038</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5327,9 +5321,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5344,22 +5353,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122824883</v>
+        <v>122824517</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5372,46 +5381,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528973</v>
+        <v>528878</v>
       </c>
       <c r="R43" t="n">
-        <v>6998038</v>
+        <v>6997997</v>
       </c>
       <c r="S43" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På död sälg (kort)</t>
+          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5470,12 +5470,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122823789</v>
+        <v>122824517</v>
       </c>
       <c r="B3" t="n">
-        <v>79848</v>
+        <v>78503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528910</v>
+        <v>528878</v>
       </c>
       <c r="R3" t="n">
-        <v>6998072</v>
+        <v>6997997</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På sälglåga i gammal granskog</t>
+          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122825157</v>
+        <v>122823876</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,34 +934,43 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528946</v>
+        <v>528897</v>
       </c>
       <c r="R4" t="n">
-        <v>6998089</v>
+        <v>6998064</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,9 +1000,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal senvuxen granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,19 +1032,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122823943</v>
+        <v>122825157</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1054,21 +1078,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528895</v>
+        <v>528946</v>
       </c>
       <c r="R5" t="n">
-        <v>6998055</v>
+        <v>6998089</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,7 +1146,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122824996</v>
+        <v>122824883</v>
       </c>
       <c r="B6" t="n">
         <v>79847</v>
@@ -1160,20 +1179,29 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528952</v>
+        <v>528973</v>
       </c>
       <c r="R6" t="n">
-        <v>6998039</v>
+        <v>6998038</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1202,7 +1230,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1212,12 +1240,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På bark på stam av levande glasbjörk med savflöde</t>
+          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,22 +1260,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122823542</v>
+        <v>122824139</v>
       </c>
       <c r="B7" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,21 +1288,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1284,13 +1312,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528881</v>
+        <v>528870</v>
       </c>
       <c r="R7" t="n">
-        <v>6998117</v>
+        <v>6997994</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1357,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:32</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,22 +1372,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122824689</v>
+        <v>122824296</v>
       </c>
       <c r="B8" t="n">
-        <v>78411</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,34 +1400,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528901</v>
+        <v>528849</v>
       </c>
       <c r="R8" t="n">
-        <v>6998033</v>
+        <v>6998016</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,24 +1462,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,22 +1484,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122824915</v>
+        <v>122823534</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,34 +1512,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528964</v>
+        <v>528883</v>
       </c>
       <c r="R9" t="n">
-        <v>6998032</v>
+        <v>6998125</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,24 +1574,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På asp i gammal barrblandskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,19 +1596,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122824729</v>
+        <v>122824294</v>
       </c>
       <c r="B10" t="n">
         <v>78766</v>
@@ -1635,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528904</v>
+        <v>528874</v>
       </c>
       <c r="R10" t="n">
-        <v>6998036</v>
+        <v>6998038</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1683,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,12 +1693,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122823653</v>
+        <v>122824940</v>
       </c>
       <c r="B11" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,37 +1741,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528898</v>
+        <v>528993</v>
       </c>
       <c r="R11" t="n">
-        <v>6998091</v>
+        <v>6998013</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1787,7 +1809,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,12 +1819,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,22 +1834,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122824775</v>
+        <v>122825263</v>
       </c>
       <c r="B12" t="n">
-        <v>90909</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,41 +1858,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528928</v>
+        <v>528938</v>
       </c>
       <c r="R12" t="n">
-        <v>6998037</v>
+        <v>6998101</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1902,24 +1924,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal död stående gran i gammal barrblandskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,22 +1946,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122825093</v>
+        <v>122824608</v>
       </c>
       <c r="B13" t="n">
-        <v>91511</v>
+        <v>56680</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1958,38 +1970,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>760</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528967</v>
+        <v>528928</v>
       </c>
       <c r="R13" t="n">
-        <v>6998079</v>
+        <v>6998035</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,24 +2040,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,22 +2057,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122823959</v>
+        <v>122825059</v>
       </c>
       <c r="B14" t="n">
-        <v>79848</v>
+        <v>77699</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2079,21 +2085,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2103,13 +2109,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528918</v>
+        <v>528960</v>
       </c>
       <c r="R14" t="n">
-        <v>6998048</v>
+        <v>6998066</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2138,7 +2144,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2148,12 +2154,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,22 +2174,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122824871</v>
+        <v>122823959</v>
       </c>
       <c r="B15" t="n">
-        <v>79751</v>
+        <v>79848</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,25 +2198,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2220,13 +2226,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528956</v>
+        <v>528918</v>
       </c>
       <c r="R15" t="n">
-        <v>6998028</v>
+        <v>6998048</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2255,7 +2261,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2265,12 +2271,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På asp i gammal granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,22 +2291,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122823666</v>
+        <v>122824915</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2313,39 +2319,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528890</v>
+        <v>528964</v>
       </c>
       <c r="R16" t="n">
-        <v>6998089</v>
+        <v>6998032</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,14 +2376,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,22 +2408,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122825059</v>
+        <v>122825093</v>
       </c>
       <c r="B17" t="n">
-        <v>77699</v>
+        <v>91511</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2421,25 +2432,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>760</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2449,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528960</v>
+        <v>528967</v>
       </c>
       <c r="R17" t="n">
-        <v>6998066</v>
+        <v>6998079</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2484,7 +2495,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2494,12 +2505,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,10 +2537,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122823640</v>
+        <v>122824729</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2542,21 +2553,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2566,10 +2577,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528890</v>
+        <v>528904</v>
       </c>
       <c r="R18" t="n">
-        <v>6998093</v>
+        <v>6998036</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2599,9 +2610,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2616,22 +2642,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122824203</v>
+        <v>122823605</v>
       </c>
       <c r="B19" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2640,43 +2666,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528874</v>
+        <v>528887</v>
       </c>
       <c r="R19" t="n">
-        <v>6998038</v>
+        <v>6998073</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2708,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2718,12 +2739,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt med spillning under tall</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2738,22 +2759,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122824504</v>
+        <v>122824669</v>
       </c>
       <c r="B20" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2766,43 +2787,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528884</v>
+        <v>528962</v>
       </c>
       <c r="R20" t="n">
-        <v>6997998</v>
+        <v>6998022</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2861,10 +2873,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122823308</v>
+        <v>122824689</v>
       </c>
       <c r="B21" t="n">
-        <v>78502</v>
+        <v>78411</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2877,21 +2889,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2901,13 +2913,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528904</v>
+        <v>528901</v>
       </c>
       <c r="R21" t="n">
-        <v>6998141</v>
+        <v>6998033</v>
       </c>
       <c r="S21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2936,7 +2948,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2946,12 +2958,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,10 +2990,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122824419</v>
+        <v>122823943</v>
       </c>
       <c r="B22" t="n">
-        <v>79384</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2994,34 +3006,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528853</v>
+        <v>528895</v>
       </c>
       <c r="R22" t="n">
-        <v>6998012</v>
+        <v>6998055</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3051,24 +3068,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3083,22 +3085,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122824138</v>
+        <v>122823776</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3111,31 +3113,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3144,10 +3142,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528887</v>
+        <v>528879</v>
       </c>
       <c r="R23" t="n">
-        <v>6998044</v>
+        <v>6998065</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3177,24 +3175,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3209,22 +3192,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122823935</v>
+        <v>122824203</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3233,41 +3216,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528934</v>
+        <v>528874</v>
       </c>
       <c r="R24" t="n">
-        <v>6998051</v>
+        <v>6998038</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3296,7 +3284,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3306,12 +3294,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Rikligt med spillning under tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3326,22 +3314,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122824139</v>
+        <v>122824645</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3354,21 +3342,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3378,13 +3366,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528870</v>
+        <v>528897</v>
       </c>
       <c r="R25" t="n">
-        <v>6997994</v>
+        <v>6998014</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3413,7 +3401,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3423,7 +3411,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3438,22 +3431,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122823776</v>
+        <v>122824798</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3466,42 +3459,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528879</v>
+        <v>528929</v>
       </c>
       <c r="R26" t="n">
-        <v>6998065</v>
+        <v>6998043</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3528,9 +3516,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3545,22 +3548,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122825263</v>
+        <v>122823616</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>79807</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3569,43 +3572,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528938</v>
+        <v>528903</v>
       </c>
       <c r="R27" t="n">
-        <v>6998101</v>
+        <v>6998106</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3635,14 +3633,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3657,19 +3665,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122823780</v>
+        <v>122825192</v>
       </c>
       <c r="B28" t="n">
         <v>79848</v>
@@ -3709,10 +3717,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528879</v>
+        <v>528946</v>
       </c>
       <c r="R28" t="n">
-        <v>6998066</v>
+        <v>6998089</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3771,10 +3779,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122823389</v>
+        <v>122824617</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>78502</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3787,46 +3795,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528893</v>
+        <v>528897</v>
       </c>
       <c r="R29" t="n">
-        <v>6998121</v>
+        <v>6998014</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3855,7 +3854,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3865,12 +3864,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3885,22 +3884,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122823616</v>
+        <v>122823224</v>
       </c>
       <c r="B30" t="n">
-        <v>79807</v>
+        <v>79751</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3913,21 +3912,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>6456</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3937,10 +3936,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528903</v>
+        <v>528911</v>
       </c>
       <c r="R30" t="n">
-        <v>6998106</v>
+        <v>6998157</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3972,7 +3971,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3982,12 +3981,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4014,10 +4013,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122824159</v>
+        <v>122824996</v>
       </c>
       <c r="B31" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4030,21 +4029,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4054,13 +4053,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528887</v>
+        <v>528952</v>
       </c>
       <c r="R31" t="n">
-        <v>6998044</v>
+        <v>6998039</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4089,7 +4088,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4099,12 +4098,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande glasbjörk med savflöde</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4131,10 +4130,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122825055</v>
+        <v>122824114</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4147,21 +4146,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4171,13 +4170,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>529003</v>
+        <v>528886</v>
       </c>
       <c r="R32" t="n">
-        <v>6998021</v>
+        <v>6998049</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4206,7 +4205,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4216,12 +4215,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4236,22 +4235,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122824716</v>
+        <v>122823389</v>
       </c>
       <c r="B33" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4264,37 +4263,46 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528980</v>
+        <v>528893</v>
       </c>
       <c r="R33" t="n">
-        <v>6998018</v>
+        <v>6998121</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4321,9 +4329,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4338,22 +4361,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122824114</v>
+        <v>122823640</v>
       </c>
       <c r="B34" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4366,21 +4389,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4390,10 +4413,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528886</v>
+        <v>528890</v>
       </c>
       <c r="R34" t="n">
-        <v>6998049</v>
+        <v>6998093</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4423,24 +4446,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4455,22 +4463,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122824928</v>
+        <v>122824871</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4479,25 +4487,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4507,13 +4515,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528989</v>
+        <v>528956</v>
       </c>
       <c r="R35" t="n">
-        <v>6998039</v>
+        <v>6998028</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4540,9 +4548,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4557,22 +4580,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122824940</v>
+        <v>122824775</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>90909</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4581,50 +4604,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528993</v>
+        <v>528928</v>
       </c>
       <c r="R36" t="n">
-        <v>6998013</v>
+        <v>6998037</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4653,7 +4667,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4663,7 +4677,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gammal död stående gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4678,22 +4697,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122824608</v>
+        <v>122823789</v>
       </c>
       <c r="B37" t="n">
-        <v>56680</v>
+        <v>79848</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4706,43 +4725,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528928</v>
+        <v>528910</v>
       </c>
       <c r="R37" t="n">
-        <v>6998035</v>
+        <v>6998072</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4772,9 +4782,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4789,19 +4814,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122824669</v>
+        <v>122824716</v>
       </c>
       <c r="B38" t="n">
         <v>79847</v>
@@ -4841,10 +4866,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528962</v>
+        <v>528980</v>
       </c>
       <c r="R38" t="n">
-        <v>6998022</v>
+        <v>6998018</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4903,10 +4928,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122824798</v>
+        <v>122823308</v>
       </c>
       <c r="B39" t="n">
-        <v>74863</v>
+        <v>78502</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4919,21 +4944,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4943,10 +4968,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528929</v>
+        <v>528904</v>
       </c>
       <c r="R39" t="n">
-        <v>6998043</v>
+        <v>6998141</v>
       </c>
       <c r="S39" t="n">
         <v>6</v>
@@ -4978,7 +5003,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4988,12 +5013,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5008,7 +5033,7 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -5020,10 +5045,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122824294</v>
+        <v>122824504</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5036,34 +5061,43 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528874</v>
+        <v>528884</v>
       </c>
       <c r="R40" t="n">
-        <v>6998038</v>
+        <v>6997998</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5093,24 +5127,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På gammal tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5125,19 +5144,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122825192</v>
+        <v>122823780</v>
       </c>
       <c r="B41" t="n">
         <v>79848</v>
@@ -5177,10 +5196,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528946</v>
+        <v>528879</v>
       </c>
       <c r="R41" t="n">
-        <v>6998089</v>
+        <v>6998066</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5239,10 +5258,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122824883</v>
+        <v>122823653</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5255,46 +5274,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528973</v>
+        <v>528898</v>
       </c>
       <c r="R42" t="n">
-        <v>6998038</v>
+        <v>6998091</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5323,7 +5333,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5333,12 +5343,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På död sälg (kort)</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5353,22 +5363,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122824517</v>
+        <v>122823666</v>
       </c>
       <c r="B43" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5381,37 +5391,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528878</v>
+        <v>528890</v>
       </c>
       <c r="R43" t="n">
-        <v>6997997</v>
+        <v>6998089</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5438,24 +5453,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5470,22 +5475,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122824645</v>
+        <v>122824159</v>
       </c>
       <c r="B44" t="n">
-        <v>78503</v>
+        <v>77699</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5498,21 +5503,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>228579</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5522,10 +5527,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528897</v>
+        <v>528887</v>
       </c>
       <c r="R44" t="n">
-        <v>6998014</v>
+        <v>6998044</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5557,7 +5562,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5567,12 +5572,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5599,10 +5604,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122823876</v>
+        <v>122823935</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5615,46 +5620,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528897</v>
+        <v>528934</v>
       </c>
       <c r="R45" t="n">
-        <v>6998064</v>
+        <v>6998051</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5683,7 +5679,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5693,12 +5689,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal senvuxen granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5713,22 +5709,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122824617</v>
+        <v>122824928</v>
       </c>
       <c r="B46" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5741,21 +5737,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5765,10 +5761,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528897</v>
+        <v>528989</v>
       </c>
       <c r="R46" t="n">
-        <v>6998014</v>
+        <v>6998039</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5798,24 +5794,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5830,22 +5811,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122823224</v>
+        <v>122824138</v>
       </c>
       <c r="B47" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5854,38 +5835,47 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528911</v>
+        <v>528887</v>
       </c>
       <c r="R47" t="n">
-        <v>6998157</v>
+        <v>6998044</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5917,7 +5907,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5927,12 +5917,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5959,10 +5949,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122824296</v>
+        <v>122823542</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5975,42 +5965,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528849</v>
+        <v>528881</v>
       </c>
       <c r="R48" t="n">
-        <v>6998016</v>
+        <v>6998117</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6037,14 +6022,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6059,22 +6054,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122823534</v>
+        <v>122824314</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6087,42 +6082,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528883</v>
+        <v>528828</v>
       </c>
       <c r="R49" t="n">
-        <v>6998125</v>
+        <v>6998005</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6149,14 +6139,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6171,19 +6171,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122823605</v>
+        <v>122825055</v>
       </c>
       <c r="B50" t="n">
         <v>79847</v>
@@ -6223,13 +6223,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528887</v>
+        <v>529003</v>
       </c>
       <c r="R50" t="n">
-        <v>6998073</v>
+        <v>6998021</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6300,10 +6300,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122824314</v>
+        <v>122824419</v>
       </c>
       <c r="B51" t="n">
-        <v>78503</v>
+        <v>79384</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6316,21 +6316,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528828</v>
+        <v>528853</v>
       </c>
       <c r="R51" t="n">
-        <v>6998005</v>
+        <v>6998012</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe</t>
+          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6405,7 +6405,7 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -6066,10 +6066,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122824314</v>
+        <v>122825055</v>
       </c>
       <c r="B49" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6082,21 +6082,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6106,13 +6106,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528828</v>
+        <v>529003</v>
       </c>
       <c r="R49" t="n">
-        <v>6998005</v>
+        <v>6998021</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6183,10 +6183,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122825055</v>
+        <v>122824419</v>
       </c>
       <c r="B50" t="n">
-        <v>79847</v>
+        <v>79384</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6199,21 +6199,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6223,13 +6223,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>529003</v>
+        <v>528853</v>
       </c>
       <c r="R50" t="n">
-        <v>6998021</v>
+        <v>6998012</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6288,22 +6288,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122824419</v>
+        <v>122824314</v>
       </c>
       <c r="B51" t="n">
-        <v>79384</v>
+        <v>78503</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6316,21 +6316,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528853</v>
+        <v>528828</v>
       </c>
       <c r="R51" t="n">
-        <v>6998012</v>
+        <v>6998005</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På ved på gammal tallhögstubbe</t>
+          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6405,12 +6405,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -5375,10 +5375,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122823666</v>
+        <v>122824159</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5391,39 +5391,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528890</v>
+        <v>528887</v>
       </c>
       <c r="R43" t="n">
-        <v>6998089</v>
+        <v>6998044</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5453,14 +5448,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5475,22 +5480,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122824159</v>
+        <v>122823666</v>
       </c>
       <c r="B44" t="n">
-        <v>77699</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5503,34 +5508,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528887</v>
+        <v>528890</v>
       </c>
       <c r="R44" t="n">
-        <v>6998044</v>
+        <v>6998089</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5560,24 +5570,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5592,12 +5592,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6066,10 +6066,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122825055</v>
+        <v>122824314</v>
       </c>
       <c r="B49" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6082,21 +6082,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6106,13 +6106,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>529003</v>
+        <v>528828</v>
       </c>
       <c r="R49" t="n">
-        <v>6998021</v>
+        <v>6998005</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6141,7 +6141,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6183,10 +6183,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122824419</v>
+        <v>122825055</v>
       </c>
       <c r="B50" t="n">
-        <v>79384</v>
+        <v>79847</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6199,21 +6199,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6223,13 +6223,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528853</v>
+        <v>529003</v>
       </c>
       <c r="R50" t="n">
-        <v>6998012</v>
+        <v>6998021</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6268,12 +6268,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På ved på gammal tallhögstubbe</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6288,22 +6288,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122824314</v>
+        <v>122824419</v>
       </c>
       <c r="B51" t="n">
-        <v>78503</v>
+        <v>79384</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6316,21 +6316,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528828</v>
+        <v>528853</v>
       </c>
       <c r="R51" t="n">
-        <v>6998005</v>
+        <v>6998012</v>
       </c>
       <c r="S51" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe</t>
+          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6405,12 +6405,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122824517</v>
+        <v>122825093</v>
       </c>
       <c r="B3" t="n">
-        <v>78503</v>
+        <v>91519</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,25 +813,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>760</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528878</v>
+        <v>528967</v>
       </c>
       <c r="R3" t="n">
-        <v>6997997</v>
+        <v>6998079</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122823876</v>
+        <v>122824729</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -951,26 +951,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528897</v>
+        <v>528904</v>
       </c>
       <c r="R4" t="n">
-        <v>6998064</v>
+        <v>6998036</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal senvuxen granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122825157</v>
+        <v>122823605</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1084,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528946</v>
+        <v>528887</v>
       </c>
       <c r="R5" t="n">
-        <v>6998089</v>
+        <v>6998073</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,9 +1108,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,22 +1140,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122824883</v>
+        <v>122825263</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,31 +1168,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1195,13 +1197,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528973</v>
+        <v>528938</v>
       </c>
       <c r="R6" t="n">
-        <v>6998038</v>
+        <v>6998101</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1228,24 +1230,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På död sälg (kort)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,22 +1252,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122824139</v>
+        <v>122823389</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,37 +1280,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528870</v>
+        <v>528893</v>
       </c>
       <c r="R7" t="n">
-        <v>6997994</v>
+        <v>6998121</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1347,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1357,7 +1358,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122824296</v>
+        <v>122824716</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1400,39 +1406,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528849</v>
+        <v>528980</v>
       </c>
       <c r="R8" t="n">
-        <v>6998016</v>
+        <v>6998018</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,11 +1466,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,7 +1492,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122823534</v>
+        <v>122824296</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1541,10 +1537,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528883</v>
+        <v>528849</v>
       </c>
       <c r="R9" t="n">
-        <v>6998125</v>
+        <v>6998016</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1608,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122824294</v>
+        <v>122823666</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1624,34 +1620,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528874</v>
+        <v>528890</v>
       </c>
       <c r="R10" t="n">
-        <v>6998038</v>
+        <v>6998089</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,24 +1682,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1713,22 +1704,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122824940</v>
+        <v>122825059</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,46 +1732,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528993</v>
+        <v>528960</v>
       </c>
       <c r="R11" t="n">
-        <v>6998013</v>
+        <v>6998066</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1809,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1819,7 +1801,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,22 +1821,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122825263</v>
+        <v>122823640</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1862,39 +1849,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528938</v>
+        <v>528890</v>
       </c>
       <c r="R12" t="n">
-        <v>6998101</v>
+        <v>6998093</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,11 +1909,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,10 +1935,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122824608</v>
+        <v>122823780</v>
       </c>
       <c r="B13" t="n">
-        <v>56680</v>
+        <v>79848</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,43 +1951,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528928</v>
+        <v>528879</v>
       </c>
       <c r="R13" t="n">
-        <v>6998035</v>
+        <v>6998066</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2069,10 +2037,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122825059</v>
+        <v>122823959</v>
       </c>
       <c r="B14" t="n">
-        <v>77699</v>
+        <v>79848</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,21 +2053,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2109,13 +2077,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528960</v>
+        <v>528918</v>
       </c>
       <c r="R14" t="n">
-        <v>6998066</v>
+        <v>6998048</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2144,7 +2112,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2154,12 +2122,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,19 +2142,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122823959</v>
+        <v>122825192</v>
       </c>
       <c r="B15" t="n">
         <v>79848</v>
@@ -2226,13 +2194,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528918</v>
+        <v>528946</v>
       </c>
       <c r="R15" t="n">
-        <v>6998048</v>
+        <v>6998089</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2259,24 +2227,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,19 +2244,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122824915</v>
+        <v>122824996</v>
       </c>
       <c r="B16" t="n">
         <v>79847</v>
@@ -2343,13 +2296,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528964</v>
+        <v>528952</v>
       </c>
       <c r="R16" t="n">
-        <v>6998032</v>
+        <v>6998039</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2378,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2388,12 +2341,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På asp i gammal barrblandskog</t>
+          <t>På bark på stam av levande glasbjörk med savflöde</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2420,10 +2373,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122825093</v>
+        <v>122823308</v>
       </c>
       <c r="B17" t="n">
-        <v>91511</v>
+        <v>78502</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2432,25 +2385,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>760</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2460,13 +2413,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528967</v>
+        <v>528904</v>
       </c>
       <c r="R17" t="n">
-        <v>6998079</v>
+        <v>6998141</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2495,7 +2448,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2505,12 +2458,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2537,10 +2490,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122824729</v>
+        <v>122823943</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2553,34 +2506,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528904</v>
+        <v>528895</v>
       </c>
       <c r="R18" t="n">
-        <v>6998036</v>
+        <v>6998055</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2610,24 +2568,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2642,22 +2585,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122823605</v>
+        <v>122824419</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>79384</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2670,21 +2613,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2694,10 +2637,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528887</v>
+        <v>528853</v>
       </c>
       <c r="R19" t="n">
-        <v>6998073</v>
+        <v>6998012</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2729,7 +2672,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,12 +2682,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2759,22 +2702,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122824669</v>
+        <v>122823616</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2783,25 +2726,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2811,10 +2754,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528962</v>
+        <v>528903</v>
       </c>
       <c r="R20" t="n">
-        <v>6998022</v>
+        <v>6998106</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2844,9 +2787,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2861,22 +2819,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122824689</v>
+        <v>122823876</v>
       </c>
       <c r="B21" t="n">
-        <v>78411</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2889,34 +2847,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528901</v>
+        <v>528897</v>
       </c>
       <c r="R21" t="n">
-        <v>6998033</v>
+        <v>6998064</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2948,7 +2915,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2958,12 +2925,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>På gamla granar i gammal senvuxen granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2990,10 +2957,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122823943</v>
+        <v>122824689</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>78411</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3006,39 +2973,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528895</v>
+        <v>528901</v>
       </c>
       <c r="R22" t="n">
-        <v>6998055</v>
+        <v>6998033</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3068,9 +3030,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3085,22 +3062,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122823776</v>
+        <v>122823224</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3109,43 +3086,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528879</v>
+        <v>528911</v>
       </c>
       <c r="R23" t="n">
-        <v>6998065</v>
+        <v>6998157</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3175,9 +3147,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3192,22 +3179,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122824203</v>
+        <v>122823542</v>
       </c>
       <c r="B24" t="n">
-        <v>56688</v>
+        <v>78503</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3216,46 +3203,41 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528874</v>
+        <v>528881</v>
       </c>
       <c r="R24" t="n">
-        <v>6998038</v>
+        <v>6998117</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3284,7 +3266,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3294,12 +3276,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt med spillning under tall</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3326,7 +3308,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122824645</v>
+        <v>122824517</v>
       </c>
       <c r="B25" t="n">
         <v>78503</v>
@@ -3366,13 +3348,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528897</v>
+        <v>528878</v>
       </c>
       <c r="R25" t="n">
-        <v>6998014</v>
+        <v>6997997</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3401,7 +3383,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3411,12 +3393,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
+          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3443,10 +3425,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122824798</v>
+        <v>122823789</v>
       </c>
       <c r="B26" t="n">
-        <v>74863</v>
+        <v>79848</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3459,21 +3441,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3483,13 +3465,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528929</v>
+        <v>528910</v>
       </c>
       <c r="R26" t="n">
-        <v>6998043</v>
+        <v>6998072</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3518,7 +3500,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3528,12 +3510,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3548,22 +3530,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122823616</v>
+        <v>122823534</v>
       </c>
       <c r="B27" t="n">
-        <v>79807</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3572,38 +3554,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528903</v>
+        <v>528883</v>
       </c>
       <c r="R27" t="n">
-        <v>6998106</v>
+        <v>6998125</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3633,24 +3620,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,22 +3642,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122825192</v>
+        <v>122825055</v>
       </c>
       <c r="B28" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3693,21 +3670,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3717,13 +3694,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528946</v>
+        <v>529003</v>
       </c>
       <c r="R28" t="n">
-        <v>6998089</v>
+        <v>6998021</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3750,9 +3727,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3767,22 +3759,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122824617</v>
+        <v>122823653</v>
       </c>
       <c r="B29" t="n">
-        <v>78502</v>
+        <v>74863</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3795,21 +3787,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3819,10 +3811,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528897</v>
+        <v>528898</v>
       </c>
       <c r="R29" t="n">
-        <v>6998014</v>
+        <v>6998091</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3854,7 +3846,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3864,12 +3856,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3896,7 +3888,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122823224</v>
+        <v>122824871</v>
       </c>
       <c r="B30" t="n">
         <v>79751</v>
@@ -3936,13 +3928,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528911</v>
+        <v>528956</v>
       </c>
       <c r="R30" t="n">
-        <v>6998157</v>
+        <v>6998028</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3971,7 +3963,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3981,12 +3973,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4013,7 +4005,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122824996</v>
+        <v>122823776</v>
       </c>
       <c r="B31" t="n">
         <v>79847</v>
@@ -4047,19 +4039,24 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528952</v>
+        <v>528879</v>
       </c>
       <c r="R31" t="n">
-        <v>6998039</v>
+        <v>6998065</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4086,24 +4083,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande glasbjörk med savflöde</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4118,22 +4100,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122824114</v>
+        <v>122824203</v>
       </c>
       <c r="B32" t="n">
-        <v>74863</v>
+        <v>56688</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4142,38 +4124,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528886</v>
+        <v>528874</v>
       </c>
       <c r="R32" t="n">
-        <v>6998049</v>
+        <v>6998038</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4205,7 +4192,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4215,12 +4202,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Rikligt med spillning under tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4247,10 +4234,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122823389</v>
+        <v>122824608</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>56680</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4263,21 +4250,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4285,9 +4272,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4296,13 +4283,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528893</v>
+        <v>528928</v>
       </c>
       <c r="R33" t="n">
-        <v>6998121</v>
+        <v>6998035</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4329,24 +4316,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4361,22 +4333,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122823640</v>
+        <v>122824294</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4389,21 +4361,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4413,10 +4385,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528890</v>
+        <v>528874</v>
       </c>
       <c r="R34" t="n">
-        <v>6998093</v>
+        <v>6998038</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4446,9 +4418,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På gammal tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4463,22 +4450,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122824871</v>
+        <v>122824915</v>
       </c>
       <c r="B35" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4487,25 +4474,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4515,13 +4502,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528956</v>
+        <v>528964</v>
       </c>
       <c r="R35" t="n">
-        <v>6998028</v>
+        <v>6998032</v>
       </c>
       <c r="S35" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4550,7 +4537,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4560,12 +4547,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På asp i gammal granskog</t>
+          <t>På asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4592,10 +4579,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122824775</v>
+        <v>122824504</v>
       </c>
       <c r="B36" t="n">
-        <v>90909</v>
+        <v>57631</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4604,41 +4591,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528928</v>
+        <v>528884</v>
       </c>
       <c r="R36" t="n">
-        <v>6998037</v>
+        <v>6997998</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4665,24 +4661,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gammal död stående gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4697,22 +4678,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122823789</v>
+        <v>122823935</v>
       </c>
       <c r="B37" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4725,21 +4706,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4749,13 +4730,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528910</v>
+        <v>528934</v>
       </c>
       <c r="R37" t="n">
-        <v>6998072</v>
+        <v>6998051</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4784,7 +4765,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4794,12 +4775,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På sälglåga i gammal granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4814,22 +4795,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122824716</v>
+        <v>122824645</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4842,21 +4823,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4866,10 +4847,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528980</v>
+        <v>528897</v>
       </c>
       <c r="R38" t="n">
-        <v>6998018</v>
+        <v>6998014</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4899,9 +4880,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4916,22 +4912,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122823308</v>
+        <v>122825157</v>
       </c>
       <c r="B39" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4944,21 +4940,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4968,13 +4964,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528904</v>
+        <v>528946</v>
       </c>
       <c r="R39" t="n">
-        <v>6998141</v>
+        <v>6998089</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5001,24 +4997,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5033,22 +5014,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122824504</v>
+        <v>122824669</v>
       </c>
       <c r="B40" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5061,43 +5042,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528884</v>
+        <v>528962</v>
       </c>
       <c r="R40" t="n">
-        <v>6997998</v>
+        <v>6998022</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5156,10 +5128,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122823780</v>
+        <v>122824114</v>
       </c>
       <c r="B41" t="n">
-        <v>79848</v>
+        <v>74863</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5172,21 +5144,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5196,10 +5168,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528879</v>
+        <v>528886</v>
       </c>
       <c r="R41" t="n">
-        <v>6998066</v>
+        <v>6998049</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5229,9 +5201,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5246,22 +5233,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122823653</v>
+        <v>122824940</v>
       </c>
       <c r="B42" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5274,37 +5261,46 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528898</v>
+        <v>528993</v>
       </c>
       <c r="R42" t="n">
-        <v>6998091</v>
+        <v>6998013</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5333,7 +5329,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5343,12 +5339,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5363,22 +5354,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122824159</v>
+        <v>122824139</v>
       </c>
       <c r="B43" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5391,21 +5382,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5415,13 +5406,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528887</v>
+        <v>528870</v>
       </c>
       <c r="R43" t="n">
-        <v>6998044</v>
+        <v>6997994</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5450,7 +5441,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5460,12 +5451,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5480,22 +5466,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122823666</v>
+        <v>122824314</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5508,42 +5494,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528890</v>
+        <v>528828</v>
       </c>
       <c r="R44" t="n">
-        <v>6998089</v>
+        <v>6998005</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5570,14 +5551,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5592,22 +5583,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122823935</v>
+        <v>122824138</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5620,37 +5611,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528934</v>
+        <v>528887</v>
       </c>
       <c r="R45" t="n">
-        <v>6998051</v>
+        <v>6998044</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5709,22 +5709,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122824928</v>
+        <v>122824798</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5737,21 +5737,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5761,13 +5761,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528989</v>
+        <v>528929</v>
       </c>
       <c r="R46" t="n">
-        <v>6998039</v>
+        <v>6998043</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5794,9 +5794,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5811,22 +5826,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122824138</v>
+        <v>122824159</v>
       </c>
       <c r="B47" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5839,33 +5854,24 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
@@ -5907,7 +5913,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5917,12 +5923,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5949,10 +5955,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122823542</v>
+        <v>122824883</v>
       </c>
       <c r="B48" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5965,34 +5971,43 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528881</v>
+        <v>528973</v>
       </c>
       <c r="R48" t="n">
-        <v>6998117</v>
+        <v>6998038</v>
       </c>
       <c r="S48" t="n">
         <v>7</v>
@@ -6024,7 +6039,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6034,12 +6049,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6054,22 +6069,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122824314</v>
+        <v>122824617</v>
       </c>
       <c r="B49" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6082,21 +6097,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6106,13 +6121,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528828</v>
+        <v>528897</v>
       </c>
       <c r="R49" t="n">
-        <v>6998005</v>
+        <v>6998014</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6141,7 +6156,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6151,12 +6166,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6171,22 +6186,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122825055</v>
+        <v>122824775</v>
       </c>
       <c r="B50" t="n">
-        <v>79847</v>
+        <v>90917</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6195,25 +6210,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6223,13 +6238,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>529003</v>
+        <v>528928</v>
       </c>
       <c r="R50" t="n">
-        <v>6998021</v>
+        <v>6998037</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6258,7 +6273,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6268,12 +6283,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gammal död stående gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6288,22 +6303,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122824419</v>
+        <v>122824928</v>
       </c>
       <c r="B51" t="n">
-        <v>79384</v>
+        <v>79847</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6316,21 +6331,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6340,10 +6355,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528853</v>
+        <v>528989</v>
       </c>
       <c r="R51" t="n">
-        <v>6998012</v>
+        <v>6998039</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6373,24 +6388,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6405,12 +6405,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -5478,10 +5478,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122824314</v>
+        <v>122824798</v>
       </c>
       <c r="B44" t="n">
-        <v>78503</v>
+        <v>74863</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5494,21 +5494,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5518,13 +5518,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528828</v>
+        <v>528929</v>
       </c>
       <c r="R44" t="n">
-        <v>6998005</v>
+        <v>6998043</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5563,12 +5563,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5595,10 +5595,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122824138</v>
+        <v>122824314</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5611,46 +5611,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528887</v>
+        <v>528828</v>
       </c>
       <c r="R45" t="n">
-        <v>6998044</v>
+        <v>6998005</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5679,7 +5670,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5689,12 +5680,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5709,22 +5700,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122824798</v>
+        <v>122824138</v>
       </c>
       <c r="B46" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5737,37 +5728,46 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528929</v>
+        <v>528887</v>
       </c>
       <c r="R46" t="n">
-        <v>6998043</v>
+        <v>6998044</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5826,12 +5826,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122825093</v>
+        <v>122823666</v>
       </c>
       <c r="B3" t="n">
-        <v>91519</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,38 +813,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528967</v>
+        <v>528890</v>
       </c>
       <c r="R3" t="n">
-        <v>6998079</v>
+        <v>6998089</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,24 +879,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,19 +901,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122824729</v>
+        <v>122823389</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -951,20 +946,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528904</v>
+        <v>528893</v>
       </c>
       <c r="R4" t="n">
-        <v>6998036</v>
+        <v>6998121</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1007,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,19 +1027,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122823605</v>
+        <v>122825157</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1075,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528887</v>
+        <v>528946</v>
       </c>
       <c r="R5" t="n">
-        <v>6998073</v>
+        <v>6998089</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,24 +1112,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,22 +1129,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122825263</v>
+        <v>122823640</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,39 +1157,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528938</v>
+        <v>528890</v>
       </c>
       <c r="R6" t="n">
-        <v>6998101</v>
+        <v>6998093</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,11 +1217,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122823389</v>
+        <v>122823616</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79807</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,50 +1255,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528893</v>
+        <v>528903</v>
       </c>
       <c r="R7" t="n">
-        <v>6998121</v>
+        <v>6998106</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1348,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,12 +1328,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,22 +1348,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122824716</v>
+        <v>122824517</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1406,21 +1376,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1430,13 +1400,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528980</v>
+        <v>528878</v>
       </c>
       <c r="R8" t="n">
-        <v>6998018</v>
+        <v>6997997</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,9 +1433,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,22 +1465,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122824296</v>
+        <v>122825059</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>77699</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,39 +1493,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528849</v>
+        <v>528960</v>
       </c>
       <c r="R9" t="n">
-        <v>6998016</v>
+        <v>6998066</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,14 +1550,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,22 +1582,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122823666</v>
+        <v>122824645</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>78503</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,39 +1610,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528890</v>
+        <v>528897</v>
       </c>
       <c r="R10" t="n">
-        <v>6998089</v>
+        <v>6998014</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1682,14 +1667,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,22 +1699,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122825059</v>
+        <v>122823943</v>
       </c>
       <c r="B11" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1732,34 +1727,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528960</v>
+        <v>528895</v>
       </c>
       <c r="R11" t="n">
-        <v>6998066</v>
+        <v>6998055</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,24 +1789,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,22 +1806,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122823640</v>
+        <v>122824504</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,34 +1834,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528890</v>
+        <v>528884</v>
       </c>
       <c r="R12" t="n">
-        <v>6998093</v>
+        <v>6997998</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1935,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122823780</v>
+        <v>122825093</v>
       </c>
       <c r="B13" t="n">
-        <v>79848</v>
+        <v>91519</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,25 +1941,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1975,10 +1969,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528879</v>
+        <v>528967</v>
       </c>
       <c r="R13" t="n">
-        <v>6998066</v>
+        <v>6998079</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2008,9 +2002,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2025,22 +2034,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122823959</v>
+        <v>122824883</v>
       </c>
       <c r="B14" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,34 +2062,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528918</v>
+        <v>528973</v>
       </c>
       <c r="R14" t="n">
-        <v>6998048</v>
+        <v>6998038</v>
       </c>
       <c r="S14" t="n">
         <v>7</v>
@@ -2112,7 +2130,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2122,12 +2140,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122825192</v>
+        <v>122824915</v>
       </c>
       <c r="B15" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2170,21 +2188,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2194,10 +2212,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528946</v>
+        <v>528964</v>
       </c>
       <c r="R15" t="n">
-        <v>6998089</v>
+        <v>6998032</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2227,9 +2245,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2244,22 +2277,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122824996</v>
+        <v>122823959</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,21 +2305,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2296,13 +2329,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528952</v>
+        <v>528918</v>
       </c>
       <c r="R16" t="n">
-        <v>6998039</v>
+        <v>6998048</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2331,7 +2364,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,12 +2374,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande glasbjörk med savflöde</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2361,22 +2394,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122823308</v>
+        <v>122824729</v>
       </c>
       <c r="B17" t="n">
-        <v>78502</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2389,21 +2422,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2416,10 +2449,10 @@
         <v>528904</v>
       </c>
       <c r="R17" t="n">
-        <v>6998141</v>
+        <v>6998036</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2448,7 +2481,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2458,12 +2491,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122823943</v>
+        <v>122824871</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>79751</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2502,46 +2535,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528895</v>
+        <v>528956</v>
       </c>
       <c r="R18" t="n">
-        <v>6998055</v>
+        <v>6998028</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2568,9 +2596,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2585,12 +2628,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2714,10 +2757,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122823616</v>
+        <v>122823542</v>
       </c>
       <c r="B20" t="n">
-        <v>79807</v>
+        <v>78503</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2726,25 +2769,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2754,13 +2797,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528903</v>
+        <v>528881</v>
       </c>
       <c r="R20" t="n">
-        <v>6998106</v>
+        <v>6998117</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2789,7 +2832,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2799,12 +2842,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2831,10 +2874,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122823876</v>
+        <v>122824314</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2847,46 +2890,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528897</v>
+        <v>528828</v>
       </c>
       <c r="R21" t="n">
-        <v>6998064</v>
+        <v>6998005</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2915,7 +2949,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2925,12 +2959,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal senvuxen granskog</t>
+          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2945,22 +2979,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122824689</v>
+        <v>122824159</v>
       </c>
       <c r="B22" t="n">
-        <v>78411</v>
+        <v>77699</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2973,21 +3007,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2997,10 +3031,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528901</v>
+        <v>528887</v>
       </c>
       <c r="R22" t="n">
-        <v>6998033</v>
+        <v>6998044</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3032,7 +3066,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3042,12 +3076,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,10 +3108,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122823224</v>
+        <v>122824139</v>
       </c>
       <c r="B23" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3086,25 +3120,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3114,13 +3148,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528911</v>
+        <v>528870</v>
       </c>
       <c r="R23" t="n">
-        <v>6998157</v>
+        <v>6997994</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3149,7 +3183,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3159,12 +3193,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3179,22 +3208,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122823542</v>
+        <v>122824689</v>
       </c>
       <c r="B24" t="n">
-        <v>78503</v>
+        <v>78411</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3207,21 +3236,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3231,13 +3260,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528881</v>
+        <v>528901</v>
       </c>
       <c r="R24" t="n">
-        <v>6998117</v>
+        <v>6998033</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3266,7 +3295,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3276,12 +3305,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3308,10 +3337,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122824517</v>
+        <v>122824608</v>
       </c>
       <c r="B25" t="n">
-        <v>78503</v>
+        <v>56680</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3324,37 +3353,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528878</v>
+        <v>528928</v>
       </c>
       <c r="R25" t="n">
-        <v>6997997</v>
+        <v>6998035</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3381,24 +3419,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3413,22 +3436,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122823789</v>
+        <v>122823935</v>
       </c>
       <c r="B26" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3441,21 +3464,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3465,13 +3488,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528910</v>
+        <v>528934</v>
       </c>
       <c r="R26" t="n">
-        <v>6998072</v>
+        <v>6998051</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3500,7 +3523,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3510,12 +3533,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På sälglåga i gammal granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3530,22 +3553,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122823534</v>
+        <v>122823876</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3558,27 +3581,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3587,10 +3614,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528883</v>
+        <v>528897</v>
       </c>
       <c r="R27" t="n">
-        <v>6998125</v>
+        <v>6998064</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3620,14 +3647,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gamla granar i gammal senvuxen granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3642,22 +3679,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122825055</v>
+        <v>122825263</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3670,37 +3707,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529003</v>
+        <v>528938</v>
       </c>
       <c r="R28" t="n">
-        <v>6998021</v>
+        <v>6998101</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3727,24 +3769,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3759,19 +3791,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122823653</v>
+        <v>122824114</v>
       </c>
       <c r="B29" t="n">
         <v>74863</v>
@@ -3811,10 +3843,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528898</v>
+        <v>528886</v>
       </c>
       <c r="R29" t="n">
-        <v>6998091</v>
+        <v>6998049</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3846,7 +3878,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3856,7 +3888,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -3888,10 +3920,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122824871</v>
+        <v>122824294</v>
       </c>
       <c r="B30" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3900,25 +3932,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3928,13 +3960,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528956</v>
+        <v>528874</v>
       </c>
       <c r="R30" t="n">
-        <v>6998028</v>
+        <v>6998038</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3963,7 +3995,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3973,12 +4005,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På asp i gammal granskog</t>
+          <t>På gammal tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4005,10 +4037,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122823776</v>
+        <v>122824296</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4021,27 +4053,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4050,10 +4082,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528879</v>
+        <v>528849</v>
       </c>
       <c r="R31" t="n">
-        <v>6998065</v>
+        <v>6998016</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4086,6 +4118,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4112,10 +4149,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122824203</v>
+        <v>122823789</v>
       </c>
       <c r="B32" t="n">
-        <v>56688</v>
+        <v>79848</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4124,43 +4161,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528874</v>
+        <v>528910</v>
       </c>
       <c r="R32" t="n">
-        <v>6998038</v>
+        <v>6998072</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4192,7 +4224,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4202,12 +4234,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Rikligt med spillning under tall</t>
+          <t>På sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4234,10 +4266,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122824608</v>
+        <v>122823780</v>
       </c>
       <c r="B33" t="n">
-        <v>56680</v>
+        <v>79848</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4250,43 +4282,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528928</v>
+        <v>528879</v>
       </c>
       <c r="R33" t="n">
-        <v>6998035</v>
+        <v>6998066</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4345,10 +4368,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122824294</v>
+        <v>122823605</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4361,21 +4384,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4385,10 +4408,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528874</v>
+        <v>528887</v>
       </c>
       <c r="R34" t="n">
-        <v>6998038</v>
+        <v>6998073</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4420,7 +4443,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4430,12 +4453,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal tall</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4450,19 +4473,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122824915</v>
+        <v>122824996</v>
       </c>
       <c r="B35" t="n">
         <v>79847</v>
@@ -4502,13 +4525,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528964</v>
+        <v>528952</v>
       </c>
       <c r="R35" t="n">
-        <v>6998032</v>
+        <v>6998039</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4537,7 +4560,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4547,12 +4570,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På asp i gammal barrblandskog</t>
+          <t>På bark på stam av levande glasbjörk med savflöde</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4579,10 +4602,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122824504</v>
+        <v>122823776</v>
       </c>
       <c r="B36" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4595,31 +4618,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4628,10 +4647,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528884</v>
+        <v>528879</v>
       </c>
       <c r="R36" t="n">
-        <v>6997998</v>
+        <v>6998065</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4690,10 +4709,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122823935</v>
+        <v>122823308</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4706,21 +4725,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4730,13 +4749,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528934</v>
+        <v>528904</v>
       </c>
       <c r="R37" t="n">
-        <v>6998051</v>
+        <v>6998141</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4765,7 +4784,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4775,12 +4794,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4795,22 +4814,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122824645</v>
+        <v>122823534</v>
       </c>
       <c r="B38" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4823,34 +4842,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528897</v>
+        <v>528883</v>
       </c>
       <c r="R38" t="n">
-        <v>6998014</v>
+        <v>6998125</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4880,24 +4904,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4912,22 +4926,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122825157</v>
+        <v>122823653</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4940,21 +4954,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4964,10 +4978,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528946</v>
+        <v>528898</v>
       </c>
       <c r="R39" t="n">
-        <v>6998089</v>
+        <v>6998091</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4997,9 +5011,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5014,19 +5043,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122824669</v>
+        <v>122824940</v>
       </c>
       <c r="B40" t="n">
         <v>79847</v>
@@ -5059,20 +5088,29 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528962</v>
+        <v>528993</v>
       </c>
       <c r="R40" t="n">
-        <v>6998022</v>
+        <v>6998013</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5099,9 +5137,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5116,22 +5164,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122824114</v>
+        <v>122824775</v>
       </c>
       <c r="B41" t="n">
-        <v>74863</v>
+        <v>90917</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5140,25 +5188,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5168,13 +5216,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528886</v>
+        <v>528928</v>
       </c>
       <c r="R41" t="n">
-        <v>6998049</v>
+        <v>6998037</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5203,7 +5251,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5213,12 +5261,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal död stående gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5245,7 +5293,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122824940</v>
+        <v>122824716</v>
       </c>
       <c r="B42" t="n">
         <v>79847</v>
@@ -5278,29 +5326,20 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528993</v>
+        <v>528980</v>
       </c>
       <c r="R42" t="n">
-        <v>6998013</v>
+        <v>6998018</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5327,19 +5366,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:26</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5354,19 +5383,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122824139</v>
+        <v>122824928</v>
       </c>
       <c r="B43" t="n">
         <v>79847</v>
@@ -5406,13 +5435,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528870</v>
+        <v>528989</v>
       </c>
       <c r="R43" t="n">
-        <v>6997994</v>
+        <v>6998039</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5439,19 +5468,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5466,22 +5485,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122824798</v>
+        <v>122823224</v>
       </c>
       <c r="B44" t="n">
-        <v>74863</v>
+        <v>79751</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5490,25 +5509,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5518,13 +5537,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528929</v>
+        <v>528911</v>
       </c>
       <c r="R44" t="n">
-        <v>6998043</v>
+        <v>6998157</v>
       </c>
       <c r="S44" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5553,7 +5572,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5563,12 +5582,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5583,22 +5602,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122824314</v>
+        <v>122824617</v>
       </c>
       <c r="B45" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5611,21 +5630,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5635,13 +5654,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528828</v>
+        <v>528897</v>
       </c>
       <c r="R45" t="n">
-        <v>6998005</v>
+        <v>6998014</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5670,7 +5689,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5680,12 +5699,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5700,12 +5719,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5838,10 +5857,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122824159</v>
+        <v>122824798</v>
       </c>
       <c r="B47" t="n">
-        <v>77699</v>
+        <v>74863</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5854,21 +5873,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5878,13 +5897,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528887</v>
+        <v>528929</v>
       </c>
       <c r="R47" t="n">
-        <v>6998044</v>
+        <v>6998043</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5913,7 +5932,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5923,12 +5942,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5943,19 +5962,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122824883</v>
+        <v>122825055</v>
       </c>
       <c r="B48" t="n">
         <v>79847</v>
@@ -5988,26 +6007,17 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528973</v>
+        <v>529003</v>
       </c>
       <c r="R48" t="n">
-        <v>6998038</v>
+        <v>6998021</v>
       </c>
       <c r="S48" t="n">
         <v>7</v>
@@ -6039,7 +6049,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6049,12 +6059,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På död sälg (kort)</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6081,10 +6091,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122824617</v>
+        <v>122824669</v>
       </c>
       <c r="B49" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6097,21 +6107,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6121,10 +6131,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528897</v>
+        <v>528962</v>
       </c>
       <c r="R49" t="n">
-        <v>6998014</v>
+        <v>6998022</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6154,24 +6164,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6186,22 +6181,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122824775</v>
+        <v>122825192</v>
       </c>
       <c r="B50" t="n">
-        <v>90917</v>
+        <v>79848</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6210,25 +6205,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6238,13 +6233,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528928</v>
+        <v>528946</v>
       </c>
       <c r="R50" t="n">
-        <v>6998037</v>
+        <v>6998089</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6271,24 +6266,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gammal död stående gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6303,22 +6283,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122824928</v>
+        <v>122824203</v>
       </c>
       <c r="B51" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6327,38 +6307,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528989</v>
+        <v>528874</v>
       </c>
       <c r="R51" t="n">
-        <v>6998039</v>
+        <v>6998038</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6388,9 +6373,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Rikligt med spillning under tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6405,12 +6405,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -2991,10 +2991,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122824159</v>
+        <v>122824139</v>
       </c>
       <c r="B22" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3007,21 +3007,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3031,13 +3031,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528887</v>
+        <v>528870</v>
       </c>
       <c r="R22" t="n">
-        <v>6998044</v>
+        <v>6997994</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3076,12 +3076,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,22 +3091,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122824139</v>
+        <v>122824159</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3124,21 +3119,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3148,13 +3143,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528870</v>
+        <v>528887</v>
       </c>
       <c r="R23" t="n">
-        <v>6997994</v>
+        <v>6998044</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3183,7 +3178,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3193,7 +3188,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,12 +3208,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -4037,10 +4037,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122824296</v>
+        <v>122823789</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4053,39 +4053,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528849</v>
+        <v>528910</v>
       </c>
       <c r="R31" t="n">
-        <v>6998016</v>
+        <v>6998072</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4115,14 +4110,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4137,19 +4142,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122823789</v>
+        <v>122823780</v>
       </c>
       <c r="B32" t="n">
         <v>79848</v>
@@ -4189,10 +4194,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528910</v>
+        <v>528879</v>
       </c>
       <c r="R32" t="n">
-        <v>6998072</v>
+        <v>6998066</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4222,24 +4227,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4254,22 +4244,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122823780</v>
+        <v>122824296</v>
       </c>
       <c r="B33" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4282,34 +4272,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528879</v>
+        <v>528849</v>
       </c>
       <c r="R33" t="n">
-        <v>6998066</v>
+        <v>6998016</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4342,6 +4337,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4368,10 +4368,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122823605</v>
+        <v>122823308</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4384,21 +4384,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4408,13 +4408,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528887</v>
+        <v>528904</v>
       </c>
       <c r="R34" t="n">
-        <v>6998073</v>
+        <v>6998141</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4473,22 +4473,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122824996</v>
+        <v>122823534</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4501,37 +4501,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528952</v>
+        <v>528883</v>
       </c>
       <c r="R35" t="n">
-        <v>6998039</v>
+        <v>6998125</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4558,24 +4563,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark på stam av levande glasbjörk med savflöde</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4590,19 +4585,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122823776</v>
+        <v>122823605</v>
       </c>
       <c r="B36" t="n">
         <v>79847</v>
@@ -4636,21 +4631,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528879</v>
+        <v>528887</v>
       </c>
       <c r="R36" t="n">
-        <v>6998065</v>
+        <v>6998073</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4680,9 +4670,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4697,22 +4702,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122823308</v>
+        <v>122824996</v>
       </c>
       <c r="B37" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4725,21 +4730,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4749,10 +4754,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528904</v>
+        <v>528952</v>
       </c>
       <c r="R37" t="n">
-        <v>6998141</v>
+        <v>6998039</v>
       </c>
       <c r="S37" t="n">
         <v>6</v>
@@ -4784,7 +4789,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4794,12 +4799,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>På bark på stam av levande glasbjörk med savflöde</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4826,10 +4831,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122823534</v>
+        <v>122823776</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4842,27 +4847,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4871,10 +4876,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528883</v>
+        <v>528879</v>
       </c>
       <c r="R38" t="n">
-        <v>6998125</v>
+        <v>6998065</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4907,11 +4912,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5497,10 +5497,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122823224</v>
+        <v>122825055</v>
       </c>
       <c r="B44" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5509,25 +5509,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5537,13 +5537,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528911</v>
+        <v>529003</v>
       </c>
       <c r="R44" t="n">
-        <v>6998157</v>
+        <v>6998021</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5602,22 +5602,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122824617</v>
+        <v>122824669</v>
       </c>
       <c r="B45" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5630,21 +5630,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5654,10 +5654,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528897</v>
+        <v>528962</v>
       </c>
       <c r="R45" t="n">
-        <v>6998014</v>
+        <v>6998022</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5687,24 +5687,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5719,22 +5704,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122824138</v>
+        <v>122823224</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>79751</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5743,47 +5728,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528887</v>
+        <v>528911</v>
       </c>
       <c r="R46" t="n">
-        <v>6998044</v>
+        <v>6998157</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5815,7 +5791,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5825,12 +5801,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5857,10 +5833,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122824798</v>
+        <v>122824617</v>
       </c>
       <c r="B47" t="n">
-        <v>74863</v>
+        <v>78502</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5873,21 +5849,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5897,13 +5873,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528929</v>
+        <v>528897</v>
       </c>
       <c r="R47" t="n">
-        <v>6998043</v>
+        <v>6998014</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5932,7 +5908,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5942,12 +5918,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5962,22 +5938,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122825055</v>
+        <v>122824138</v>
       </c>
       <c r="B48" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5990,37 +5966,46 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>529003</v>
+        <v>528887</v>
       </c>
       <c r="R48" t="n">
-        <v>6998021</v>
+        <v>6998044</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6049,7 +6034,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6059,12 +6044,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6079,22 +6064,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122824669</v>
+        <v>122824798</v>
       </c>
       <c r="B49" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6107,21 +6092,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6131,13 +6116,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528962</v>
+        <v>528929</v>
       </c>
       <c r="R49" t="n">
-        <v>6998022</v>
+        <v>6998043</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6164,9 +6149,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6181,12 +6181,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -4037,10 +4037,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122823789</v>
+        <v>122824296</v>
       </c>
       <c r="B31" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4053,34 +4053,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528910</v>
+        <v>528849</v>
       </c>
       <c r="R31" t="n">
-        <v>6998072</v>
+        <v>6998016</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4110,24 +4115,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På sälglåga i gammal granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4142,19 +4137,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122823780</v>
+        <v>122823789</v>
       </c>
       <c r="B32" t="n">
         <v>79848</v>
@@ -4194,10 +4189,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528879</v>
+        <v>528910</v>
       </c>
       <c r="R32" t="n">
-        <v>6998066</v>
+        <v>6998072</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4227,9 +4222,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4244,22 +4254,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122824296</v>
+        <v>122823780</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4272,39 +4282,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528849</v>
+        <v>528879</v>
       </c>
       <c r="R33" t="n">
-        <v>6998016</v>
+        <v>6998066</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4337,11 +4342,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4485,10 +4485,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122823534</v>
+        <v>122823605</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4501,39 +4501,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528883</v>
+        <v>528887</v>
       </c>
       <c r="R35" t="n">
-        <v>6998125</v>
+        <v>6998073</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4563,14 +4558,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4585,19 +4590,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122823605</v>
+        <v>122824996</v>
       </c>
       <c r="B36" t="n">
         <v>79847</v>
@@ -4637,13 +4642,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528887</v>
+        <v>528952</v>
       </c>
       <c r="R36" t="n">
-        <v>6998073</v>
+        <v>6998039</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4672,7 +4677,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4682,12 +4687,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På bark på stam av levande glasbjörk med savflöde</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4702,19 +4707,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122824996</v>
+        <v>122823776</v>
       </c>
       <c r="B37" t="n">
         <v>79847</v>
@@ -4748,19 +4753,24 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528952</v>
+        <v>528879</v>
       </c>
       <c r="R37" t="n">
-        <v>6998039</v>
+        <v>6998065</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4787,24 +4797,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande glasbjörk med savflöde</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4819,22 +4814,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122823776</v>
+        <v>122823534</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4847,27 +4842,27 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4876,10 +4871,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528879</v>
+        <v>528883</v>
       </c>
       <c r="R38" t="n">
-        <v>6998065</v>
+        <v>6998125</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4912,6 +4907,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122823666</v>
+        <v>122824883</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,27 +817,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,13 +850,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528890</v>
+        <v>528973</v>
       </c>
       <c r="R3" t="n">
-        <v>6998089</v>
+        <v>6998038</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,14 +883,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,22 +915,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122823389</v>
+        <v>122823789</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,46 +943,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528893</v>
+        <v>528910</v>
       </c>
       <c r="R4" t="n">
-        <v>6998121</v>
+        <v>6998072</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -997,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,12 +1012,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,22 +1032,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122825157</v>
+        <v>122824608</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,34 +1060,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528946</v>
+        <v>528928</v>
       </c>
       <c r="R5" t="n">
-        <v>6998089</v>
+        <v>6998035</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1141,10 +1155,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122823640</v>
+        <v>122824294</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,21 +1171,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1181,10 +1195,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528890</v>
+        <v>528874</v>
       </c>
       <c r="R6" t="n">
-        <v>6998093</v>
+        <v>6998038</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1214,9 +1228,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,22 +1260,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122823616</v>
+        <v>122824159</v>
       </c>
       <c r="B7" t="n">
-        <v>79807</v>
+        <v>77699</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,25 +1284,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>228579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1283,10 +1312,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528903</v>
+        <v>528887</v>
       </c>
       <c r="R7" t="n">
-        <v>6998106</v>
+        <v>6998044</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,12 +1357,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122824517</v>
+        <v>122823605</v>
       </c>
       <c r="B8" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,21 +1405,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1400,13 +1429,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528878</v>
+        <v>528887</v>
       </c>
       <c r="R8" t="n">
-        <v>6997997</v>
+        <v>6998073</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,7 +1464,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1445,12 +1474,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,22 +1494,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122825059</v>
+        <v>122824203</v>
       </c>
       <c r="B9" t="n">
-        <v>77699</v>
+        <v>56688</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,38 +1518,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528960</v>
+        <v>528874</v>
       </c>
       <c r="R9" t="n">
-        <v>6998066</v>
+        <v>6998038</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,12 +1596,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>Rikligt med spillning under tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122824645</v>
+        <v>122824617</v>
       </c>
       <c r="B10" t="n">
-        <v>78503</v>
+        <v>78502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,21 +1644,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1711,7 +1745,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122823943</v>
+        <v>122824915</v>
       </c>
       <c r="B11" t="n">
         <v>79847</v>
@@ -1745,21 +1779,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528895</v>
+        <v>528964</v>
       </c>
       <c r="R11" t="n">
-        <v>6998055</v>
+        <v>6998032</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,9 +1818,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,22 +1850,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122824504</v>
+        <v>122823640</v>
       </c>
       <c r="B12" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,43 +1878,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528884</v>
+        <v>528890</v>
       </c>
       <c r="R12" t="n">
-        <v>6997998</v>
+        <v>6998093</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2046,10 +2081,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122824883</v>
+        <v>122825192</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,46 +2097,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528973</v>
+        <v>528946</v>
       </c>
       <c r="R14" t="n">
-        <v>6998038</v>
+        <v>6998089</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2128,24 +2154,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2160,22 +2171,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122824915</v>
+        <v>122823308</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,21 +2199,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2212,13 +2223,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528964</v>
+        <v>528904</v>
       </c>
       <c r="R15" t="n">
-        <v>6998032</v>
+        <v>6998141</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2247,7 +2258,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2257,12 +2268,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På asp i gammal barrblandskog</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,10 +2300,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122823959</v>
+        <v>122823653</v>
       </c>
       <c r="B16" t="n">
-        <v>79848</v>
+        <v>74863</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2305,21 +2316,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2329,13 +2340,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528918</v>
+        <v>528898</v>
       </c>
       <c r="R16" t="n">
-        <v>6998048</v>
+        <v>6998091</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2364,7 +2375,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2374,12 +2385,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2394,22 +2405,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122824729</v>
+        <v>122823780</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,21 +2433,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2446,10 +2457,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528904</v>
+        <v>528879</v>
       </c>
       <c r="R17" t="n">
-        <v>6998036</v>
+        <v>6998066</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2479,24 +2490,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,12 +2507,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2640,10 +2636,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122824419</v>
+        <v>122824940</v>
       </c>
       <c r="B19" t="n">
-        <v>79384</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2656,37 +2652,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528853</v>
+        <v>528993</v>
       </c>
       <c r="R19" t="n">
-        <v>6998012</v>
+        <v>6998013</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2715,7 +2720,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2725,12 +2730,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På ved på gammal tallhögstubbe</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,22 +2745,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122823542</v>
+        <v>122823876</v>
       </c>
       <c r="B20" t="n">
-        <v>78503</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2773,37 +2773,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528881</v>
+        <v>528897</v>
       </c>
       <c r="R20" t="n">
-        <v>6998117</v>
+        <v>6998064</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2832,7 +2841,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2842,12 +2851,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>På gamla granar i gammal senvuxen granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2874,10 +2883,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122824314</v>
+        <v>122825263</v>
       </c>
       <c r="B21" t="n">
-        <v>78503</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2890,37 +2899,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528828</v>
+        <v>528938</v>
       </c>
       <c r="R21" t="n">
-        <v>6998005</v>
+        <v>6998101</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2947,24 +2961,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,22 +2983,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122824139</v>
+        <v>122824314</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3007,21 +3011,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3031,13 +3035,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528870</v>
+        <v>528828</v>
       </c>
       <c r="R22" t="n">
-        <v>6997994</v>
+        <v>6998005</v>
       </c>
       <c r="S22" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3066,7 +3070,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3076,7 +3080,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3103,10 +3112,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122824159</v>
+        <v>122825157</v>
       </c>
       <c r="B23" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3119,21 +3128,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3143,10 +3152,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528887</v>
+        <v>528946</v>
       </c>
       <c r="R23" t="n">
-        <v>6998044</v>
+        <v>6998089</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3176,24 +3185,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,22 +3202,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122824689</v>
+        <v>122823224</v>
       </c>
       <c r="B24" t="n">
-        <v>78411</v>
+        <v>79751</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3232,25 +3226,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3260,10 +3254,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528901</v>
+        <v>528911</v>
       </c>
       <c r="R24" t="n">
-        <v>6998033</v>
+        <v>6998157</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3295,7 +3289,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3305,12 +3299,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3337,10 +3331,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122824608</v>
+        <v>122824419</v>
       </c>
       <c r="B25" t="n">
-        <v>56680</v>
+        <v>79384</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3353,43 +3347,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528928</v>
+        <v>528853</v>
       </c>
       <c r="R25" t="n">
-        <v>6998035</v>
+        <v>6998012</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3419,9 +3404,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3436,22 +3436,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122823935</v>
+        <v>122823534</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3464,37 +3464,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528934</v>
+        <v>528883</v>
       </c>
       <c r="R26" t="n">
-        <v>6998051</v>
+        <v>6998125</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3521,24 +3526,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3553,22 +3548,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122823876</v>
+        <v>122824928</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3581,43 +3576,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528897</v>
+        <v>528989</v>
       </c>
       <c r="R27" t="n">
-        <v>6998064</v>
+        <v>6998039</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3647,24 +3633,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal senvuxen granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3679,22 +3650,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122825263</v>
+        <v>122824996</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3707,42 +3678,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528938</v>
+        <v>528952</v>
       </c>
       <c r="R28" t="n">
-        <v>6998101</v>
+        <v>6998039</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3769,14 +3735,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På bark på stam av levande glasbjörk med savflöde</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3791,22 +3767,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122824114</v>
+        <v>122823959</v>
       </c>
       <c r="B29" t="n">
-        <v>74863</v>
+        <v>79848</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3819,21 +3795,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3843,13 +3819,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528886</v>
+        <v>528918</v>
       </c>
       <c r="R29" t="n">
-        <v>6998049</v>
+        <v>6998048</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3878,7 +3854,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3888,12 +3864,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3908,22 +3884,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122824294</v>
+        <v>122823542</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>78503</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3936,21 +3912,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3960,13 +3936,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528874</v>
+        <v>528881</v>
       </c>
       <c r="R30" t="n">
-        <v>6998038</v>
+        <v>6998117</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3995,7 +3971,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4005,12 +3981,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal tall</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4037,10 +4013,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122824296</v>
+        <v>122825055</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4053,42 +4029,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528849</v>
+        <v>529003</v>
       </c>
       <c r="R31" t="n">
-        <v>6998016</v>
+        <v>6998021</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4115,14 +4086,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4137,22 +4118,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122823789</v>
+        <v>122824669</v>
       </c>
       <c r="B32" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4165,21 +4146,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4189,10 +4170,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528910</v>
+        <v>528962</v>
       </c>
       <c r="R32" t="n">
-        <v>6998072</v>
+        <v>6998022</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4222,24 +4203,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4254,22 +4220,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122823780</v>
+        <v>122824138</v>
       </c>
       <c r="B33" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4282,34 +4248,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528879</v>
+        <v>528887</v>
       </c>
       <c r="R33" t="n">
-        <v>6998066</v>
+        <v>6998044</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4339,9 +4314,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4356,22 +4346,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122823308</v>
+        <v>122824296</v>
       </c>
       <c r="B34" t="n">
-        <v>78502</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4384,37 +4374,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528904</v>
+        <v>528849</v>
       </c>
       <c r="R34" t="n">
-        <v>6998141</v>
+        <v>6998016</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4441,24 +4436,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4473,22 +4458,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122823605</v>
+        <v>122825059</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>77699</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4501,21 +4486,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4525,10 +4510,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528887</v>
+        <v>528960</v>
       </c>
       <c r="R35" t="n">
-        <v>6998073</v>
+        <v>6998066</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4560,7 +4545,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4570,12 +4555,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4590,22 +4575,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122824996</v>
+        <v>122824517</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4618,21 +4603,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4642,13 +4627,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528952</v>
+        <v>528878</v>
       </c>
       <c r="R36" t="n">
-        <v>6998039</v>
+        <v>6997997</v>
       </c>
       <c r="S36" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4677,7 +4662,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4687,12 +4672,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På bark på stam av levande glasbjörk med savflöde</t>
+          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4719,10 +4704,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122823776</v>
+        <v>122824504</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4735,27 +4720,31 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4764,10 +4753,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528879</v>
+        <v>528884</v>
       </c>
       <c r="R37" t="n">
-        <v>6998065</v>
+        <v>6997998</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4826,10 +4815,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122823534</v>
+        <v>122824729</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4842,39 +4831,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528883</v>
+        <v>528904</v>
       </c>
       <c r="R38" t="n">
-        <v>6998125</v>
+        <v>6998036</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4904,14 +4888,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4926,19 +4920,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122823653</v>
+        <v>122824798</v>
       </c>
       <c r="B39" t="n">
         <v>74863</v>
@@ -4978,13 +4972,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528898</v>
+        <v>528929</v>
       </c>
       <c r="R39" t="n">
-        <v>6998091</v>
+        <v>6998043</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5013,7 +5007,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5023,12 +5017,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5043,19 +5037,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122824940</v>
+        <v>122824139</v>
       </c>
       <c r="B40" t="n">
         <v>79847</v>
@@ -5088,29 +5082,20 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528993</v>
+        <v>528870</v>
       </c>
       <c r="R40" t="n">
-        <v>6998013</v>
+        <v>6997994</v>
       </c>
       <c r="S40" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5139,7 +5124,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5149,7 +5134,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5176,10 +5161,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122824775</v>
+        <v>122823776</v>
       </c>
       <c r="B41" t="n">
-        <v>90917</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5188,41 +5173,46 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528928</v>
+        <v>528879</v>
       </c>
       <c r="R41" t="n">
-        <v>6998037</v>
+        <v>6998065</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5249,24 +5239,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På gammal död stående gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5281,19 +5256,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122824716</v>
+        <v>122823943</v>
       </c>
       <c r="B42" t="n">
         <v>79847</v>
@@ -5327,16 +5302,21 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528980</v>
+        <v>528895</v>
       </c>
       <c r="R42" t="n">
-        <v>6998018</v>
+        <v>6998055</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5395,10 +5375,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122824928</v>
+        <v>122824114</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>74863</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5411,21 +5391,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5435,10 +5415,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528989</v>
+        <v>528886</v>
       </c>
       <c r="R43" t="n">
-        <v>6998039</v>
+        <v>6998049</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5468,9 +5448,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5485,22 +5480,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122825055</v>
+        <v>122823389</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5513,37 +5508,46 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>529003</v>
+        <v>528893</v>
       </c>
       <c r="R44" t="n">
-        <v>6998021</v>
+        <v>6998121</v>
       </c>
       <c r="S44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5572,7 +5576,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5582,7 +5586,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -5614,7 +5618,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122824669</v>
+        <v>122824716</v>
       </c>
       <c r="B45" t="n">
         <v>79847</v>
@@ -5654,10 +5658,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528962</v>
+        <v>528980</v>
       </c>
       <c r="R45" t="n">
-        <v>6998022</v>
+        <v>6998018</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5716,10 +5720,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122823224</v>
+        <v>122824689</v>
       </c>
       <c r="B46" t="n">
-        <v>79751</v>
+        <v>78411</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5728,25 +5732,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5756,10 +5760,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528911</v>
+        <v>528901</v>
       </c>
       <c r="R46" t="n">
-        <v>6998157</v>
+        <v>6998033</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5791,7 +5795,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5801,12 +5805,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5833,10 +5837,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122824617</v>
+        <v>122824645</v>
       </c>
       <c r="B47" t="n">
-        <v>78502</v>
+        <v>78503</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5849,21 +5853,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5950,10 +5954,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122824138</v>
+        <v>122823616</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>79807</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5962,47 +5966,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528887</v>
+        <v>528903</v>
       </c>
       <c r="R48" t="n">
-        <v>6998044</v>
+        <v>6998106</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6034,7 +6029,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6044,12 +6039,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6076,10 +6071,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122824798</v>
+        <v>122823666</v>
       </c>
       <c r="B49" t="n">
-        <v>74863</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6092,37 +6087,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528929</v>
+        <v>528890</v>
       </c>
       <c r="R49" t="n">
-        <v>6998043</v>
+        <v>6998089</v>
       </c>
       <c r="S49" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6149,24 +6149,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6181,22 +6171,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122825192</v>
+        <v>122823935</v>
       </c>
       <c r="B50" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6209,21 +6199,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6233,13 +6223,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528946</v>
+        <v>528934</v>
       </c>
       <c r="R50" t="n">
-        <v>6998089</v>
+        <v>6998051</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6266,9 +6256,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6283,22 +6288,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122824203</v>
+        <v>122824775</v>
       </c>
       <c r="B51" t="n">
-        <v>56688</v>
+        <v>90917</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6311,42 +6316,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528874</v>
+        <v>528928</v>
       </c>
       <c r="R51" t="n">
-        <v>6998038</v>
+        <v>6998037</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Rikligt med spillning under tall</t>
+          <t>På gammal död stående gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122824883</v>
+        <v>122824915</v>
       </c>
       <c r="B3" t="n">
         <v>79847</v>
@@ -834,29 +834,20 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528973</v>
+        <v>528964</v>
       </c>
       <c r="R3" t="n">
-        <v>6998038</v>
+        <v>6998032</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På död sälg (kort)</t>
+          <t>På asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,22 +906,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122823789</v>
+        <v>122824871</v>
       </c>
       <c r="B4" t="n">
-        <v>79848</v>
+        <v>79751</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,25 +930,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,13 +958,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528910</v>
+        <v>528956</v>
       </c>
       <c r="R4" t="n">
-        <v>6998072</v>
+        <v>6998028</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På sälglåga i gammal granskog</t>
+          <t>På asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122824608</v>
+        <v>122823959</v>
       </c>
       <c r="B5" t="n">
-        <v>56680</v>
+        <v>79848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,46 +1051,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528928</v>
+        <v>528918</v>
       </c>
       <c r="R5" t="n">
-        <v>6998035</v>
+        <v>6998048</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,9 +1108,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,19 +1140,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122824294</v>
+        <v>122823876</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1188,17 +1185,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528874</v>
+        <v>528897</v>
       </c>
       <c r="R6" t="n">
-        <v>6998038</v>
+        <v>6998064</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1240,12 +1246,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gammal tall</t>
+          <t>På gamla granar i gammal senvuxen granskog</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122824159</v>
+        <v>122823780</v>
       </c>
       <c r="B7" t="n">
-        <v>77699</v>
+        <v>79848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1288,21 +1294,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1312,10 +1318,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528887</v>
+        <v>528879</v>
       </c>
       <c r="R7" t="n">
-        <v>6998044</v>
+        <v>6998066</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,24 +1351,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,22 +1368,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122823605</v>
+        <v>122823534</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,34 +1396,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528887</v>
+        <v>528883</v>
       </c>
       <c r="R8" t="n">
-        <v>6998073</v>
+        <v>6998125</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1462,24 +1458,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,22 +1480,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122824203</v>
+        <v>122823224</v>
       </c>
       <c r="B9" t="n">
-        <v>56688</v>
+        <v>79751</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,39 +1508,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>6456</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528874</v>
+        <v>528911</v>
       </c>
       <c r="R9" t="n">
-        <v>6998038</v>
+        <v>6998157</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1586,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,12 +1577,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt med spillning under tall</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,10 +1609,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122824617</v>
+        <v>122824996</v>
       </c>
       <c r="B10" t="n">
-        <v>78502</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1644,21 +1625,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,13 +1649,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528897</v>
+        <v>528952</v>
       </c>
       <c r="R10" t="n">
-        <v>6998014</v>
+        <v>6998039</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1703,7 +1684,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1713,12 +1694,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
+          <t>På bark på stam av levande glasbjörk med savflöde</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1726,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122824915</v>
+        <v>122823389</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1761,37 +1742,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528964</v>
+        <v>528893</v>
       </c>
       <c r="R11" t="n">
-        <v>6998032</v>
+        <v>6998121</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1820,7 +1810,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,12 +1820,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På asp i gammal barrblandskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,22 +1840,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122823640</v>
+        <v>122824517</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>78503</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,21 +1868,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1902,13 +1892,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528890</v>
+        <v>528878</v>
       </c>
       <c r="R12" t="n">
-        <v>6998093</v>
+        <v>6997997</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1935,9 +1925,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,22 +1957,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122825093</v>
+        <v>122825157</v>
       </c>
       <c r="B13" t="n">
-        <v>91519</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1976,25 +1981,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2004,10 +2009,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528967</v>
+        <v>528946</v>
       </c>
       <c r="R13" t="n">
-        <v>6998079</v>
+        <v>6998089</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2037,24 +2042,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,22 +2059,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122825192</v>
+        <v>122824617</v>
       </c>
       <c r="B14" t="n">
-        <v>79848</v>
+        <v>78502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2097,21 +2087,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2121,10 +2111,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528946</v>
+        <v>528897</v>
       </c>
       <c r="R14" t="n">
-        <v>6998089</v>
+        <v>6998014</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2154,9 +2144,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2171,22 +2176,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122823308</v>
+        <v>122823653</v>
       </c>
       <c r="B15" t="n">
-        <v>78502</v>
+        <v>74863</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2199,21 +2204,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,13 +2228,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528904</v>
+        <v>528898</v>
       </c>
       <c r="R15" t="n">
-        <v>6998141</v>
+        <v>6998091</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2258,7 +2263,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2268,12 +2273,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,7 +2305,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122823653</v>
+        <v>122824798</v>
       </c>
       <c r="B16" t="n">
         <v>74863</v>
@@ -2340,13 +2345,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528898</v>
+        <v>528929</v>
       </c>
       <c r="R16" t="n">
-        <v>6998091</v>
+        <v>6998043</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2375,7 +2380,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2385,12 +2390,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2405,22 +2410,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122823780</v>
+        <v>122824296</v>
       </c>
       <c r="B17" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2433,34 +2438,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528879</v>
+        <v>528849</v>
       </c>
       <c r="R17" t="n">
-        <v>6998066</v>
+        <v>6998016</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2493,6 +2503,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2519,10 +2534,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122824871</v>
+        <v>122824114</v>
       </c>
       <c r="B18" t="n">
-        <v>79751</v>
+        <v>74863</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,25 +2546,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2559,13 +2574,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528956</v>
+        <v>528886</v>
       </c>
       <c r="R18" t="n">
-        <v>6998028</v>
+        <v>6998049</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2594,7 +2609,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2604,12 +2619,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På asp i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2636,10 +2651,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122824940</v>
+        <v>122825192</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2652,46 +2667,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528993</v>
+        <v>528946</v>
       </c>
       <c r="R19" t="n">
-        <v>6998013</v>
+        <v>6998089</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2718,19 +2724,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2745,22 +2741,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122823876</v>
+        <v>122825059</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2773,43 +2769,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528897</v>
+        <v>528960</v>
       </c>
       <c r="R20" t="n">
-        <v>6998064</v>
+        <v>6998066</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2841,7 +2828,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2851,12 +2838,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal senvuxen granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3105,14 +3092,14 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122825157</v>
+        <v>122823943</v>
       </c>
       <c r="B23" t="n">
         <v>79847</v>
@@ -3146,16 +3133,21 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528946</v>
+        <v>528895</v>
       </c>
       <c r="R23" t="n">
-        <v>6998089</v>
+        <v>6998055</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3214,10 +3206,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122823224</v>
+        <v>122823935</v>
       </c>
       <c r="B24" t="n">
-        <v>79751</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3226,25 +3218,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3254,13 +3246,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528911</v>
+        <v>528934</v>
       </c>
       <c r="R24" t="n">
-        <v>6998157</v>
+        <v>6998051</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3289,7 +3281,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3299,12 +3291,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3319,22 +3311,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122824419</v>
+        <v>122823789</v>
       </c>
       <c r="B25" t="n">
-        <v>79384</v>
+        <v>79848</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3347,21 +3339,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3371,10 +3363,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528853</v>
+        <v>528910</v>
       </c>
       <c r="R25" t="n">
-        <v>6998012</v>
+        <v>6998072</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3406,7 +3398,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3416,12 +3408,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På ved på gammal tallhögstubbe</t>
+          <t>På sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3448,10 +3440,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122823534</v>
+        <v>122824608</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>56680</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3464,16 +3456,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3481,10 +3473,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3493,10 +3489,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528883</v>
+        <v>528928</v>
       </c>
       <c r="R26" t="n">
-        <v>6998125</v>
+        <v>6998035</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3529,11 +3525,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3560,7 +3551,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122824928</v>
+        <v>122824669</v>
       </c>
       <c r="B27" t="n">
         <v>79847</v>
@@ -3600,10 +3591,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528989</v>
+        <v>528962</v>
       </c>
       <c r="R27" t="n">
-        <v>6998039</v>
+        <v>6998022</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3662,7 +3653,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122824996</v>
+        <v>122824928</v>
       </c>
       <c r="B28" t="n">
         <v>79847</v>
@@ -3702,13 +3693,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528952</v>
+        <v>528989</v>
       </c>
       <c r="R28" t="n">
         <v>6998039</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3735,24 +3726,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande glasbjörk med savflöde</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3767,22 +3743,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122823959</v>
+        <v>122824294</v>
       </c>
       <c r="B29" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3795,21 +3771,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3819,13 +3795,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528918</v>
+        <v>528874</v>
       </c>
       <c r="R29" t="n">
-        <v>6998048</v>
+        <v>6998038</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3854,7 +3830,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3864,12 +3840,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På gammal tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3884,7 +3860,7 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -3896,10 +3872,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122823542</v>
+        <v>122823616</v>
       </c>
       <c r="B30" t="n">
-        <v>78503</v>
+        <v>79807</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3908,25 +3884,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3936,13 +3912,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528881</v>
+        <v>528903</v>
       </c>
       <c r="R30" t="n">
-        <v>6998117</v>
+        <v>6998106</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3971,7 +3947,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3981,12 +3957,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4013,10 +3989,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122825055</v>
+        <v>122825093</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>91519</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4025,25 +4001,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4053,13 +4029,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>529003</v>
+        <v>528967</v>
       </c>
       <c r="R31" t="n">
-        <v>6998021</v>
+        <v>6998079</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4088,7 +4064,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4098,12 +4074,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4118,19 +4094,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122824669</v>
+        <v>122824139</v>
       </c>
       <c r="B32" t="n">
         <v>79847</v>
@@ -4170,13 +4146,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528962</v>
+        <v>528870</v>
       </c>
       <c r="R32" t="n">
-        <v>6998022</v>
+        <v>6997994</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4203,9 +4179,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4220,22 +4206,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122824138</v>
+        <v>122823605</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4248,33 +4234,24 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
@@ -4284,7 +4261,7 @@
         <v>528887</v>
       </c>
       <c r="R33" t="n">
-        <v>6998044</v>
+        <v>6998073</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4316,7 +4293,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4326,12 +4303,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4346,22 +4323,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122824296</v>
+        <v>122823776</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4374,27 +4351,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4403,10 +4380,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528849</v>
+        <v>528879</v>
       </c>
       <c r="R34" t="n">
-        <v>6998016</v>
+        <v>6998065</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4439,11 +4416,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4470,10 +4442,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122825059</v>
+        <v>122824645</v>
       </c>
       <c r="B35" t="n">
-        <v>77699</v>
+        <v>78503</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4486,21 +4458,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4510,10 +4482,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528960</v>
+        <v>528897</v>
       </c>
       <c r="R35" t="n">
-        <v>6998066</v>
+        <v>6998014</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4545,7 +4517,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4555,12 +4527,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4587,10 +4559,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122824517</v>
+        <v>122824775</v>
       </c>
       <c r="B36" t="n">
-        <v>78503</v>
+        <v>90917</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4599,25 +4571,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4627,10 +4599,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528878</v>
+        <v>528928</v>
       </c>
       <c r="R36" t="n">
-        <v>6997997</v>
+        <v>6998037</v>
       </c>
       <c r="S36" t="n">
         <v>8</v>
@@ -4662,7 +4634,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4672,12 +4644,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
+          <t>På gammal död stående gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4704,10 +4676,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122824504</v>
+        <v>122823542</v>
       </c>
       <c r="B37" t="n">
-        <v>57631</v>
+        <v>78503</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4720,46 +4692,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528884</v>
+        <v>528881</v>
       </c>
       <c r="R37" t="n">
-        <v>6997998</v>
+        <v>6998117</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4786,9 +4749,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4803,22 +4781,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122824729</v>
+        <v>122824203</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4827,38 +4805,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528904</v>
+        <v>528874</v>
       </c>
       <c r="R38" t="n">
-        <v>6998036</v>
+        <v>6998038</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4890,7 +4873,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4900,12 +4883,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Rikligt med spillning under tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4932,10 +4915,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122824798</v>
+        <v>122825055</v>
       </c>
       <c r="B39" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4948,21 +4931,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4972,13 +4955,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528929</v>
+        <v>529003</v>
       </c>
       <c r="R39" t="n">
-        <v>6998043</v>
+        <v>6998021</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5007,7 +4990,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5017,12 +5000,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5049,10 +5032,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122824139</v>
+        <v>122823308</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>78502</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5065,21 +5048,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5089,10 +5072,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528870</v>
+        <v>528904</v>
       </c>
       <c r="R40" t="n">
-        <v>6997994</v>
+        <v>6998141</v>
       </c>
       <c r="S40" t="n">
         <v>6</v>
@@ -5124,7 +5107,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5134,7 +5117,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5149,22 +5137,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122823776</v>
+        <v>122824689</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>78411</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5177,39 +5165,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528879</v>
+        <v>528901</v>
       </c>
       <c r="R41" t="n">
-        <v>6998065</v>
+        <v>6998033</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5239,9 +5222,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5256,22 +5254,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122823943</v>
+        <v>122824729</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5284,39 +5282,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528895</v>
+        <v>528904</v>
       </c>
       <c r="R42" t="n">
-        <v>6998055</v>
+        <v>6998036</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5346,9 +5339,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5363,22 +5371,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122824114</v>
+        <v>122824504</v>
       </c>
       <c r="B43" t="n">
-        <v>74863</v>
+        <v>57631</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5391,34 +5399,43 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528886</v>
+        <v>528884</v>
       </c>
       <c r="R43" t="n">
-        <v>6998049</v>
+        <v>6997998</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5448,24 +5465,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5480,22 +5482,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122823389</v>
+        <v>122824159</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5508,46 +5510,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528893</v>
+        <v>528887</v>
       </c>
       <c r="R44" t="n">
-        <v>6998121</v>
+        <v>6998044</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5576,7 +5569,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5586,12 +5579,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5606,19 +5599,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122824716</v>
+        <v>122824883</v>
       </c>
       <c r="B45" t="n">
         <v>79847</v>
@@ -5651,20 +5644,29 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528980</v>
+        <v>528973</v>
       </c>
       <c r="R45" t="n">
-        <v>6998018</v>
+        <v>6998038</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5691,9 +5693,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5708,22 +5725,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122824689</v>
+        <v>122824940</v>
       </c>
       <c r="B46" t="n">
-        <v>78411</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5736,37 +5753,46 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528901</v>
+        <v>528993</v>
       </c>
       <c r="R46" t="n">
-        <v>6998033</v>
+        <v>6998013</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5795,7 +5821,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5805,12 +5831,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5825,22 +5846,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122824645</v>
+        <v>122824716</v>
       </c>
       <c r="B47" t="n">
-        <v>78503</v>
+        <v>79847</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5853,21 +5874,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5877,10 +5898,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528897</v>
+        <v>528980</v>
       </c>
       <c r="R47" t="n">
-        <v>6998014</v>
+        <v>6998018</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5910,24 +5931,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5942,22 +5948,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122823616</v>
+        <v>122824419</v>
       </c>
       <c r="B48" t="n">
-        <v>79807</v>
+        <v>79384</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5966,25 +5972,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5994,10 +6000,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528903</v>
+        <v>528853</v>
       </c>
       <c r="R48" t="n">
-        <v>6998106</v>
+        <v>6998012</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6029,7 +6035,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6039,12 +6045,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
+          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6071,10 +6077,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122823666</v>
+        <v>122823640</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6087,29 +6093,24 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
@@ -6119,7 +6120,7 @@
         <v>528890</v>
       </c>
       <c r="R49" t="n">
-        <v>6998089</v>
+        <v>6998093</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6152,11 +6153,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6183,10 +6179,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122823935</v>
+        <v>122824138</v>
       </c>
       <c r="B50" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6199,37 +6195,46 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528934</v>
+        <v>528887</v>
       </c>
       <c r="R50" t="n">
-        <v>6998051</v>
+        <v>6998044</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6258,7 +6263,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6268,12 +6273,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6288,22 +6293,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122824775</v>
+        <v>122823666</v>
       </c>
       <c r="B51" t="n">
-        <v>90917</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6312,41 +6317,46 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528928</v>
+        <v>528890</v>
       </c>
       <c r="R51" t="n">
-        <v>6998037</v>
+        <v>6998089</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6373,24 +6383,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal död stående gran i gammal barrblandskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6405,12 +6405,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122824871</v>
+        <v>122823959</v>
       </c>
       <c r="B4" t="n">
-        <v>79751</v>
+        <v>79848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,25 +930,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,13 +958,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528956</v>
+        <v>528918</v>
       </c>
       <c r="R4" t="n">
-        <v>6998028</v>
+        <v>6998048</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På asp i gammal granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,22 +1023,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122823959</v>
+        <v>122824871</v>
       </c>
       <c r="B5" t="n">
-        <v>79848</v>
+        <v>79751</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,25 +1047,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6456</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1075,13 +1075,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528918</v>
+        <v>528956</v>
       </c>
       <c r="R5" t="n">
-        <v>6998048</v>
+        <v>6998028</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,12 +1140,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -3872,10 +3872,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122823616</v>
+        <v>122825093</v>
       </c>
       <c r="B30" t="n">
-        <v>79807</v>
+        <v>91519</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3884,25 +3884,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>760</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3912,10 +3912,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528903</v>
+        <v>528967</v>
       </c>
       <c r="R30" t="n">
-        <v>6998106</v>
+        <v>6998079</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3989,10 +3989,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122825093</v>
+        <v>122824139</v>
       </c>
       <c r="B31" t="n">
-        <v>91519</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4001,25 +4001,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4029,13 +4029,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528967</v>
+        <v>528870</v>
       </c>
       <c r="R31" t="n">
-        <v>6998079</v>
+        <v>6997994</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4074,12 +4074,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4094,22 +4089,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122824139</v>
+        <v>122823616</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>79807</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4118,25 +4113,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4146,13 +4141,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528870</v>
+        <v>528903</v>
       </c>
       <c r="R32" t="n">
-        <v>6997994</v>
+        <v>6998106</v>
       </c>
       <c r="S32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4181,7 +4176,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4191,7 +4186,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4206,12 +4206,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -5858,10 +5858,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122824716</v>
+        <v>122824419</v>
       </c>
       <c r="B47" t="n">
-        <v>79847</v>
+        <v>79384</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5874,21 +5874,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5898,10 +5898,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528980</v>
+        <v>528853</v>
       </c>
       <c r="R47" t="n">
-        <v>6998018</v>
+        <v>6998012</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5931,9 +5931,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5948,22 +5963,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122824419</v>
+        <v>122824716</v>
       </c>
       <c r="B48" t="n">
-        <v>79384</v>
+        <v>79847</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5976,21 +5991,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6000,10 +6015,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528853</v>
+        <v>528980</v>
       </c>
       <c r="R48" t="n">
-        <v>6998012</v>
+        <v>6998018</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6033,24 +6048,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6065,12 +6065,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -4793,10 +4793,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122824203</v>
+        <v>122825055</v>
       </c>
       <c r="B38" t="n">
-        <v>56688</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4805,46 +4805,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528874</v>
+        <v>529003</v>
       </c>
       <c r="R38" t="n">
-        <v>6998038</v>
+        <v>6998021</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4873,7 +4868,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4883,12 +4878,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Rikligt med spillning under tall</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4903,22 +4898,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122825055</v>
+        <v>122824203</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>56688</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4927,41 +4922,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>529003</v>
+        <v>528874</v>
       </c>
       <c r="R39" t="n">
-        <v>6998021</v>
+        <v>6998038</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5000,12 +5000,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Rikligt med spillning under tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5020,12 +5020,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -5149,10 +5149,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122824689</v>
+        <v>122824504</v>
       </c>
       <c r="B41" t="n">
-        <v>78411</v>
+        <v>57631</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5165,34 +5165,43 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528901</v>
+        <v>528884</v>
       </c>
       <c r="R41" t="n">
-        <v>6998033</v>
+        <v>6997998</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5222,24 +5231,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5254,22 +5248,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122824729</v>
+        <v>122824689</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>78411</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5282,21 +5276,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5306,10 +5300,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528904</v>
+        <v>528901</v>
       </c>
       <c r="R42" t="n">
-        <v>6998036</v>
+        <v>6998033</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5341,7 +5335,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5351,12 +5345,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5383,10 +5377,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122824504</v>
+        <v>122824729</v>
       </c>
       <c r="B43" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5399,43 +5393,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528884</v>
+        <v>528904</v>
       </c>
       <c r="R43" t="n">
-        <v>6997998</v>
+        <v>6998036</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5465,9 +5450,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5482,12 +5482,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122824915</v>
+        <v>122823789</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>79851</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528964</v>
+        <v>528910</v>
       </c>
       <c r="R3" t="n">
-        <v>6998032</v>
+        <v>6998072</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På asp i gammal barrblandskog</t>
+          <t>På sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122823959</v>
+        <v>122823943</v>
       </c>
       <c r="B4" t="n">
-        <v>79848</v>
+        <v>79850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,37 +934,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528918</v>
+        <v>528895</v>
       </c>
       <c r="R4" t="n">
-        <v>6998048</v>
+        <v>6998055</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,24 +996,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122824871</v>
+        <v>122824940</v>
       </c>
       <c r="B5" t="n">
-        <v>79751</v>
+        <v>79850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,38 +1037,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528956</v>
+        <v>528993</v>
       </c>
       <c r="R5" t="n">
-        <v>6998028</v>
+        <v>6998013</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1110,7 +1109,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1119,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På asp i gammal granskog</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,22 +1134,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122823876</v>
+        <v>122824296</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,31 +1162,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1201,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528897</v>
+        <v>528849</v>
       </c>
       <c r="R6" t="n">
-        <v>6998064</v>
+        <v>6998016</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,24 +1224,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal senvuxen granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,22 +1246,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122823780</v>
+        <v>122823542</v>
       </c>
       <c r="B7" t="n">
-        <v>79848</v>
+        <v>78506</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,21 +1274,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1318,13 +1298,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528879</v>
+        <v>528881</v>
       </c>
       <c r="R7" t="n">
-        <v>6998066</v>
+        <v>6998117</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,9 +1331,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,22 +1363,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122823534</v>
+        <v>122823666</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1425,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528883</v>
+        <v>528890</v>
       </c>
       <c r="R8" t="n">
-        <v>6998125</v>
+        <v>6998089</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1492,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122823224</v>
+        <v>122823959</v>
       </c>
       <c r="B9" t="n">
-        <v>79751</v>
+        <v>79851</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,25 +1499,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6456</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1532,13 +1527,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528911</v>
+        <v>528918</v>
       </c>
       <c r="R9" t="n">
-        <v>6998157</v>
+        <v>6998048</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,12 +1572,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1597,22 +1592,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122824996</v>
+        <v>122823308</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>78505</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,21 +1620,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1649,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528952</v>
+        <v>528904</v>
       </c>
       <c r="R10" t="n">
-        <v>6998039</v>
+        <v>6998141</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1684,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1694,12 +1689,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark på stam av levande glasbjörk med savflöde</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1726,10 +1721,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122823389</v>
+        <v>122824915</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,46 +1737,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528893</v>
+        <v>528964</v>
       </c>
       <c r="R11" t="n">
-        <v>6998121</v>
+        <v>6998032</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1810,7 +1796,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1820,12 +1806,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,22 +1826,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122824517</v>
+        <v>122823389</v>
       </c>
       <c r="B12" t="n">
-        <v>78503</v>
+        <v>78769</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,34 +1854,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528878</v>
+        <v>528893</v>
       </c>
       <c r="R12" t="n">
-        <v>6997997</v>
+        <v>6998121</v>
       </c>
       <c r="S12" t="n">
         <v>8</v>
@@ -1927,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1937,12 +1932,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,22 +1952,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122825157</v>
+        <v>122824729</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,21 +1980,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2009,10 +2004,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528946</v>
+        <v>528904</v>
       </c>
       <c r="R13" t="n">
-        <v>6998089</v>
+        <v>6998036</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2042,9 +2037,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,22 +2069,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122824617</v>
+        <v>122824114</v>
       </c>
       <c r="B14" t="n">
-        <v>78502</v>
+        <v>74866</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,21 +2097,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2111,10 +2121,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528897</v>
+        <v>528886</v>
       </c>
       <c r="R14" t="n">
-        <v>6998014</v>
+        <v>6998049</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2146,7 +2156,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2156,12 +2166,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2188,10 +2198,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122823653</v>
+        <v>122824608</v>
       </c>
       <c r="B15" t="n">
-        <v>74863</v>
+        <v>56683</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2204,34 +2214,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528898</v>
+        <v>528928</v>
       </c>
       <c r="R15" t="n">
-        <v>6998091</v>
+        <v>6998035</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2261,24 +2280,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2293,22 +2297,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122824798</v>
+        <v>122825192</v>
       </c>
       <c r="B16" t="n">
-        <v>74863</v>
+        <v>79851</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2321,21 +2325,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2345,13 +2349,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528929</v>
+        <v>528946</v>
       </c>
       <c r="R16" t="n">
-        <v>6998043</v>
+        <v>6998089</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2378,24 +2382,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2410,22 +2399,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122824296</v>
+        <v>122824775</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>90920</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2434,46 +2423,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528849</v>
+        <v>528928</v>
       </c>
       <c r="R17" t="n">
-        <v>6998016</v>
+        <v>6998037</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2500,14 +2484,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal död stående gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2522,22 +2516,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122824114</v>
+        <v>122824517</v>
       </c>
       <c r="B18" t="n">
-        <v>74863</v>
+        <v>78506</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2550,21 +2544,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2574,13 +2568,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528886</v>
+        <v>528878</v>
       </c>
       <c r="R18" t="n">
-        <v>6998049</v>
+        <v>6997997</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2609,7 +2603,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2619,12 +2613,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2651,10 +2645,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122825192</v>
+        <v>122824883</v>
       </c>
       <c r="B19" t="n">
-        <v>79848</v>
+        <v>79850</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2667,37 +2661,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528946</v>
+        <v>528973</v>
       </c>
       <c r="R19" t="n">
-        <v>6998089</v>
+        <v>6998038</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2724,9 +2727,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2741,22 +2759,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122825059</v>
+        <v>122824871</v>
       </c>
       <c r="B20" t="n">
-        <v>77699</v>
+        <v>79754</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2765,25 +2783,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228579</v>
+        <v>6456</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2793,13 +2811,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528960</v>
+        <v>528956</v>
       </c>
       <c r="R20" t="n">
-        <v>6998066</v>
+        <v>6998028</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2828,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2838,12 +2856,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,10 +2888,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122825263</v>
+        <v>122824203</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>56691</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2882,31 +2900,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2915,10 +2933,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528938</v>
+        <v>528874</v>
       </c>
       <c r="R21" t="n">
-        <v>6998101</v>
+        <v>6998038</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2948,14 +2966,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Rikligt med spillning under tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2970,22 +2998,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122824314</v>
+        <v>122825263</v>
       </c>
       <c r="B22" t="n">
-        <v>78503</v>
+        <v>57481</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2998,37 +3026,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528828</v>
+        <v>528938</v>
       </c>
       <c r="R22" t="n">
-        <v>6998005</v>
+        <v>6998101</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3055,24 +3088,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3087,22 +3110,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122823943</v>
+        <v>122824645</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>78506</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3115,39 +3138,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528895</v>
+        <v>528897</v>
       </c>
       <c r="R23" t="n">
-        <v>6998055</v>
+        <v>6998014</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3177,9 +3195,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3194,22 +3227,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122823935</v>
+        <v>122824159</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>77702</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3222,21 +3255,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3246,13 +3279,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528934</v>
+        <v>528887</v>
       </c>
       <c r="R24" t="n">
-        <v>6998051</v>
+        <v>6998044</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3281,7 +3314,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3291,12 +3324,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3311,22 +3344,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122823789</v>
+        <v>122824689</v>
       </c>
       <c r="B25" t="n">
-        <v>79848</v>
+        <v>78414</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3339,21 +3372,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3363,10 +3396,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528910</v>
+        <v>528901</v>
       </c>
       <c r="R25" t="n">
-        <v>6998072</v>
+        <v>6998033</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3398,7 +3431,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3408,12 +3441,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På sälglåga i gammal granskog</t>
+          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3440,10 +3473,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122824608</v>
+        <v>122825055</v>
       </c>
       <c r="B26" t="n">
-        <v>56680</v>
+        <v>79850</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3456,46 +3489,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528928</v>
+        <v>529003</v>
       </c>
       <c r="R26" t="n">
-        <v>6998035</v>
+        <v>6998021</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3522,9 +3546,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3539,22 +3578,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122824669</v>
+        <v>122825093</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>91522</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3563,25 +3602,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3591,10 +3630,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528962</v>
+        <v>528967</v>
       </c>
       <c r="R27" t="n">
-        <v>6998022</v>
+        <v>6998079</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3624,9 +3663,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3641,22 +3695,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122824928</v>
+        <v>122823776</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3687,16 +3741,21 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528989</v>
+        <v>528879</v>
       </c>
       <c r="R28" t="n">
-        <v>6998039</v>
+        <v>6998065</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3755,10 +3814,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122824294</v>
+        <v>122824314</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>78506</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3771,21 +3830,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3795,13 +3854,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528874</v>
+        <v>528828</v>
       </c>
       <c r="R29" t="n">
-        <v>6998038</v>
+        <v>6998005</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3845,7 +3904,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal tall</t>
+          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3860,7 +3919,7 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
@@ -3872,10 +3931,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122825093</v>
+        <v>122823616</v>
       </c>
       <c r="B30" t="n">
-        <v>91519</v>
+        <v>79810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3884,25 +3943,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>760</v>
+        <v>229497</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3912,10 +3971,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528967</v>
+        <v>528903</v>
       </c>
       <c r="R30" t="n">
-        <v>6998079</v>
+        <v>6998106</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3947,7 +4006,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3957,12 +4016,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3989,10 +4048,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122824139</v>
+        <v>122823534</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4005,37 +4064,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528870</v>
+        <v>528883</v>
       </c>
       <c r="R31" t="n">
-        <v>6997994</v>
+        <v>6998125</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4062,19 +4126,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:57</t>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4089,22 +4148,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122823616</v>
+        <v>122824617</v>
       </c>
       <c r="B32" t="n">
-        <v>79807</v>
+        <v>78505</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4113,25 +4172,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229497</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4141,10 +4200,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528903</v>
+        <v>528897</v>
       </c>
       <c r="R32" t="n">
-        <v>6998106</v>
+        <v>6998014</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4176,7 +4235,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4186,12 +4245,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4221,7 +4280,7 @@
         <v>122823605</v>
       </c>
       <c r="B33" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4335,10 +4394,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122823776</v>
+        <v>122824798</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>74866</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4351,42 +4410,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528879</v>
+        <v>528929</v>
       </c>
       <c r="R34" t="n">
-        <v>6998065</v>
+        <v>6998043</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4413,9 +4467,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4430,22 +4499,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122824645</v>
+        <v>122825059</v>
       </c>
       <c r="B35" t="n">
-        <v>78503</v>
+        <v>77702</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4458,21 +4527,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>228579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4482,10 +4551,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528897</v>
+        <v>528960</v>
       </c>
       <c r="R35" t="n">
-        <v>6998014</v>
+        <v>6998066</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4517,7 +4586,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4527,12 +4596,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4552,17 +4621,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122824775</v>
+        <v>122823780</v>
       </c>
       <c r="B36" t="n">
-        <v>90917</v>
+        <v>79851</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4571,25 +4640,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4599,13 +4668,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528928</v>
+        <v>528879</v>
       </c>
       <c r="R36" t="n">
-        <v>6998037</v>
+        <v>6998066</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4632,24 +4701,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gammal död stående gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4664,22 +4718,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122823542</v>
+        <v>122824419</v>
       </c>
       <c r="B37" t="n">
-        <v>78503</v>
+        <v>79387</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4692,21 +4746,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4716,13 +4770,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528881</v>
+        <v>528853</v>
       </c>
       <c r="R37" t="n">
-        <v>6998117</v>
+        <v>6998012</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4751,7 +4805,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4761,12 +4815,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4793,10 +4847,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122825055</v>
+        <v>122824294</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4809,21 +4863,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4833,13 +4887,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>529003</v>
+        <v>528874</v>
       </c>
       <c r="R38" t="n">
-        <v>6998021</v>
+        <v>6998038</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4868,7 +4922,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4878,12 +4932,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gammal tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4898,22 +4952,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122824203</v>
+        <v>122824504</v>
       </c>
       <c r="B39" t="n">
-        <v>56688</v>
+        <v>57634</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4922,31 +4976,35 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4955,10 +5013,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528874</v>
+        <v>528884</v>
       </c>
       <c r="R39" t="n">
-        <v>6998038</v>
+        <v>6997998</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4988,24 +5046,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt med spillning under tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5020,22 +5063,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122823308</v>
+        <v>122823876</v>
       </c>
       <c r="B40" t="n">
-        <v>78502</v>
+        <v>78769</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5048,37 +5091,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528904</v>
+        <v>528897</v>
       </c>
       <c r="R40" t="n">
-        <v>6998141</v>
+        <v>6998064</v>
       </c>
       <c r="S40" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5107,7 +5159,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5117,12 +5169,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>På gamla granar i gammal senvuxen granskog</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5149,10 +5201,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122824504</v>
+        <v>122824669</v>
       </c>
       <c r="B41" t="n">
-        <v>57631</v>
+        <v>79850</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5165,43 +5217,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528884</v>
+        <v>528962</v>
       </c>
       <c r="R41" t="n">
-        <v>6997998</v>
+        <v>6998022</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5260,10 +5303,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122824689</v>
+        <v>122824138</v>
       </c>
       <c r="B42" t="n">
-        <v>78411</v>
+        <v>78769</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5276,34 +5319,43 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528901</v>
+        <v>528887</v>
       </c>
       <c r="R42" t="n">
-        <v>6998033</v>
+        <v>6998044</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5335,7 +5387,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5345,12 +5397,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5377,10 +5429,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122824729</v>
+        <v>122824139</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5393,21 +5445,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5417,13 +5469,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528904</v>
+        <v>528870</v>
       </c>
       <c r="R43" t="n">
-        <v>6998036</v>
+        <v>6997994</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5452,7 +5504,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5462,12 +5514,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5482,22 +5529,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122824159</v>
+        <v>122823640</v>
       </c>
       <c r="B44" t="n">
-        <v>77699</v>
+        <v>79850</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5510,21 +5557,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5534,10 +5581,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528887</v>
+        <v>528890</v>
       </c>
       <c r="R44" t="n">
-        <v>6998044</v>
+        <v>6998093</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5567,24 +5614,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5599,22 +5631,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122824883</v>
+        <v>122823653</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>74866</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5627,46 +5659,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528973</v>
+        <v>528898</v>
       </c>
       <c r="R45" t="n">
-        <v>6998038</v>
+        <v>6998091</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5695,7 +5718,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5705,12 +5728,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På död sälg (kort)</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5725,22 +5748,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122824940</v>
+        <v>122824928</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5770,29 +5793,20 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528993</v>
+        <v>528989</v>
       </c>
       <c r="R46" t="n">
-        <v>6998013</v>
+        <v>6998039</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5819,19 +5833,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>14:26</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5846,22 +5850,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122824419</v>
+        <v>122825157</v>
       </c>
       <c r="B47" t="n">
-        <v>79384</v>
+        <v>79850</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5874,21 +5878,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5898,10 +5902,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528853</v>
+        <v>528946</v>
       </c>
       <c r="R47" t="n">
-        <v>6998012</v>
+        <v>6998089</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5931,24 +5935,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:06</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5963,12 +5952,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5978,7 +5967,7 @@
         <v>122824716</v>
       </c>
       <c r="B48" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6077,10 +6066,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122823640</v>
+        <v>122823224</v>
       </c>
       <c r="B49" t="n">
-        <v>79847</v>
+        <v>79754</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6089,25 +6078,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6117,10 +6106,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528890</v>
+        <v>528911</v>
       </c>
       <c r="R49" t="n">
-        <v>6998093</v>
+        <v>6998157</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6150,9 +6139,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6167,22 +6171,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122824138</v>
+        <v>122824996</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6195,46 +6199,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528887</v>
+        <v>528952</v>
       </c>
       <c r="R50" t="n">
-        <v>6998044</v>
+        <v>6998039</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6263,7 +6258,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6273,12 +6268,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På bark på stam av levande glasbjörk med savflöde</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6298,17 +6293,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122823666</v>
+        <v>122823935</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6321,42 +6316,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528890</v>
+        <v>528934</v>
       </c>
       <c r="R51" t="n">
-        <v>6998089</v>
+        <v>6998051</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6383,14 +6373,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6405,12 +6405,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122823789</v>
+        <v>122825059</v>
       </c>
       <c r="B3" t="n">
-        <v>79851</v>
+        <v>77704</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528910</v>
+        <v>528960</v>
       </c>
       <c r="R3" t="n">
-        <v>6998072</v>
+        <v>6998066</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På sälglåga i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122823943</v>
+        <v>122823935</v>
       </c>
       <c r="B4" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,24 +952,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528895</v>
+        <v>528934</v>
       </c>
       <c r="R4" t="n">
-        <v>6998055</v>
+        <v>6998051</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,9 +991,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +1023,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122824940</v>
+        <v>122823776</v>
       </c>
       <c r="B5" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,14 +1068,10 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1074,13 +1080,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528993</v>
+        <v>528879</v>
       </c>
       <c r="R5" t="n">
-        <v>6998013</v>
+        <v>6998065</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,19 +1113,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,12 +1130,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1258,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122823542</v>
+        <v>122824775</v>
       </c>
       <c r="B7" t="n">
-        <v>78506</v>
+        <v>90922</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,25 +1266,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,13 +1294,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528881</v>
+        <v>528928</v>
       </c>
       <c r="R7" t="n">
-        <v>6998117</v>
+        <v>6998037</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1333,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,12 +1339,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>På gammal död stående gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122823666</v>
+        <v>122825192</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,36 +1387,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528890</v>
+        <v>528946</v>
       </c>
       <c r="R8" t="n">
         <v>6998089</v>
@@ -1456,11 +1447,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122823959</v>
+        <v>122823780</v>
       </c>
       <c r="B9" t="n">
-        <v>79851</v>
+        <v>79853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1527,13 +1513,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528918</v>
+        <v>528879</v>
       </c>
       <c r="R9" t="n">
-        <v>6998048</v>
+        <v>6998066</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,24 +1546,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1592,22 +1563,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122823308</v>
+        <v>122824996</v>
       </c>
       <c r="B10" t="n">
-        <v>78505</v>
+        <v>79852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,21 +1591,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1644,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528904</v>
+        <v>528952</v>
       </c>
       <c r="R10" t="n">
-        <v>6998141</v>
+        <v>6998039</v>
       </c>
       <c r="S10" t="n">
         <v>6</v>
@@ -1679,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,12 +1660,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>På bark på stam av levande glasbjörk med savflöde</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122824915</v>
+        <v>122824159</v>
       </c>
       <c r="B11" t="n">
-        <v>79850</v>
+        <v>77704</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,21 +1708,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1761,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528964</v>
+        <v>528887</v>
       </c>
       <c r="R11" t="n">
-        <v>6998032</v>
+        <v>6998044</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1767,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,12 +1777,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På asp i gammal barrblandskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,10 +1809,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122823389</v>
+        <v>122823640</v>
       </c>
       <c r="B12" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,46 +1825,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528893</v>
+        <v>528890</v>
       </c>
       <c r="R12" t="n">
-        <v>6998121</v>
+        <v>6998093</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1920,24 +1882,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,22 +1899,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122824729</v>
+        <v>122824314</v>
       </c>
       <c r="B13" t="n">
-        <v>78769</v>
+        <v>78508</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1980,21 +1927,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2004,13 +1951,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528904</v>
+        <v>528828</v>
       </c>
       <c r="R13" t="n">
-        <v>6998036</v>
+        <v>6998005</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2039,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2049,12 +1996,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,22 +2016,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122824114</v>
+        <v>122825055</v>
       </c>
       <c r="B14" t="n">
-        <v>74866</v>
+        <v>79852</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2097,21 +2044,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2121,13 +2068,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528886</v>
+        <v>529003</v>
       </c>
       <c r="R14" t="n">
-        <v>6998049</v>
+        <v>6998021</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2156,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2166,12 +2113,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,22 +2133,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122824608</v>
+        <v>122824729</v>
       </c>
       <c r="B15" t="n">
-        <v>56683</v>
+        <v>78771</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2214,43 +2161,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528928</v>
+        <v>528904</v>
       </c>
       <c r="R15" t="n">
-        <v>6998035</v>
+        <v>6998036</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2280,9 +2218,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,22 +2250,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122825192</v>
+        <v>122824617</v>
       </c>
       <c r="B16" t="n">
-        <v>79851</v>
+        <v>78507</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2325,21 +2278,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2349,10 +2302,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528946</v>
+        <v>528897</v>
       </c>
       <c r="R16" t="n">
-        <v>6998089</v>
+        <v>6998014</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2382,9 +2335,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,22 +2367,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122824775</v>
+        <v>122824915</v>
       </c>
       <c r="B17" t="n">
-        <v>90920</v>
+        <v>79852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,25 +2391,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2451,13 +2419,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528928</v>
+        <v>528964</v>
       </c>
       <c r="R17" t="n">
-        <v>6998037</v>
+        <v>6998032</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2486,7 +2454,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,12 +2464,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal död stående gran i gammal barrblandskog</t>
+          <t>På asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2528,10 +2496,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122824517</v>
+        <v>122824798</v>
       </c>
       <c r="B18" t="n">
-        <v>78506</v>
+        <v>74866</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,21 +2512,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2568,13 +2536,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528878</v>
+        <v>528929</v>
       </c>
       <c r="R18" t="n">
-        <v>6997997</v>
+        <v>6998043</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2603,7 +2571,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,12 +2581,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2633,22 +2601,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122824883</v>
+        <v>122824294</v>
       </c>
       <c r="B19" t="n">
-        <v>79850</v>
+        <v>78771</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2661,46 +2629,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528973</v>
+        <v>528874</v>
       </c>
       <c r="R19" t="n">
         <v>6998038</v>
       </c>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2729,7 +2688,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,12 +2698,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På död sälg (kort)</t>
+          <t>På gammal tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2759,22 +2718,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122824871</v>
+        <v>122823542</v>
       </c>
       <c r="B20" t="n">
-        <v>79754</v>
+        <v>78508</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2783,25 +2742,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2811,13 +2770,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528956</v>
+        <v>528881</v>
       </c>
       <c r="R20" t="n">
-        <v>6998028</v>
+        <v>6998117</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2846,7 +2805,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2856,12 +2815,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På asp i gammal granskog</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2881,17 +2840,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122824203</v>
+        <v>122824645</v>
       </c>
       <c r="B21" t="n">
-        <v>56691</v>
+        <v>78508</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2900,43 +2859,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528874</v>
+        <v>528897</v>
       </c>
       <c r="R21" t="n">
-        <v>6998038</v>
+        <v>6998014</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2968,7 +2922,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2978,12 +2932,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt med spillning under tall</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3010,7 +2964,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122825263</v>
+        <v>122823534</v>
       </c>
       <c r="B22" t="n">
         <v>57481</v>
@@ -3055,10 +3009,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528938</v>
+        <v>528883</v>
       </c>
       <c r="R22" t="n">
-        <v>6998101</v>
+        <v>6998125</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3095,7 +3049,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3122,10 +3076,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122824645</v>
+        <v>122824608</v>
       </c>
       <c r="B23" t="n">
-        <v>78506</v>
+        <v>56683</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3138,34 +3092,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528897</v>
+        <v>528928</v>
       </c>
       <c r="R23" t="n">
-        <v>6998014</v>
+        <v>6998035</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3195,24 +3158,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3227,22 +3175,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122824159</v>
+        <v>122824716</v>
       </c>
       <c r="B24" t="n">
-        <v>77702</v>
+        <v>79852</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3255,21 +3203,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3279,10 +3227,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528887</v>
+        <v>528980</v>
       </c>
       <c r="R24" t="n">
-        <v>6998044</v>
+        <v>6998018</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3312,24 +3260,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3344,22 +3277,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122824689</v>
+        <v>122824669</v>
       </c>
       <c r="B25" t="n">
-        <v>78414</v>
+        <v>79852</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3372,21 +3305,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3396,10 +3329,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528901</v>
+        <v>528962</v>
       </c>
       <c r="R25" t="n">
-        <v>6998033</v>
+        <v>6998022</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3429,24 +3362,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3461,22 +3379,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122825055</v>
+        <v>122824504</v>
       </c>
       <c r="B26" t="n">
-        <v>79850</v>
+        <v>57634</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3489,37 +3407,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529003</v>
+        <v>528884</v>
       </c>
       <c r="R26" t="n">
-        <v>6998021</v>
+        <v>6997998</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3546,24 +3473,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3578,22 +3490,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122825093</v>
+        <v>122823224</v>
       </c>
       <c r="B27" t="n">
-        <v>91522</v>
+        <v>79756</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3602,25 +3514,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>760</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3630,10 +3542,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528967</v>
+        <v>528911</v>
       </c>
       <c r="R27" t="n">
-        <v>6998079</v>
+        <v>6998157</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3665,7 +3577,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3675,12 +3587,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3700,17 +3612,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122823776</v>
+        <v>122823653</v>
       </c>
       <c r="B28" t="n">
-        <v>79850</v>
+        <v>74866</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3723,39 +3635,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528879</v>
+        <v>528898</v>
       </c>
       <c r="R28" t="n">
-        <v>6998065</v>
+        <v>6998091</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3785,9 +3692,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3802,22 +3724,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122824314</v>
+        <v>122824114</v>
       </c>
       <c r="B29" t="n">
-        <v>78506</v>
+        <v>74866</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3830,21 +3752,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3854,13 +3776,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528828</v>
+        <v>528886</v>
       </c>
       <c r="R29" t="n">
-        <v>6998005</v>
+        <v>6998049</v>
       </c>
       <c r="S29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3889,7 +3811,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3899,12 +3821,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3919,22 +3841,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122823616</v>
+        <v>122824138</v>
       </c>
       <c r="B30" t="n">
-        <v>79810</v>
+        <v>78771</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3943,38 +3865,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>528903</v>
+        <v>528887</v>
       </c>
       <c r="R30" t="n">
-        <v>6998106</v>
+        <v>6998044</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4006,7 +3937,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4016,12 +3947,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4048,10 +3979,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122823534</v>
+        <v>122824517</v>
       </c>
       <c r="B31" t="n">
-        <v>57481</v>
+        <v>78508</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4064,42 +3995,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528883</v>
+        <v>528878</v>
       </c>
       <c r="R31" t="n">
-        <v>6998125</v>
+        <v>6997997</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4126,14 +4052,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4148,22 +4084,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122824617</v>
+        <v>122825263</v>
       </c>
       <c r="B32" t="n">
-        <v>78505</v>
+        <v>57481</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4176,34 +4112,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528897</v>
+        <v>528938</v>
       </c>
       <c r="R32" t="n">
-        <v>6998014</v>
+        <v>6998101</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4233,24 +4174,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4265,22 +4196,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122823605</v>
+        <v>122823876</v>
       </c>
       <c r="B33" t="n">
-        <v>79850</v>
+        <v>78771</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4293,34 +4224,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528887</v>
+        <v>528897</v>
       </c>
       <c r="R33" t="n">
-        <v>6998073</v>
+        <v>6998064</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4352,7 +4292,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4362,12 +4302,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På gamla granar i gammal senvuxen granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4382,22 +4322,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122824798</v>
+        <v>122824871</v>
       </c>
       <c r="B34" t="n">
-        <v>74866</v>
+        <v>79756</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4406,25 +4346,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4434,13 +4374,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528929</v>
+        <v>528956</v>
       </c>
       <c r="R34" t="n">
-        <v>6998043</v>
+        <v>6998028</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4469,7 +4409,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4479,12 +4419,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4499,22 +4439,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122825059</v>
+        <v>122824928</v>
       </c>
       <c r="B35" t="n">
-        <v>77702</v>
+        <v>79852</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4527,21 +4467,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4551,10 +4491,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528960</v>
+        <v>528989</v>
       </c>
       <c r="R35" t="n">
-        <v>6998066</v>
+        <v>6998039</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4584,24 +4524,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4616,22 +4541,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122823780</v>
+        <v>122824940</v>
       </c>
       <c r="B36" t="n">
-        <v>79851</v>
+        <v>79852</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4644,37 +4569,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528879</v>
+        <v>528993</v>
       </c>
       <c r="R36" t="n">
-        <v>6998066</v>
+        <v>6998013</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4701,9 +4635,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4718,22 +4662,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122824419</v>
+        <v>122823308</v>
       </c>
       <c r="B37" t="n">
-        <v>79387</v>
+        <v>78507</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4746,21 +4690,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4770,13 +4714,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528853</v>
+        <v>528904</v>
       </c>
       <c r="R37" t="n">
-        <v>6998012</v>
+        <v>6998141</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4805,7 +4749,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4815,12 +4759,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På ved på gammal tallhögstubbe</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4847,10 +4791,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122824294</v>
+        <v>122824419</v>
       </c>
       <c r="B38" t="n">
-        <v>78769</v>
+        <v>79389</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4863,21 +4807,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4887,10 +4831,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528874</v>
+        <v>528853</v>
       </c>
       <c r="R38" t="n">
-        <v>6998038</v>
+        <v>6998012</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4922,7 +4866,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4932,12 +4876,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal tall</t>
+          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4964,10 +4908,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122824504</v>
+        <v>122823959</v>
       </c>
       <c r="B39" t="n">
-        <v>57634</v>
+        <v>79853</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4980,46 +4924,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528884</v>
+        <v>528918</v>
       </c>
       <c r="R39" t="n">
-        <v>6997998</v>
+        <v>6998048</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5046,9 +4981,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5063,22 +5013,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122823876</v>
+        <v>122823666</v>
       </c>
       <c r="B40" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5091,31 +5041,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5124,10 +5070,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528897</v>
+        <v>528890</v>
       </c>
       <c r="R40" t="n">
-        <v>6998064</v>
+        <v>6998089</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5157,24 +5103,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal senvuxen granskog</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5189,22 +5125,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122824669</v>
+        <v>122825093</v>
       </c>
       <c r="B41" t="n">
-        <v>79850</v>
+        <v>91524</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5213,25 +5149,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5241,10 +5177,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528962</v>
+        <v>528967</v>
       </c>
       <c r="R41" t="n">
-        <v>6998022</v>
+        <v>6998079</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5274,9 +5210,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5291,22 +5242,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122824138</v>
+        <v>122824139</v>
       </c>
       <c r="B42" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5319,46 +5270,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528887</v>
+        <v>528870</v>
       </c>
       <c r="R42" t="n">
-        <v>6998044</v>
+        <v>6997994</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5387,7 +5329,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5397,12 +5339,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5417,22 +5354,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122824139</v>
+        <v>122825157</v>
       </c>
       <c r="B43" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5469,13 +5406,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528870</v>
+        <v>528946</v>
       </c>
       <c r="R43" t="n">
-        <v>6997994</v>
+        <v>6998089</v>
       </c>
       <c r="S43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5502,19 +5439,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5529,22 +5456,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122823640</v>
+        <v>122823605</v>
       </c>
       <c r="B44" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5581,10 +5508,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528890</v>
+        <v>528887</v>
       </c>
       <c r="R44" t="n">
-        <v>6998093</v>
+        <v>6998073</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5614,9 +5541,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5631,22 +5573,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122823653</v>
+        <v>122823389</v>
       </c>
       <c r="B45" t="n">
-        <v>74866</v>
+        <v>78771</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5659,37 +5601,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528898</v>
+        <v>528893</v>
       </c>
       <c r="R45" t="n">
-        <v>6998091</v>
+        <v>6998121</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5718,7 +5669,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5728,12 +5679,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5748,22 +5699,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122824928</v>
+        <v>122824203</v>
       </c>
       <c r="B46" t="n">
-        <v>79850</v>
+        <v>56691</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5772,38 +5723,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528989</v>
+        <v>528874</v>
       </c>
       <c r="R46" t="n">
-        <v>6998039</v>
+        <v>6998038</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5833,9 +5789,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Rikligt med spillning under tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5850,22 +5821,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122825157</v>
+        <v>122823616</v>
       </c>
       <c r="B47" t="n">
-        <v>79850</v>
+        <v>79812</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5874,25 +5845,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5902,10 +5873,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528946</v>
+        <v>528903</v>
       </c>
       <c r="R47" t="n">
-        <v>6998089</v>
+        <v>6998106</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5935,9 +5906,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5952,22 +5938,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122824716</v>
+        <v>122824883</v>
       </c>
       <c r="B48" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5997,20 +5983,29 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528980</v>
+        <v>528973</v>
       </c>
       <c r="R48" t="n">
-        <v>6998018</v>
+        <v>6998038</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6037,9 +6032,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6054,22 +6064,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122823224</v>
+        <v>122824689</v>
       </c>
       <c r="B49" t="n">
-        <v>79754</v>
+        <v>78416</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6078,25 +6088,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6456</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6106,10 +6116,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528911</v>
+        <v>528901</v>
       </c>
       <c r="R49" t="n">
-        <v>6998157</v>
+        <v>6998033</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6141,7 +6151,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6151,12 +6161,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6183,10 +6193,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122824996</v>
+        <v>122823789</v>
       </c>
       <c r="B50" t="n">
-        <v>79850</v>
+        <v>79853</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6199,21 +6209,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6223,13 +6233,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528952</v>
+        <v>528910</v>
       </c>
       <c r="R50" t="n">
-        <v>6998039</v>
+        <v>6998072</v>
       </c>
       <c r="S50" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6258,7 +6268,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6268,12 +6278,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På bark på stam av levande glasbjörk med savflöde</t>
+          <t>På sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6293,17 +6303,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122823935</v>
+        <v>122823943</v>
       </c>
       <c r="B51" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6334,19 +6344,24 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528934</v>
+        <v>528895</v>
       </c>
       <c r="R51" t="n">
-        <v>6998051</v>
+        <v>6998055</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6373,24 +6388,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6405,12 +6405,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122824159</v>
+        <v>122823640</v>
       </c>
       <c r="B11" t="n">
-        <v>77704</v>
+        <v>79852</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1708,21 +1708,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528887</v>
+        <v>528890</v>
       </c>
       <c r="R11" t="n">
-        <v>6998044</v>
+        <v>6998093</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,24 +1765,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,22 +1782,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122823640</v>
+        <v>122824159</v>
       </c>
       <c r="B12" t="n">
-        <v>79852</v>
+        <v>77704</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1825,21 +1810,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1849,10 +1834,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528890</v>
+        <v>528887</v>
       </c>
       <c r="R12" t="n">
-        <v>6998093</v>
+        <v>6998044</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,9 +1867,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,22 +1899,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122824314</v>
+        <v>122825055</v>
       </c>
       <c r="B13" t="n">
-        <v>78508</v>
+        <v>79852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1927,21 +1927,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,13 +1951,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>528828</v>
+        <v>529003</v>
       </c>
       <c r="R13" t="n">
-        <v>6998005</v>
+        <v>6998021</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2028,10 +2028,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122825055</v>
+        <v>122824729</v>
       </c>
       <c r="B14" t="n">
-        <v>79852</v>
+        <v>78771</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529003</v>
+        <v>528904</v>
       </c>
       <c r="R14" t="n">
-        <v>6998021</v>
+        <v>6998036</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,22 +2133,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122824729</v>
+        <v>122824314</v>
       </c>
       <c r="B15" t="n">
-        <v>78771</v>
+        <v>78508</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2161,21 +2161,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528904</v>
+        <v>528828</v>
       </c>
       <c r="R15" t="n">
-        <v>6998036</v>
+        <v>6998005</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2250,12 +2250,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -4674,10 +4674,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122823308</v>
+        <v>122823666</v>
       </c>
       <c r="B37" t="n">
-        <v>78507</v>
+        <v>57481</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4690,37 +4690,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528904</v>
+        <v>528890</v>
       </c>
       <c r="R37" t="n">
-        <v>6998141</v>
+        <v>6998089</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4747,24 +4752,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4779,22 +4774,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122824419</v>
+        <v>122823959</v>
       </c>
       <c r="B38" t="n">
-        <v>79389</v>
+        <v>79853</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4807,21 +4802,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>2081</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4831,13 +4826,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528853</v>
+        <v>528918</v>
       </c>
       <c r="R38" t="n">
-        <v>6998012</v>
+        <v>6998048</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4866,7 +4861,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4876,12 +4871,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På ved på gammal tallhögstubbe</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4896,22 +4891,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122823959</v>
+        <v>122823308</v>
       </c>
       <c r="B39" t="n">
-        <v>79853</v>
+        <v>78507</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4924,21 +4919,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4948,13 +4943,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528918</v>
+        <v>528904</v>
       </c>
       <c r="R39" t="n">
-        <v>6998048</v>
+        <v>6998141</v>
       </c>
       <c r="S39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4983,7 +4978,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4993,12 +4988,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5013,22 +5008,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122823666</v>
+        <v>122824419</v>
       </c>
       <c r="B40" t="n">
-        <v>57481</v>
+        <v>79389</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5041,39 +5036,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528890</v>
+        <v>528853</v>
       </c>
       <c r="R40" t="n">
-        <v>6998089</v>
+        <v>6998012</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5103,14 +5093,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5125,12 +5125,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122825157</v>
+        <v>122824203</v>
       </c>
       <c r="B43" t="n">
-        <v>79852</v>
+        <v>56691</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5378,38 +5378,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528946</v>
+        <v>528874</v>
       </c>
       <c r="R43" t="n">
-        <v>6998089</v>
+        <v>6998038</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5439,9 +5444,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt med spillning under tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5456,19 +5476,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122823605</v>
+        <v>122825157</v>
       </c>
       <c r="B44" t="n">
         <v>79852</v>
@@ -5508,10 +5528,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528887</v>
+        <v>528946</v>
       </c>
       <c r="R44" t="n">
-        <v>6998073</v>
+        <v>6998089</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5541,24 +5561,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5573,22 +5578,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122823389</v>
+        <v>122823605</v>
       </c>
       <c r="B45" t="n">
-        <v>78771</v>
+        <v>79852</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5601,46 +5606,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528893</v>
+        <v>528887</v>
       </c>
       <c r="R45" t="n">
-        <v>6998121</v>
+        <v>6998073</v>
       </c>
       <c r="S45" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5669,7 +5665,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5679,12 +5675,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5711,10 +5707,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122824203</v>
+        <v>122823389</v>
       </c>
       <c r="B46" t="n">
-        <v>56691</v>
+        <v>78771</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5723,31 +5719,35 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5756,13 +5756,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528874</v>
+        <v>528893</v>
       </c>
       <c r="R46" t="n">
-        <v>6998038</v>
+        <v>6998121</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5791,7 +5791,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Rikligt med spillning under tall</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5821,12 +5821,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 55395-2024 artfynd.xlsx
+++ b/artfynd/A 55395-2024 artfynd.xlsx
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122825059</v>
+        <v>122824504</v>
       </c>
       <c r="B3" t="n">
-        <v>77704</v>
+        <v>57634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,34 +817,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228579</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>528960</v>
+        <v>528884</v>
       </c>
       <c r="R3" t="n">
-        <v>6998066</v>
+        <v>6997998</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,24 +883,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,22 +900,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122823935</v>
+        <v>122823308</v>
       </c>
       <c r="B4" t="n">
-        <v>79852</v>
+        <v>78508</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,21 +928,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>528934</v>
+        <v>528904</v>
       </c>
       <c r="R4" t="n">
-        <v>6998051</v>
+        <v>6998141</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +997,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,22 +1017,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122823776</v>
+        <v>122824996</v>
       </c>
       <c r="B5" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,24 +1063,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528879</v>
+        <v>528952</v>
       </c>
       <c r="R5" t="n">
-        <v>6998065</v>
+        <v>6998039</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1113,9 +1102,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande glasbjörk med savflöde</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,22 +1134,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122824296</v>
+        <v>122823959</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
+        <v>79854</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,42 +1162,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>528849</v>
+        <v>528918</v>
       </c>
       <c r="R6" t="n">
-        <v>6998016</v>
+        <v>6998048</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1220,14 +1219,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,22 +1251,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122824775</v>
+        <v>122823876</v>
       </c>
       <c r="B7" t="n">
-        <v>90922</v>
+        <v>78772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,41 +1275,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>528928</v>
+        <v>528897</v>
       </c>
       <c r="R7" t="n">
-        <v>6998037</v>
+        <v>6998064</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,12 +1357,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal död stående gran i gammal barrblandskog</t>
+          <t>På gamla granar i gammal senvuxen granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122825192</v>
+        <v>122824798</v>
       </c>
       <c r="B8" t="n">
-        <v>79853</v>
+        <v>74866</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,21 +1405,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,13 +1429,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>528946</v>
+        <v>528929</v>
       </c>
       <c r="R8" t="n">
-        <v>6998089</v>
+        <v>6998043</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,9 +1462,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1461,22 +1494,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122823780</v>
+        <v>122823616</v>
       </c>
       <c r="B9" t="n">
-        <v>79853</v>
+        <v>79813</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,25 +1518,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>229497</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,10 +1546,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>528879</v>
+        <v>528903</v>
       </c>
       <c r="R9" t="n">
-        <v>6998066</v>
+        <v>6998106</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,9 +1579,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,22 +1611,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122824996</v>
+        <v>122825263</v>
       </c>
       <c r="B10" t="n">
-        <v>79852</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,37 +1639,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>528952</v>
+        <v>528938</v>
       </c>
       <c r="R10" t="n">
-        <v>6998039</v>
+        <v>6998101</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1648,24 +1701,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark på stam av levande glasbjörk med savflöde</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1680,22 +1723,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122823640</v>
+        <v>122825093</v>
       </c>
       <c r="B11" t="n">
-        <v>79852</v>
+        <v>91530</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,25 +1747,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1732,10 +1775,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>528890</v>
+        <v>528967</v>
       </c>
       <c r="R11" t="n">
-        <v>6998093</v>
+        <v>6998079</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1765,9 +1808,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1782,22 +1840,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122824159</v>
+        <v>122825192</v>
       </c>
       <c r="B12" t="n">
-        <v>77704</v>
+        <v>79854</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1810,21 +1868,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1834,10 +1892,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>528887</v>
+        <v>528946</v>
       </c>
       <c r="R12" t="n">
-        <v>6998044</v>
+        <v>6998089</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1867,24 +1925,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1899,22 +1942,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122825055</v>
+        <v>122823224</v>
       </c>
       <c r="B13" t="n">
-        <v>79852</v>
+        <v>79757</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,25 +1966,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1951,13 +1994,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529003</v>
+        <v>528911</v>
       </c>
       <c r="R13" t="n">
-        <v>6998021</v>
+        <v>6998157</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1986,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1996,12 +2039,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På bark på stam av levande gammal asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2016,22 +2059,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122824729</v>
+        <v>122823935</v>
       </c>
       <c r="B14" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,21 +2087,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2068,13 +2111,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>528904</v>
+        <v>528934</v>
       </c>
       <c r="R14" t="n">
-        <v>6998036</v>
+        <v>6998051</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2103,7 +2146,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2113,12 +2156,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2133,22 +2176,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122824314</v>
+        <v>122823640</v>
       </c>
       <c r="B15" t="n">
-        <v>78508</v>
+        <v>79853</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2161,21 +2204,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2185,13 +2228,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>528828</v>
+        <v>528890</v>
       </c>
       <c r="R15" t="n">
-        <v>6998005</v>
+        <v>6998093</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2218,24 +2261,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2250,22 +2278,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122824617</v>
+        <v>122824669</v>
       </c>
       <c r="B16" t="n">
-        <v>78507</v>
+        <v>79853</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2278,21 +2306,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2302,10 +2330,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>528897</v>
+        <v>528962</v>
       </c>
       <c r="R16" t="n">
-        <v>6998014</v>
+        <v>6998022</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,24 +2363,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2367,22 +2380,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122824915</v>
+        <v>122824138</v>
       </c>
       <c r="B17" t="n">
-        <v>79852</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2395,34 +2408,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>528964</v>
+        <v>528887</v>
       </c>
       <c r="R17" t="n">
-        <v>6998032</v>
+        <v>6998044</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,7 +2476,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2464,12 +2486,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På asp i gammal barrblandskog</t>
+          <t>På gamla granar i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,10 +2518,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122824798</v>
+        <v>122824608</v>
       </c>
       <c r="B18" t="n">
-        <v>74866</v>
+        <v>56683</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2512,37 +2534,46 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>528929</v>
+        <v>528928</v>
       </c>
       <c r="R18" t="n">
-        <v>6998043</v>
+        <v>6998035</v>
       </c>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2569,24 +2600,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,22 +2617,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122824294</v>
+        <v>122824617</v>
       </c>
       <c r="B19" t="n">
-        <v>78771</v>
+        <v>78508</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2629,21 +2645,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2653,10 +2669,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528874</v>
+        <v>528897</v>
       </c>
       <c r="R19" t="n">
-        <v>6998038</v>
+        <v>6998014</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2688,7 +2704,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2698,12 +2714,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal tall</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,10 +2746,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122823542</v>
+        <v>122823653</v>
       </c>
       <c r="B20" t="n">
-        <v>78508</v>
+        <v>74866</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2746,21 +2762,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2770,13 +2786,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>528881</v>
+        <v>528898</v>
       </c>
       <c r="R20" t="n">
-        <v>6998117</v>
+        <v>6998091</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2805,7 +2821,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2815,12 +2831,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2840,17 +2856,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122824645</v>
+        <v>122823789</v>
       </c>
       <c r="B21" t="n">
-        <v>78508</v>
+        <v>79854</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2863,21 +2879,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2887,10 +2903,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>528897</v>
+        <v>528910</v>
       </c>
       <c r="R21" t="n">
-        <v>6998014</v>
+        <v>6998072</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2922,7 +2938,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2932,12 +2948,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
+          <t>På sälglåga i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2964,7 +2980,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122823534</v>
+        <v>122823666</v>
       </c>
       <c r="B22" t="n">
         <v>57481</v>
@@ -3009,10 +3025,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>528883</v>
+        <v>528890</v>
       </c>
       <c r="R22" t="n">
-        <v>6998125</v>
+        <v>6998089</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3076,10 +3092,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122824608</v>
+        <v>122825157</v>
       </c>
       <c r="B23" t="n">
-        <v>56683</v>
+        <v>79853</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3092,43 +3108,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>528928</v>
+        <v>528946</v>
       </c>
       <c r="R23" t="n">
-        <v>6998035</v>
+        <v>6998089</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3187,10 +3194,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122824716</v>
+        <v>122824294</v>
       </c>
       <c r="B24" t="n">
-        <v>79852</v>
+        <v>78772</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3203,21 +3210,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3227,10 +3234,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>528980</v>
+        <v>528874</v>
       </c>
       <c r="R24" t="n">
-        <v>6998018</v>
+        <v>6998038</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3260,9 +3267,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På gammal tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3277,22 +3299,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122824669</v>
+        <v>122823389</v>
       </c>
       <c r="B25" t="n">
-        <v>79852</v>
+        <v>78772</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3305,37 +3327,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>528962</v>
+        <v>528893</v>
       </c>
       <c r="R25" t="n">
-        <v>6998022</v>
+        <v>6998121</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3362,9 +3393,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3379,22 +3425,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122824504</v>
+        <v>122823542</v>
       </c>
       <c r="B26" t="n">
-        <v>57634</v>
+        <v>78509</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3407,46 +3453,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>528884</v>
+        <v>528881</v>
       </c>
       <c r="R26" t="n">
-        <v>6997998</v>
+        <v>6998117</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3473,9 +3510,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3490,22 +3542,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122823224</v>
+        <v>122824689</v>
       </c>
       <c r="B27" t="n">
-        <v>79756</v>
+        <v>78417</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3514,25 +3566,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3542,10 +3594,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>528911</v>
+        <v>528901</v>
       </c>
       <c r="R27" t="n">
-        <v>6998157</v>
+        <v>6998033</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3577,7 +3629,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3587,12 +3639,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp i gammal granskog</t>
+          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3619,10 +3671,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122823653</v>
+        <v>122823780</v>
       </c>
       <c r="B28" t="n">
-        <v>74866</v>
+        <v>79854</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3635,21 +3687,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3659,10 +3711,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>528898</v>
+        <v>528879</v>
       </c>
       <c r="R28" t="n">
-        <v>6998091</v>
+        <v>6998066</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3692,24 +3744,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:38</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3724,22 +3761,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122824114</v>
+        <v>122824915</v>
       </c>
       <c r="B29" t="n">
-        <v>74866</v>
+        <v>79853</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3752,21 +3789,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3776,10 +3813,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>528886</v>
+        <v>528964</v>
       </c>
       <c r="R29" t="n">
-        <v>6998049</v>
+        <v>6998032</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3811,7 +3848,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3821,12 +3858,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På asp i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3853,10 +3890,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122824138</v>
+        <v>122823605</v>
       </c>
       <c r="B30" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3869,33 +3906,24 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
@@ -3905,7 +3933,7 @@
         <v>528887</v>
       </c>
       <c r="R30" t="n">
-        <v>6998044</v>
+        <v>6998073</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3937,7 +3965,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3947,12 +3975,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal granskog</t>
+          <t>På asplåga</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3967,22 +3995,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122824517</v>
+        <v>122824940</v>
       </c>
       <c r="B31" t="n">
-        <v>78508</v>
+        <v>79853</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3995,37 +4023,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>528878</v>
+        <v>528993</v>
       </c>
       <c r="R31" t="n">
-        <v>6997997</v>
+        <v>6998013</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4054,7 +4091,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4064,12 +4101,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4084,22 +4116,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122825263</v>
+        <v>122823943</v>
       </c>
       <c r="B32" t="n">
-        <v>57481</v>
+        <v>79853</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4112,27 +4144,27 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4141,10 +4173,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>528938</v>
+        <v>528895</v>
       </c>
       <c r="R32" t="n">
-        <v>6998101</v>
+        <v>6998055</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4177,11 +4209,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4208,10 +4235,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122823876</v>
+        <v>122824314</v>
       </c>
       <c r="B33" t="n">
-        <v>78771</v>
+        <v>78509</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4224,46 +4251,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>528897</v>
+        <v>528828</v>
       </c>
       <c r="R33" t="n">
-        <v>6998064</v>
+        <v>6998005</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4292,7 +4310,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4302,12 +4320,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gamla granar i gammal senvuxen granskog</t>
+          <t>På kolad ved på gammal tallstubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4322,22 +4340,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122824871</v>
+        <v>122824419</v>
       </c>
       <c r="B34" t="n">
-        <v>79756</v>
+        <v>79390</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4346,25 +4364,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4374,13 +4392,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>528956</v>
+        <v>528853</v>
       </c>
       <c r="R34" t="n">
-        <v>6998028</v>
+        <v>6998012</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4409,7 +4427,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4419,12 +4437,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På asp i gammal granskog</t>
+          <t>På ved på gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4451,10 +4469,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122824928</v>
+        <v>122824871</v>
       </c>
       <c r="B35" t="n">
-        <v>79852</v>
+        <v>79757</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4463,25 +4481,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4491,13 +4509,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>528989</v>
+        <v>528956</v>
       </c>
       <c r="R35" t="n">
-        <v>6998039</v>
+        <v>6998028</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4524,9 +4542,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På asp i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4541,22 +4574,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122824940</v>
+        <v>122824775</v>
       </c>
       <c r="B36" t="n">
-        <v>79852</v>
+        <v>90928</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4565,50 +4598,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>528993</v>
+        <v>528928</v>
       </c>
       <c r="R36" t="n">
-        <v>6998013</v>
+        <v>6998037</v>
       </c>
       <c r="S36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4637,7 +4661,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4647,7 +4671,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gammal död stående gran i gammal barrblandskog</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4662,22 +4691,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122823666</v>
+        <v>122824517</v>
       </c>
       <c r="B37" t="n">
-        <v>57481</v>
+        <v>78509</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4690,42 +4719,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>528890</v>
+        <v>528878</v>
       </c>
       <c r="R37" t="n">
-        <v>6998089</v>
+        <v>6997997</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4752,14 +4776,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På kolad ved på gammal dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4774,19 +4808,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122823959</v>
+        <v>122824139</v>
       </c>
       <c r="B38" t="n">
         <v>79853</v>
@@ -4802,21 +4836,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4826,13 +4860,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>528918</v>
+        <v>528870</v>
       </c>
       <c r="R38" t="n">
-        <v>6998048</v>
+        <v>6997994</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4861,7 +4895,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4871,12 +4905,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På gammal sälg</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4903,10 +4932,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122823308</v>
+        <v>122824296</v>
       </c>
       <c r="B39" t="n">
-        <v>78507</v>
+        <v>57481</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4919,37 +4948,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>528904</v>
+        <v>528849</v>
       </c>
       <c r="R39" t="n">
-        <v>6998141</v>
+        <v>6998016</v>
       </c>
       <c r="S39" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4976,24 +5010,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:26</t>
-        </is>
-      </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På kolad ved på grov dimensionsavverkningsstubbe av tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5008,22 +5032,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122824419</v>
+        <v>122824729</v>
       </c>
       <c r="B40" t="n">
-        <v>79389</v>
+        <v>78772</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5036,21 +5060,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5060,10 +5084,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>528853</v>
+        <v>528904</v>
       </c>
       <c r="R40" t="n">
-        <v>6998012</v>
+        <v>6998036</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5095,7 +5119,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5105,12 +5129,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På ved på gammal tallhögstubbe</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5137,10 +5161,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122825093</v>
+        <v>122824114</v>
       </c>
       <c r="B41" t="n">
-        <v>91524</v>
+        <v>74866</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5149,25 +5173,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>760</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5177,10 +5201,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>528967</v>
+        <v>528886</v>
       </c>
       <c r="R41" t="n">
-        <v>6998079</v>
+        <v>6998049</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5212,7 +5236,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5222,12 +5246,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal sälg</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5254,10 +5278,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122824139</v>
+        <v>122825059</v>
       </c>
       <c r="B42" t="n">
-        <v>79852</v>
+        <v>77705</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5270,21 +5294,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5294,13 +5318,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>528870</v>
+        <v>528960</v>
       </c>
       <c r="R42" t="n">
-        <v>6997994</v>
+        <v>6998066</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5329,7 +5353,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5339,7 +5363,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5354,7 +5383,7 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -5366,10 +5395,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122824203</v>
+        <v>122823534</v>
       </c>
       <c r="B43" t="n">
-        <v>56691</v>
+        <v>57481</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5378,31 +5407,31 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5411,10 +5440,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>528874</v>
+        <v>528883</v>
       </c>
       <c r="R43" t="n">
-        <v>6998038</v>
+        <v>6998125</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5444,24 +5473,14 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt med spillning under tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5476,22 +5495,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122825157</v>
+        <v>122824203</v>
       </c>
       <c r="B44" t="n">
-        <v>79852</v>
+        <v>56691</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5500,38 +5519,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>528946</v>
+        <v>528874</v>
       </c>
       <c r="R44" t="n">
-        <v>6998089</v>
+        <v>6998038</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5561,9 +5585,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Rikligt med spillning under tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5578,22 +5617,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122823605</v>
+        <v>122825055</v>
       </c>
       <c r="B45" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5630,13 +5669,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>528887</v>
+        <v>529003</v>
       </c>
       <c r="R45" t="n">
-        <v>6998073</v>
+        <v>6998021</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5665,7 +5704,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5675,12 +5714,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På asplåga</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5700,17 +5739,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122823389</v>
+        <v>122824928</v>
       </c>
       <c r="B46" t="n">
-        <v>78771</v>
+        <v>79853</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5723,46 +5762,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>528893</v>
+        <v>528989</v>
       </c>
       <c r="R46" t="n">
-        <v>6998121</v>
+        <v>6998039</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5789,24 +5819,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5821,22 +5836,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122823616</v>
+        <v>122823776</v>
       </c>
       <c r="B47" t="n">
-        <v>79812</v>
+        <v>79853</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5845,38 +5860,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>528903</v>
+        <v>528879</v>
       </c>
       <c r="R47" t="n">
-        <v>6998106</v>
+        <v>6998065</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5906,24 +5926,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På bark på mycket grov asplåga (70 cm diameter)</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5938,22 +5943,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122824883</v>
+        <v>122824716</v>
       </c>
       <c r="B48" t="n">
-        <v>79852</v>
+        <v>79853</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5983,29 +5988,20 @@
           <t>(L.) Hoffm.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>528973</v>
+        <v>528980</v>
       </c>
       <c r="R48" t="n">
-        <v>6998038</v>
+        <v>6998018</v>
       </c>
       <c r="S48" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6032,24 +6028,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6064,22 +6045,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122824689</v>
+        <v>122824645</v>
       </c>
       <c r="B49" t="n">
-        <v>78416</v>
+        <v>78509</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6092,21 +6073,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6116,10 +6097,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>528901</v>
+        <v>528897</v>
       </c>
       <c r="R49" t="n">
-        <v>6998033</v>
+        <v>6998014</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6151,7 +6132,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6161,12 +6142,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gammal grov dimensionsavverkningsstubbe av tall i gammal tallskog</t>
+          <t>På kolad ved på gammal grov dimensionsavverkningsstubbe av tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6193,7 +6174,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122823789</v>
+        <v>122824883</v>
       </c>
       <c r="B50" t="n">
         <v>79853</v>
@@ -6209,37 +6190,46 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>528910</v>
+        <v>528973</v>
       </c>
       <c r="R50" t="n">
-        <v>6998072</v>
+        <v>6998038</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6268,7 +6258,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6278,12 +6268,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På sälglåga i gammal granskog</t>
+          <t>På död sälg (kort)</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6298,22 +6288,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122823943</v>
+        <v>122824159</v>
       </c>
       <c r="B51" t="n">
-        <v>79852</v>
+        <v>77705</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6326,39 +6316,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Valbergsmyran, Valbergsmyran, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>528895</v>
+        <v>528887</v>
       </c>
       <c r="R51" t="n">
-        <v>6998055</v>
+        <v>6998044</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6388,9 +6373,24 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6405,12 +6405,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
